--- a/app-karyawan/public/templates/master-karyawan-import-template.xlsx
+++ b/app-karyawan/public/templates/master-karyawan-import-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data Import" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Referensi" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Import" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referensi" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="EmploymentTypeList">'Referensi'!$A$2:$A$3</definedName>
@@ -19,6 +19,7 @@
     <definedName name="DepartmentList">'Referensi'!$F$2:$F$2</definedName>
     <definedName name="JobRoleList">'Referensi'!$G$2:$G$2</definedName>
     <definedName name="JobLevelList">'Referensi'!$H$2:$H$2</definedName>
+    <definedName name="GroupShiftList">'Referensi'!$I$2:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Import'!$A$1:$R$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -542,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R202"/>
+  <dimension ref="A1:S202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -596,62 +597,67 @@
           <t>Department</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Group Shift</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Length Of Service</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Birth Date</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Gender</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Work Location</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Job Role</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Job Level</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Education Level</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Join Date</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Phone Number</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
@@ -688,62 +694,67 @@
           <t>Harus sesuai Master Department</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Harus sesuai Master Group Shift</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Otomatis dari Join Date</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Otomatis dari Birth Date</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Format tanggal DD/MM/YYYY</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Pilih Male atau Female</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Harus sesuai Master Work Location</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Harus sesuai Master Job Role</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Harus sesuai Master Job Level</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Pilih SMA, D3, S1, atau S2</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Pilih Rank 1 sampai Rank 9</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>Format tanggal DD/MM/YYYY</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Nomor telepon</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Email aktif karyawan</t>
         </is>
@@ -760,24 +771,24 @@
         </is>
       </c>
       <c r="F3" s="4" t="n"/>
-      <c r="G3" s="5">
-        <f>IF(P3="","",DATEDIF(P3,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P3,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H3" s="5">
-        <f>IF(I3="","",DATEDIF(I3,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I3" s="6" t="n"/>
-      <c r="J3" s="4" t="n"/>
+        <f>IF(Q3="","",DATEDIF(Q3,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q3,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I3" s="5">
+        <f>IF(J3="","",DATEDIF(J3,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J3" s="6" t="n"/>
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
       <c r="M3" s="4" t="n"/>
       <c r="N3" s="4" t="n"/>
       <c r="O3" s="4" t="n"/>
-      <c r="P3" s="6" t="n"/>
-      <c r="Q3" s="3" t="n"/>
-      <c r="R3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
+      <c r="Q3" s="6" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
@@ -790,24 +801,24 @@
         </is>
       </c>
       <c r="F4" s="4" t="n"/>
-      <c r="G4" s="5">
-        <f>IF(P4="","",DATEDIF(P4,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P4,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H4" s="5">
-        <f>IF(I4="","",DATEDIF(I4,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="4" t="n"/>
+        <f>IF(Q4="","",DATEDIF(Q4,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q4,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I4" s="5">
+        <f>IF(J4="","",DATEDIF(J4,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J4" s="6" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="4" t="n"/>
       <c r="N4" s="4" t="n"/>
       <c r="O4" s="4" t="n"/>
-      <c r="P4" s="6" t="n"/>
-      <c r="Q4" s="3" t="n"/>
-      <c r="R4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
+      <c r="Q4" s="6" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
@@ -820,24 +831,24 @@
         </is>
       </c>
       <c r="F5" s="4" t="n"/>
-      <c r="G5" s="5">
-        <f>IF(P5="","",DATEDIF(P5,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P5,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H5" s="5">
-        <f>IF(I5="","",DATEDIF(I5,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="4" t="n"/>
+        <f>IF(Q5="","",DATEDIF(Q5,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q5,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I5" s="5">
+        <f>IF(J5="","",DATEDIF(J5,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J5" s="6" t="n"/>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
       <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
-      <c r="P5" s="6" t="n"/>
-      <c r="Q5" s="3" t="n"/>
-      <c r="R5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="6" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
@@ -850,24 +861,24 @@
         </is>
       </c>
       <c r="F6" s="4" t="n"/>
-      <c r="G6" s="5">
-        <f>IF(P6="","",DATEDIF(P6,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P6,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H6" s="5">
-        <f>IF(I6="","",DATEDIF(I6,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="4" t="n"/>
+        <f>IF(Q6="","",DATEDIF(Q6,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q6,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I6" s="5">
+        <f>IF(J6="","",DATEDIF(J6,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J6" s="6" t="n"/>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
       <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="n"/>
-      <c r="P6" s="6" t="n"/>
-      <c r="Q6" s="3" t="n"/>
-      <c r="R6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="6" t="n"/>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
@@ -880,24 +891,24 @@
         </is>
       </c>
       <c r="F7" s="4" t="n"/>
-      <c r="G7" s="5">
-        <f>IF(P7="","",DATEDIF(P7,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P7,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H7" s="5">
-        <f>IF(I7="","",DATEDIF(I7,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="4" t="n"/>
+        <f>IF(Q7="","",DATEDIF(Q7,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q7,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I7" s="5">
+        <f>IF(J7="","",DATEDIF(J7,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J7" s="6" t="n"/>
       <c r="K7" s="4" t="n"/>
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
       <c r="N7" s="4" t="n"/>
       <c r="O7" s="4" t="n"/>
-      <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="3" t="n"/>
-      <c r="R7" s="4" t="n"/>
+      <c r="P7" s="4" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
@@ -910,24 +921,24 @@
         </is>
       </c>
       <c r="F8" s="4" t="n"/>
-      <c r="G8" s="5">
-        <f>IF(P8="","",DATEDIF(P8,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P8,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H8" s="5">
-        <f>IF(I8="","",DATEDIF(I8,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="4" t="n"/>
+        <f>IF(Q8="","",DATEDIF(Q8,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q8,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I8" s="5">
+        <f>IF(J8="","",DATEDIF(J8,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J8" s="6" t="n"/>
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
       <c r="M8" s="4" t="n"/>
       <c r="N8" s="4" t="n"/>
       <c r="O8" s="4" t="n"/>
-      <c r="P8" s="6" t="n"/>
-      <c r="Q8" s="3" t="n"/>
-      <c r="R8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
+      <c r="Q8" s="6" t="n"/>
+      <c r="R8" s="3" t="n"/>
+      <c r="S8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
@@ -940,24 +951,24 @@
         </is>
       </c>
       <c r="F9" s="4" t="n"/>
-      <c r="G9" s="5">
-        <f>IF(P9="","",DATEDIF(P9,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P9,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H9" s="5">
-        <f>IF(I9="","",DATEDIF(I9,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="4" t="n"/>
+        <f>IF(Q9="","",DATEDIF(Q9,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q9,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I9" s="5">
+        <f>IF(J9="","",DATEDIF(J9,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J9" s="6" t="n"/>
       <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n"/>
       <c r="M9" s="4" t="n"/>
       <c r="N9" s="4" t="n"/>
       <c r="O9" s="4" t="n"/>
-      <c r="P9" s="6" t="n"/>
-      <c r="Q9" s="3" t="n"/>
-      <c r="R9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
+      <c r="Q9" s="6" t="n"/>
+      <c r="R9" s="3" t="n"/>
+      <c r="S9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n"/>
@@ -970,24 +981,24 @@
         </is>
       </c>
       <c r="F10" s="4" t="n"/>
-      <c r="G10" s="5">
-        <f>IF(P10="","",DATEDIF(P10,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P10,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H10" s="5">
-        <f>IF(I10="","",DATEDIF(I10,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="4" t="n"/>
+        <f>IF(Q10="","",DATEDIF(Q10,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q10,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I10" s="5">
+        <f>IF(J10="","",DATEDIF(J10,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J10" s="6" t="n"/>
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
       <c r="N10" s="4" t="n"/>
       <c r="O10" s="4" t="n"/>
-      <c r="P10" s="6" t="n"/>
-      <c r="Q10" s="3" t="n"/>
-      <c r="R10" s="4" t="n"/>
+      <c r="P10" s="4" t="n"/>
+      <c r="Q10" s="6" t="n"/>
+      <c r="R10" s="3" t="n"/>
+      <c r="S10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
@@ -1000,24 +1011,24 @@
         </is>
       </c>
       <c r="F11" s="4" t="n"/>
-      <c r="G11" s="5">
-        <f>IF(P11="","",DATEDIF(P11,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P11,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H11" s="5">
-        <f>IF(I11="","",DATEDIF(I11,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="4" t="n"/>
+        <f>IF(Q11="","",DATEDIF(Q11,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q11,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I11" s="5">
+        <f>IF(J11="","",DATEDIF(J11,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J11" s="6" t="n"/>
       <c r="K11" s="4" t="n"/>
       <c r="L11" s="4" t="n"/>
       <c r="M11" s="4" t="n"/>
       <c r="N11" s="4" t="n"/>
       <c r="O11" s="4" t="n"/>
-      <c r="P11" s="6" t="n"/>
-      <c r="Q11" s="3" t="n"/>
-      <c r="R11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
+      <c r="Q11" s="6" t="n"/>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
@@ -1030,24 +1041,24 @@
         </is>
       </c>
       <c r="F12" s="4" t="n"/>
-      <c r="G12" s="5">
-        <f>IF(P12="","",DATEDIF(P12,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P12,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H12" s="5">
-        <f>IF(I12="","",DATEDIF(I12,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="4" t="n"/>
+        <f>IF(Q12="","",DATEDIF(Q12,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q12,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I12" s="5">
+        <f>IF(J12="","",DATEDIF(J12,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J12" s="6" t="n"/>
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4" t="n"/>
       <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
-      <c r="P12" s="6" t="n"/>
-      <c r="Q12" s="3" t="n"/>
-      <c r="R12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
+      <c r="Q12" s="6" t="n"/>
+      <c r="R12" s="3" t="n"/>
+      <c r="S12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
@@ -1060,24 +1071,24 @@
         </is>
       </c>
       <c r="F13" s="4" t="n"/>
-      <c r="G13" s="5">
-        <f>IF(P13="","",DATEDIF(P13,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P13,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H13" s="5">
-        <f>IF(I13="","",DATEDIF(I13,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="4" t="n"/>
+        <f>IF(Q13="","",DATEDIF(Q13,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q13,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I13" s="5">
+        <f>IF(J13="","",DATEDIF(J13,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J13" s="6" t="n"/>
       <c r="K13" s="4" t="n"/>
       <c r="L13" s="4" t="n"/>
       <c r="M13" s="4" t="n"/>
       <c r="N13" s="4" t="n"/>
       <c r="O13" s="4" t="n"/>
-      <c r="P13" s="6" t="n"/>
-      <c r="Q13" s="3" t="n"/>
-      <c r="R13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
+      <c r="Q13" s="6" t="n"/>
+      <c r="R13" s="3" t="n"/>
+      <c r="S13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
@@ -1090,24 +1101,24 @@
         </is>
       </c>
       <c r="F14" s="4" t="n"/>
-      <c r="G14" s="5">
-        <f>IF(P14="","",DATEDIF(P14,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P14,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H14" s="5">
-        <f>IF(I14="","",DATEDIF(I14,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="4" t="n"/>
+        <f>IF(Q14="","",DATEDIF(Q14,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q14,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I14" s="5">
+        <f>IF(J14="","",DATEDIF(J14,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J14" s="6" t="n"/>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n"/>
       <c r="N14" s="4" t="n"/>
       <c r="O14" s="4" t="n"/>
-      <c r="P14" s="6" t="n"/>
-      <c r="Q14" s="3" t="n"/>
-      <c r="R14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
+      <c r="Q14" s="6" t="n"/>
+      <c r="R14" s="3" t="n"/>
+      <c r="S14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -1120,24 +1131,24 @@
         </is>
       </c>
       <c r="F15" s="4" t="n"/>
-      <c r="G15" s="5">
-        <f>IF(P15="","",DATEDIF(P15,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P15,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H15" s="5">
-        <f>IF(I15="","",DATEDIF(I15,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="4" t="n"/>
+        <f>IF(Q15="","",DATEDIF(Q15,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q15,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I15" s="5">
+        <f>IF(J15="","",DATEDIF(J15,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J15" s="6" t="n"/>
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="n"/>
       <c r="M15" s="4" t="n"/>
       <c r="N15" s="4" t="n"/>
       <c r="O15" s="4" t="n"/>
-      <c r="P15" s="6" t="n"/>
-      <c r="Q15" s="3" t="n"/>
-      <c r="R15" s="4" t="n"/>
+      <c r="P15" s="4" t="n"/>
+      <c r="Q15" s="6" t="n"/>
+      <c r="R15" s="3" t="n"/>
+      <c r="S15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n"/>
@@ -1150,24 +1161,24 @@
         </is>
       </c>
       <c r="F16" s="4" t="n"/>
-      <c r="G16" s="5">
-        <f>IF(P16="","",DATEDIF(P16,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P16,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H16" s="5">
-        <f>IF(I16="","",DATEDIF(I16,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="4" t="n"/>
+        <f>IF(Q16="","",DATEDIF(Q16,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q16,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I16" s="5">
+        <f>IF(J16="","",DATEDIF(J16,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J16" s="6" t="n"/>
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="n"/>
       <c r="O16" s="4" t="n"/>
-      <c r="P16" s="6" t="n"/>
-      <c r="Q16" s="3" t="n"/>
-      <c r="R16" s="4" t="n"/>
+      <c r="P16" s="4" t="n"/>
+      <c r="Q16" s="6" t="n"/>
+      <c r="R16" s="3" t="n"/>
+      <c r="S16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
@@ -1180,24 +1191,24 @@
         </is>
       </c>
       <c r="F17" s="4" t="n"/>
-      <c r="G17" s="5">
-        <f>IF(P17="","",DATEDIF(P17,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P17,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H17" s="5">
-        <f>IF(I17="","",DATEDIF(I17,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="4" t="n"/>
+        <f>IF(Q17="","",DATEDIF(Q17,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q17,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I17" s="5">
+        <f>IF(J17="","",DATEDIF(J17,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J17" s="6" t="n"/>
       <c r="K17" s="4" t="n"/>
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n"/>
       <c r="O17" s="4" t="n"/>
-      <c r="P17" s="6" t="n"/>
-      <c r="Q17" s="3" t="n"/>
-      <c r="R17" s="4" t="n"/>
+      <c r="P17" s="4" t="n"/>
+      <c r="Q17" s="6" t="n"/>
+      <c r="R17" s="3" t="n"/>
+      <c r="S17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n"/>
@@ -1210,24 +1221,24 @@
         </is>
       </c>
       <c r="F18" s="4" t="n"/>
-      <c r="G18" s="5">
-        <f>IF(P18="","",DATEDIF(P18,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P18,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H18" s="5">
-        <f>IF(I18="","",DATEDIF(I18,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="4" t="n"/>
+        <f>IF(Q18="","",DATEDIF(Q18,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q18,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I18" s="5">
+        <f>IF(J18="","",DATEDIF(J18,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J18" s="6" t="n"/>
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
       <c r="N18" s="4" t="n"/>
       <c r="O18" s="4" t="n"/>
-      <c r="P18" s="6" t="n"/>
-      <c r="Q18" s="3" t="n"/>
-      <c r="R18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
+      <c r="Q18" s="6" t="n"/>
+      <c r="R18" s="3" t="n"/>
+      <c r="S18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
@@ -1240,24 +1251,24 @@
         </is>
       </c>
       <c r="F19" s="4" t="n"/>
-      <c r="G19" s="5">
-        <f>IF(P19="","",DATEDIF(P19,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P19,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H19" s="5">
-        <f>IF(I19="","",DATEDIF(I19,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="4" t="n"/>
+        <f>IF(Q19="","",DATEDIF(Q19,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q19,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I19" s="5">
+        <f>IF(J19="","",DATEDIF(J19,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J19" s="6" t="n"/>
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
       <c r="M19" s="4" t="n"/>
       <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
-      <c r="P19" s="6" t="n"/>
-      <c r="Q19" s="3" t="n"/>
-      <c r="R19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
+      <c r="Q19" s="6" t="n"/>
+      <c r="R19" s="3" t="n"/>
+      <c r="S19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
@@ -1270,24 +1281,24 @@
         </is>
       </c>
       <c r="F20" s="4" t="n"/>
-      <c r="G20" s="5">
-        <f>IF(P20="","",DATEDIF(P20,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P20,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H20" s="5">
-        <f>IF(I20="","",DATEDIF(I20,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="4" t="n"/>
+        <f>IF(Q20="","",DATEDIF(Q20,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q20,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I20" s="5">
+        <f>IF(J20="","",DATEDIF(J20,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J20" s="6" t="n"/>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
       <c r="O20" s="4" t="n"/>
-      <c r="P20" s="6" t="n"/>
-      <c r="Q20" s="3" t="n"/>
-      <c r="R20" s="4" t="n"/>
+      <c r="P20" s="4" t="n"/>
+      <c r="Q20" s="6" t="n"/>
+      <c r="R20" s="3" t="n"/>
+      <c r="S20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n"/>
@@ -1300,24 +1311,24 @@
         </is>
       </c>
       <c r="F21" s="4" t="n"/>
-      <c r="G21" s="5">
-        <f>IF(P21="","",DATEDIF(P21,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P21,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H21" s="5">
-        <f>IF(I21="","",DATEDIF(I21,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="4" t="n"/>
+        <f>IF(Q21="","",DATEDIF(Q21,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q21,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I21" s="5">
+        <f>IF(J21="","",DATEDIF(J21,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J21" s="6" t="n"/>
       <c r="K21" s="4" t="n"/>
       <c r="L21" s="4" t="n"/>
       <c r="M21" s="4" t="n"/>
       <c r="N21" s="4" t="n"/>
       <c r="O21" s="4" t="n"/>
-      <c r="P21" s="6" t="n"/>
-      <c r="Q21" s="3" t="n"/>
-      <c r="R21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
+      <c r="Q21" s="6" t="n"/>
+      <c r="R21" s="3" t="n"/>
+      <c r="S21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n"/>
@@ -1330,24 +1341,24 @@
         </is>
       </c>
       <c r="F22" s="4" t="n"/>
-      <c r="G22" s="5">
-        <f>IF(P22="","",DATEDIF(P22,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P22,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H22" s="5">
-        <f>IF(I22="","",DATEDIF(I22,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="4" t="n"/>
+        <f>IF(Q22="","",DATEDIF(Q22,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q22,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I22" s="5">
+        <f>IF(J22="","",DATEDIF(J22,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J22" s="6" t="n"/>
       <c r="K22" s="4" t="n"/>
       <c r="L22" s="4" t="n"/>
       <c r="M22" s="4" t="n"/>
       <c r="N22" s="4" t="n"/>
       <c r="O22" s="4" t="n"/>
-      <c r="P22" s="6" t="n"/>
-      <c r="Q22" s="3" t="n"/>
-      <c r="R22" s="4" t="n"/>
+      <c r="P22" s="4" t="n"/>
+      <c r="Q22" s="6" t="n"/>
+      <c r="R22" s="3" t="n"/>
+      <c r="S22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
@@ -1360,24 +1371,24 @@
         </is>
       </c>
       <c r="F23" s="4" t="n"/>
-      <c r="G23" s="5">
-        <f>IF(P23="","",DATEDIF(P23,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P23,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H23" s="5">
-        <f>IF(I23="","",DATEDIF(I23,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="4" t="n"/>
+        <f>IF(Q23="","",DATEDIF(Q23,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q23,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I23" s="5">
+        <f>IF(J23="","",DATEDIF(J23,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J23" s="6" t="n"/>
       <c r="K23" s="4" t="n"/>
       <c r="L23" s="4" t="n"/>
       <c r="M23" s="4" t="n"/>
       <c r="N23" s="4" t="n"/>
       <c r="O23" s="4" t="n"/>
-      <c r="P23" s="6" t="n"/>
-      <c r="Q23" s="3" t="n"/>
-      <c r="R23" s="4" t="n"/>
+      <c r="P23" s="4" t="n"/>
+      <c r="Q23" s="6" t="n"/>
+      <c r="R23" s="3" t="n"/>
+      <c r="S23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n"/>
@@ -1390,24 +1401,24 @@
         </is>
       </c>
       <c r="F24" s="4" t="n"/>
-      <c r="G24" s="5">
-        <f>IF(P24="","",DATEDIF(P24,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P24,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H24" s="5">
-        <f>IF(I24="","",DATEDIF(I24,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I24" s="6" t="n"/>
-      <c r="J24" s="4" t="n"/>
+        <f>IF(Q24="","",DATEDIF(Q24,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q24,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I24" s="5">
+        <f>IF(J24="","",DATEDIF(J24,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J24" s="6" t="n"/>
       <c r="K24" s="4" t="n"/>
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
       <c r="O24" s="4" t="n"/>
-      <c r="P24" s="6" t="n"/>
-      <c r="Q24" s="3" t="n"/>
-      <c r="R24" s="4" t="n"/>
+      <c r="P24" s="4" t="n"/>
+      <c r="Q24" s="6" t="n"/>
+      <c r="R24" s="3" t="n"/>
+      <c r="S24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n"/>
@@ -1420,24 +1431,24 @@
         </is>
       </c>
       <c r="F25" s="4" t="n"/>
-      <c r="G25" s="5">
-        <f>IF(P25="","",DATEDIF(P25,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P25,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H25" s="5">
-        <f>IF(I25="","",DATEDIF(I25,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I25" s="6" t="n"/>
-      <c r="J25" s="4" t="n"/>
+        <f>IF(Q25="","",DATEDIF(Q25,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q25,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I25" s="5">
+        <f>IF(J25="","",DATEDIF(J25,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J25" s="6" t="n"/>
       <c r="K25" s="4" t="n"/>
       <c r="L25" s="4" t="n"/>
       <c r="M25" s="4" t="n"/>
       <c r="N25" s="4" t="n"/>
       <c r="O25" s="4" t="n"/>
-      <c r="P25" s="6" t="n"/>
-      <c r="Q25" s="3" t="n"/>
-      <c r="R25" s="4" t="n"/>
+      <c r="P25" s="4" t="n"/>
+      <c r="Q25" s="6" t="n"/>
+      <c r="R25" s="3" t="n"/>
+      <c r="S25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
@@ -1450,24 +1461,24 @@
         </is>
       </c>
       <c r="F26" s="4" t="n"/>
-      <c r="G26" s="5">
-        <f>IF(P26="","",DATEDIF(P26,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P26,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H26" s="5">
-        <f>IF(I26="","",DATEDIF(I26,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I26" s="6" t="n"/>
-      <c r="J26" s="4" t="n"/>
+        <f>IF(Q26="","",DATEDIF(Q26,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q26,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I26" s="5">
+        <f>IF(J26="","",DATEDIF(J26,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J26" s="6" t="n"/>
       <c r="K26" s="4" t="n"/>
       <c r="L26" s="4" t="n"/>
       <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="n"/>
       <c r="O26" s="4" t="n"/>
-      <c r="P26" s="6" t="n"/>
-      <c r="Q26" s="3" t="n"/>
-      <c r="R26" s="4" t="n"/>
+      <c r="P26" s="4" t="n"/>
+      <c r="Q26" s="6" t="n"/>
+      <c r="R26" s="3" t="n"/>
+      <c r="S26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
@@ -1480,24 +1491,24 @@
         </is>
       </c>
       <c r="F27" s="4" t="n"/>
-      <c r="G27" s="5">
-        <f>IF(P27="","",DATEDIF(P27,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P27,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H27" s="5">
-        <f>IF(I27="","",DATEDIF(I27,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="4" t="n"/>
+        <f>IF(Q27="","",DATEDIF(Q27,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q27,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I27" s="5">
+        <f>IF(J27="","",DATEDIF(J27,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J27" s="6" t="n"/>
       <c r="K27" s="4" t="n"/>
       <c r="L27" s="4" t="n"/>
       <c r="M27" s="4" t="n"/>
       <c r="N27" s="4" t="n"/>
       <c r="O27" s="4" t="n"/>
-      <c r="P27" s="6" t="n"/>
-      <c r="Q27" s="3" t="n"/>
-      <c r="R27" s="4" t="n"/>
+      <c r="P27" s="4" t="n"/>
+      <c r="Q27" s="6" t="n"/>
+      <c r="R27" s="3" t="n"/>
+      <c r="S27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n"/>
@@ -1510,24 +1521,24 @@
         </is>
       </c>
       <c r="F28" s="4" t="n"/>
-      <c r="G28" s="5">
-        <f>IF(P28="","",DATEDIF(P28,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P28,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H28" s="5">
-        <f>IF(I28="","",DATEDIF(I28,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I28" s="6" t="n"/>
-      <c r="J28" s="4" t="n"/>
+        <f>IF(Q28="","",DATEDIF(Q28,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q28,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I28" s="5">
+        <f>IF(J28="","",DATEDIF(J28,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J28" s="6" t="n"/>
       <c r="K28" s="4" t="n"/>
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
       <c r="O28" s="4" t="n"/>
-      <c r="P28" s="6" t="n"/>
-      <c r="Q28" s="3" t="n"/>
-      <c r="R28" s="4" t="n"/>
+      <c r="P28" s="4" t="n"/>
+      <c r="Q28" s="6" t="n"/>
+      <c r="R28" s="3" t="n"/>
+      <c r="S28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n"/>
@@ -1540,24 +1551,24 @@
         </is>
       </c>
       <c r="F29" s="4" t="n"/>
-      <c r="G29" s="5">
-        <f>IF(P29="","",DATEDIF(P29,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P29,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H29" s="5">
-        <f>IF(I29="","",DATEDIF(I29,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="4" t="n"/>
+        <f>IF(Q29="","",DATEDIF(Q29,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q29,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I29" s="5">
+        <f>IF(J29="","",DATEDIF(J29,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J29" s="6" t="n"/>
       <c r="K29" s="4" t="n"/>
       <c r="L29" s="4" t="n"/>
       <c r="M29" s="4" t="n"/>
       <c r="N29" s="4" t="n"/>
       <c r="O29" s="4" t="n"/>
-      <c r="P29" s="6" t="n"/>
-      <c r="Q29" s="3" t="n"/>
-      <c r="R29" s="4" t="n"/>
+      <c r="P29" s="4" t="n"/>
+      <c r="Q29" s="6" t="n"/>
+      <c r="R29" s="3" t="n"/>
+      <c r="S29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n"/>
@@ -1570,24 +1581,24 @@
         </is>
       </c>
       <c r="F30" s="4" t="n"/>
-      <c r="G30" s="5">
-        <f>IF(P30="","",DATEDIF(P30,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P30,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H30" s="5">
-        <f>IF(I30="","",DATEDIF(I30,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I30" s="6" t="n"/>
-      <c r="J30" s="4" t="n"/>
+        <f>IF(Q30="","",DATEDIF(Q30,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q30,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I30" s="5">
+        <f>IF(J30="","",DATEDIF(J30,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J30" s="6" t="n"/>
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
       <c r="O30" s="4" t="n"/>
-      <c r="P30" s="6" t="n"/>
-      <c r="Q30" s="3" t="n"/>
-      <c r="R30" s="4" t="n"/>
+      <c r="P30" s="4" t="n"/>
+      <c r="Q30" s="6" t="n"/>
+      <c r="R30" s="3" t="n"/>
+      <c r="S30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n"/>
@@ -1600,24 +1611,24 @@
         </is>
       </c>
       <c r="F31" s="4" t="n"/>
-      <c r="G31" s="5">
-        <f>IF(P31="","",DATEDIF(P31,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P31,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H31" s="5">
-        <f>IF(I31="","",DATEDIF(I31,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I31" s="6" t="n"/>
-      <c r="J31" s="4" t="n"/>
+        <f>IF(Q31="","",DATEDIF(Q31,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q31,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I31" s="5">
+        <f>IF(J31="","",DATEDIF(J31,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J31" s="6" t="n"/>
       <c r="K31" s="4" t="n"/>
       <c r="L31" s="4" t="n"/>
       <c r="M31" s="4" t="n"/>
       <c r="N31" s="4" t="n"/>
       <c r="O31" s="4" t="n"/>
-      <c r="P31" s="6" t="n"/>
-      <c r="Q31" s="3" t="n"/>
-      <c r="R31" s="4" t="n"/>
+      <c r="P31" s="4" t="n"/>
+      <c r="Q31" s="6" t="n"/>
+      <c r="R31" s="3" t="n"/>
+      <c r="S31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n"/>
@@ -1630,24 +1641,24 @@
         </is>
       </c>
       <c r="F32" s="4" t="n"/>
-      <c r="G32" s="5">
-        <f>IF(P32="","",DATEDIF(P32,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P32,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H32" s="5">
-        <f>IF(I32="","",DATEDIF(I32,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I32" s="6" t="n"/>
-      <c r="J32" s="4" t="n"/>
+        <f>IF(Q32="","",DATEDIF(Q32,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q32,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I32" s="5">
+        <f>IF(J32="","",DATEDIF(J32,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J32" s="6" t="n"/>
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
       <c r="M32" s="4" t="n"/>
       <c r="N32" s="4" t="n"/>
       <c r="O32" s="4" t="n"/>
-      <c r="P32" s="6" t="n"/>
-      <c r="Q32" s="3" t="n"/>
-      <c r="R32" s="4" t="n"/>
+      <c r="P32" s="4" t="n"/>
+      <c r="Q32" s="6" t="n"/>
+      <c r="R32" s="3" t="n"/>
+      <c r="S32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n"/>
@@ -1660,24 +1671,24 @@
         </is>
       </c>
       <c r="F33" s="4" t="n"/>
-      <c r="G33" s="5">
-        <f>IF(P33="","",DATEDIF(P33,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P33,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H33" s="5">
-        <f>IF(I33="","",DATEDIF(I33,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I33" s="6" t="n"/>
-      <c r="J33" s="4" t="n"/>
+        <f>IF(Q33="","",DATEDIF(Q33,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q33,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I33" s="5">
+        <f>IF(J33="","",DATEDIF(J33,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J33" s="6" t="n"/>
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="n"/>
       <c r="M33" s="4" t="n"/>
       <c r="N33" s="4" t="n"/>
       <c r="O33" s="4" t="n"/>
-      <c r="P33" s="6" t="n"/>
-      <c r="Q33" s="3" t="n"/>
-      <c r="R33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
+      <c r="Q33" s="6" t="n"/>
+      <c r="R33" s="3" t="n"/>
+      <c r="S33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n"/>
@@ -1690,24 +1701,24 @@
         </is>
       </c>
       <c r="F34" s="4" t="n"/>
-      <c r="G34" s="5">
-        <f>IF(P34="","",DATEDIF(P34,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P34,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H34" s="5">
-        <f>IF(I34="","",DATEDIF(I34,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I34" s="6" t="n"/>
-      <c r="J34" s="4" t="n"/>
+        <f>IF(Q34="","",DATEDIF(Q34,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q34,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I34" s="5">
+        <f>IF(J34="","",DATEDIF(J34,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J34" s="6" t="n"/>
       <c r="K34" s="4" t="n"/>
       <c r="L34" s="4" t="n"/>
       <c r="M34" s="4" t="n"/>
       <c r="N34" s="4" t="n"/>
       <c r="O34" s="4" t="n"/>
-      <c r="P34" s="6" t="n"/>
-      <c r="Q34" s="3" t="n"/>
-      <c r="R34" s="4" t="n"/>
+      <c r="P34" s="4" t="n"/>
+      <c r="Q34" s="6" t="n"/>
+      <c r="R34" s="3" t="n"/>
+      <c r="S34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n"/>
@@ -1720,24 +1731,24 @@
         </is>
       </c>
       <c r="F35" s="4" t="n"/>
-      <c r="G35" s="5">
-        <f>IF(P35="","",DATEDIF(P35,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P35,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H35" s="5">
-        <f>IF(I35="","",DATEDIF(I35,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I35" s="6" t="n"/>
-      <c r="J35" s="4" t="n"/>
+        <f>IF(Q35="","",DATEDIF(Q35,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q35,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I35" s="5">
+        <f>IF(J35="","",DATEDIF(J35,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J35" s="6" t="n"/>
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n"/>
       <c r="M35" s="4" t="n"/>
       <c r="N35" s="4" t="n"/>
       <c r="O35" s="4" t="n"/>
-      <c r="P35" s="6" t="n"/>
-      <c r="Q35" s="3" t="n"/>
-      <c r="R35" s="4" t="n"/>
+      <c r="P35" s="4" t="n"/>
+      <c r="Q35" s="6" t="n"/>
+      <c r="R35" s="3" t="n"/>
+      <c r="S35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n"/>
@@ -1750,24 +1761,24 @@
         </is>
       </c>
       <c r="F36" s="4" t="n"/>
-      <c r="G36" s="5">
-        <f>IF(P36="","",DATEDIF(P36,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P36,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H36" s="5">
-        <f>IF(I36="","",DATEDIF(I36,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I36" s="6" t="n"/>
-      <c r="J36" s="4" t="n"/>
+        <f>IF(Q36="","",DATEDIF(Q36,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q36,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I36" s="5">
+        <f>IF(J36="","",DATEDIF(J36,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J36" s="6" t="n"/>
       <c r="K36" s="4" t="n"/>
       <c r="L36" s="4" t="n"/>
       <c r="M36" s="4" t="n"/>
       <c r="N36" s="4" t="n"/>
       <c r="O36" s="4" t="n"/>
-      <c r="P36" s="6" t="n"/>
-      <c r="Q36" s="3" t="n"/>
-      <c r="R36" s="4" t="n"/>
+      <c r="P36" s="4" t="n"/>
+      <c r="Q36" s="6" t="n"/>
+      <c r="R36" s="3" t="n"/>
+      <c r="S36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n"/>
@@ -1780,24 +1791,24 @@
         </is>
       </c>
       <c r="F37" s="4" t="n"/>
-      <c r="G37" s="5">
-        <f>IF(P37="","",DATEDIF(P37,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P37,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H37" s="5">
-        <f>IF(I37="","",DATEDIF(I37,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I37" s="6" t="n"/>
-      <c r="J37" s="4" t="n"/>
+        <f>IF(Q37="","",DATEDIF(Q37,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q37,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I37" s="5">
+        <f>IF(J37="","",DATEDIF(J37,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J37" s="6" t="n"/>
       <c r="K37" s="4" t="n"/>
       <c r="L37" s="4" t="n"/>
       <c r="M37" s="4" t="n"/>
       <c r="N37" s="4" t="n"/>
       <c r="O37" s="4" t="n"/>
-      <c r="P37" s="6" t="n"/>
-      <c r="Q37" s="3" t="n"/>
-      <c r="R37" s="4" t="n"/>
+      <c r="P37" s="4" t="n"/>
+      <c r="Q37" s="6" t="n"/>
+      <c r="R37" s="3" t="n"/>
+      <c r="S37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n"/>
@@ -1810,24 +1821,24 @@
         </is>
       </c>
       <c r="F38" s="4" t="n"/>
-      <c r="G38" s="5">
-        <f>IF(P38="","",DATEDIF(P38,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P38,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H38" s="5">
-        <f>IF(I38="","",DATEDIF(I38,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I38" s="6" t="n"/>
-      <c r="J38" s="4" t="n"/>
+        <f>IF(Q38="","",DATEDIF(Q38,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q38,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I38" s="5">
+        <f>IF(J38="","",DATEDIF(J38,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J38" s="6" t="n"/>
       <c r="K38" s="4" t="n"/>
       <c r="L38" s="4" t="n"/>
       <c r="M38" s="4" t="n"/>
       <c r="N38" s="4" t="n"/>
       <c r="O38" s="4" t="n"/>
-      <c r="P38" s="6" t="n"/>
-      <c r="Q38" s="3" t="n"/>
-      <c r="R38" s="4" t="n"/>
+      <c r="P38" s="4" t="n"/>
+      <c r="Q38" s="6" t="n"/>
+      <c r="R38" s="3" t="n"/>
+      <c r="S38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n"/>
@@ -1840,24 +1851,24 @@
         </is>
       </c>
       <c r="F39" s="4" t="n"/>
-      <c r="G39" s="5">
-        <f>IF(P39="","",DATEDIF(P39,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P39,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H39" s="5">
-        <f>IF(I39="","",DATEDIF(I39,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I39" s="6" t="n"/>
-      <c r="J39" s="4" t="n"/>
+        <f>IF(Q39="","",DATEDIF(Q39,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q39,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I39" s="5">
+        <f>IF(J39="","",DATEDIF(J39,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J39" s="6" t="n"/>
       <c r="K39" s="4" t="n"/>
       <c r="L39" s="4" t="n"/>
       <c r="M39" s="4" t="n"/>
       <c r="N39" s="4" t="n"/>
       <c r="O39" s="4" t="n"/>
-      <c r="P39" s="6" t="n"/>
-      <c r="Q39" s="3" t="n"/>
-      <c r="R39" s="4" t="n"/>
+      <c r="P39" s="4" t="n"/>
+      <c r="Q39" s="6" t="n"/>
+      <c r="R39" s="3" t="n"/>
+      <c r="S39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n"/>
@@ -1870,24 +1881,24 @@
         </is>
       </c>
       <c r="F40" s="4" t="n"/>
-      <c r="G40" s="5">
-        <f>IF(P40="","",DATEDIF(P40,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P40,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H40" s="5">
-        <f>IF(I40="","",DATEDIF(I40,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I40" s="6" t="n"/>
-      <c r="J40" s="4" t="n"/>
+        <f>IF(Q40="","",DATEDIF(Q40,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q40,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I40" s="5">
+        <f>IF(J40="","",DATEDIF(J40,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J40" s="6" t="n"/>
       <c r="K40" s="4" t="n"/>
       <c r="L40" s="4" t="n"/>
       <c r="M40" s="4" t="n"/>
       <c r="N40" s="4" t="n"/>
       <c r="O40" s="4" t="n"/>
-      <c r="P40" s="6" t="n"/>
-      <c r="Q40" s="3" t="n"/>
-      <c r="R40" s="4" t="n"/>
+      <c r="P40" s="4" t="n"/>
+      <c r="Q40" s="6" t="n"/>
+      <c r="R40" s="3" t="n"/>
+      <c r="S40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n"/>
@@ -1900,24 +1911,24 @@
         </is>
       </c>
       <c r="F41" s="4" t="n"/>
-      <c r="G41" s="5">
-        <f>IF(P41="","",DATEDIF(P41,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P41,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H41" s="5">
-        <f>IF(I41="","",DATEDIF(I41,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I41" s="6" t="n"/>
-      <c r="J41" s="4" t="n"/>
+        <f>IF(Q41="","",DATEDIF(Q41,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q41,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I41" s="5">
+        <f>IF(J41="","",DATEDIF(J41,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J41" s="6" t="n"/>
       <c r="K41" s="4" t="n"/>
       <c r="L41" s="4" t="n"/>
       <c r="M41" s="4" t="n"/>
       <c r="N41" s="4" t="n"/>
       <c r="O41" s="4" t="n"/>
-      <c r="P41" s="6" t="n"/>
-      <c r="Q41" s="3" t="n"/>
-      <c r="R41" s="4" t="n"/>
+      <c r="P41" s="4" t="n"/>
+      <c r="Q41" s="6" t="n"/>
+      <c r="R41" s="3" t="n"/>
+      <c r="S41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n"/>
@@ -1930,24 +1941,24 @@
         </is>
       </c>
       <c r="F42" s="4" t="n"/>
-      <c r="G42" s="5">
-        <f>IF(P42="","",DATEDIF(P42,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P42,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H42" s="5">
-        <f>IF(I42="","",DATEDIF(I42,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I42" s="6" t="n"/>
-      <c r="J42" s="4" t="n"/>
+        <f>IF(Q42="","",DATEDIF(Q42,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q42,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I42" s="5">
+        <f>IF(J42="","",DATEDIF(J42,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J42" s="6" t="n"/>
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n"/>
       <c r="M42" s="4" t="n"/>
       <c r="N42" s="4" t="n"/>
       <c r="O42" s="4" t="n"/>
-      <c r="P42" s="6" t="n"/>
-      <c r="Q42" s="3" t="n"/>
-      <c r="R42" s="4" t="n"/>
+      <c r="P42" s="4" t="n"/>
+      <c r="Q42" s="6" t="n"/>
+      <c r="R42" s="3" t="n"/>
+      <c r="S42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n"/>
@@ -1960,24 +1971,24 @@
         </is>
       </c>
       <c r="F43" s="4" t="n"/>
-      <c r="G43" s="5">
-        <f>IF(P43="","",DATEDIF(P43,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P43,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H43" s="5">
-        <f>IF(I43="","",DATEDIF(I43,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I43" s="6" t="n"/>
-      <c r="J43" s="4" t="n"/>
+        <f>IF(Q43="","",DATEDIF(Q43,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q43,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I43" s="5">
+        <f>IF(J43="","",DATEDIF(J43,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J43" s="6" t="n"/>
       <c r="K43" s="4" t="n"/>
       <c r="L43" s="4" t="n"/>
       <c r="M43" s="4" t="n"/>
       <c r="N43" s="4" t="n"/>
       <c r="O43" s="4" t="n"/>
-      <c r="P43" s="6" t="n"/>
-      <c r="Q43" s="3" t="n"/>
-      <c r="R43" s="4" t="n"/>
+      <c r="P43" s="4" t="n"/>
+      <c r="Q43" s="6" t="n"/>
+      <c r="R43" s="3" t="n"/>
+      <c r="S43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n"/>
@@ -1990,24 +2001,24 @@
         </is>
       </c>
       <c r="F44" s="4" t="n"/>
-      <c r="G44" s="5">
-        <f>IF(P44="","",DATEDIF(P44,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P44,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H44" s="5">
-        <f>IF(I44="","",DATEDIF(I44,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I44" s="6" t="n"/>
-      <c r="J44" s="4" t="n"/>
+        <f>IF(Q44="","",DATEDIF(Q44,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q44,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I44" s="5">
+        <f>IF(J44="","",DATEDIF(J44,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J44" s="6" t="n"/>
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n"/>
       <c r="M44" s="4" t="n"/>
       <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="n"/>
-      <c r="P44" s="6" t="n"/>
-      <c r="Q44" s="3" t="n"/>
-      <c r="R44" s="4" t="n"/>
+      <c r="P44" s="4" t="n"/>
+      <c r="Q44" s="6" t="n"/>
+      <c r="R44" s="3" t="n"/>
+      <c r="S44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n"/>
@@ -2020,24 +2031,24 @@
         </is>
       </c>
       <c r="F45" s="4" t="n"/>
-      <c r="G45" s="5">
-        <f>IF(P45="","",DATEDIF(P45,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P45,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H45" s="5">
-        <f>IF(I45="","",DATEDIF(I45,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I45" s="6" t="n"/>
-      <c r="J45" s="4" t="n"/>
+        <f>IF(Q45="","",DATEDIF(Q45,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q45,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I45" s="5">
+        <f>IF(J45="","",DATEDIF(J45,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J45" s="6" t="n"/>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
       <c r="M45" s="4" t="n"/>
       <c r="N45" s="4" t="n"/>
       <c r="O45" s="4" t="n"/>
-      <c r="P45" s="6" t="n"/>
-      <c r="Q45" s="3" t="n"/>
-      <c r="R45" s="4" t="n"/>
+      <c r="P45" s="4" t="n"/>
+      <c r="Q45" s="6" t="n"/>
+      <c r="R45" s="3" t="n"/>
+      <c r="S45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n"/>
@@ -2050,24 +2061,24 @@
         </is>
       </c>
       <c r="F46" s="4" t="n"/>
-      <c r="G46" s="5">
-        <f>IF(P46="","",DATEDIF(P46,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P46,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H46" s="5">
-        <f>IF(I46="","",DATEDIF(I46,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I46" s="6" t="n"/>
-      <c r="J46" s="4" t="n"/>
+        <f>IF(Q46="","",DATEDIF(Q46,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q46,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I46" s="5">
+        <f>IF(J46="","",DATEDIF(J46,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J46" s="6" t="n"/>
       <c r="K46" s="4" t="n"/>
       <c r="L46" s="4" t="n"/>
       <c r="M46" s="4" t="n"/>
       <c r="N46" s="4" t="n"/>
       <c r="O46" s="4" t="n"/>
-      <c r="P46" s="6" t="n"/>
-      <c r="Q46" s="3" t="n"/>
-      <c r="R46" s="4" t="n"/>
+      <c r="P46" s="4" t="n"/>
+      <c r="Q46" s="6" t="n"/>
+      <c r="R46" s="3" t="n"/>
+      <c r="S46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n"/>
@@ -2080,24 +2091,24 @@
         </is>
       </c>
       <c r="F47" s="4" t="n"/>
-      <c r="G47" s="5">
-        <f>IF(P47="","",DATEDIF(P47,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P47,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H47" s="5">
-        <f>IF(I47="","",DATEDIF(I47,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I47" s="6" t="n"/>
-      <c r="J47" s="4" t="n"/>
+        <f>IF(Q47="","",DATEDIF(Q47,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q47,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I47" s="5">
+        <f>IF(J47="","",DATEDIF(J47,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J47" s="6" t="n"/>
       <c r="K47" s="4" t="n"/>
       <c r="L47" s="4" t="n"/>
       <c r="M47" s="4" t="n"/>
       <c r="N47" s="4" t="n"/>
       <c r="O47" s="4" t="n"/>
-      <c r="P47" s="6" t="n"/>
-      <c r="Q47" s="3" t="n"/>
-      <c r="R47" s="4" t="n"/>
+      <c r="P47" s="4" t="n"/>
+      <c r="Q47" s="6" t="n"/>
+      <c r="R47" s="3" t="n"/>
+      <c r="S47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n"/>
@@ -2110,24 +2121,24 @@
         </is>
       </c>
       <c r="F48" s="4" t="n"/>
-      <c r="G48" s="5">
-        <f>IF(P48="","",DATEDIF(P48,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P48,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H48" s="5">
-        <f>IF(I48="","",DATEDIF(I48,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I48" s="6" t="n"/>
-      <c r="J48" s="4" t="n"/>
+        <f>IF(Q48="","",DATEDIF(Q48,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q48,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I48" s="5">
+        <f>IF(J48="","",DATEDIF(J48,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J48" s="6" t="n"/>
       <c r="K48" s="4" t="n"/>
       <c r="L48" s="4" t="n"/>
       <c r="M48" s="4" t="n"/>
       <c r="N48" s="4" t="n"/>
       <c r="O48" s="4" t="n"/>
-      <c r="P48" s="6" t="n"/>
-      <c r="Q48" s="3" t="n"/>
-      <c r="R48" s="4" t="n"/>
+      <c r="P48" s="4" t="n"/>
+      <c r="Q48" s="6" t="n"/>
+      <c r="R48" s="3" t="n"/>
+      <c r="S48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n"/>
@@ -2140,24 +2151,24 @@
         </is>
       </c>
       <c r="F49" s="4" t="n"/>
-      <c r="G49" s="5">
-        <f>IF(P49="","",DATEDIF(P49,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P49,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H49" s="5">
-        <f>IF(I49="","",DATEDIF(I49,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I49" s="6" t="n"/>
-      <c r="J49" s="4" t="n"/>
+        <f>IF(Q49="","",DATEDIF(Q49,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q49,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I49" s="5">
+        <f>IF(J49="","",DATEDIF(J49,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J49" s="6" t="n"/>
       <c r="K49" s="4" t="n"/>
       <c r="L49" s="4" t="n"/>
       <c r="M49" s="4" t="n"/>
       <c r="N49" s="4" t="n"/>
       <c r="O49" s="4" t="n"/>
-      <c r="P49" s="6" t="n"/>
-      <c r="Q49" s="3" t="n"/>
-      <c r="R49" s="4" t="n"/>
+      <c r="P49" s="4" t="n"/>
+      <c r="Q49" s="6" t="n"/>
+      <c r="R49" s="3" t="n"/>
+      <c r="S49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n"/>
@@ -2170,24 +2181,24 @@
         </is>
       </c>
       <c r="F50" s="4" t="n"/>
-      <c r="G50" s="5">
-        <f>IF(P50="","",DATEDIF(P50,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P50,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H50" s="5">
-        <f>IF(I50="","",DATEDIF(I50,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I50" s="6" t="n"/>
-      <c r="J50" s="4" t="n"/>
+        <f>IF(Q50="","",DATEDIF(Q50,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q50,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I50" s="5">
+        <f>IF(J50="","",DATEDIF(J50,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J50" s="6" t="n"/>
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
       <c r="M50" s="4" t="n"/>
       <c r="N50" s="4" t="n"/>
       <c r="O50" s="4" t="n"/>
-      <c r="P50" s="6" t="n"/>
-      <c r="Q50" s="3" t="n"/>
-      <c r="R50" s="4" t="n"/>
+      <c r="P50" s="4" t="n"/>
+      <c r="Q50" s="6" t="n"/>
+      <c r="R50" s="3" t="n"/>
+      <c r="S50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n"/>
@@ -2200,24 +2211,24 @@
         </is>
       </c>
       <c r="F51" s="4" t="n"/>
-      <c r="G51" s="5">
-        <f>IF(P51="","",DATEDIF(P51,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P51,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H51" s="5">
-        <f>IF(I51="","",DATEDIF(I51,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I51" s="6" t="n"/>
-      <c r="J51" s="4" t="n"/>
+        <f>IF(Q51="","",DATEDIF(Q51,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q51,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I51" s="5">
+        <f>IF(J51="","",DATEDIF(J51,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J51" s="6" t="n"/>
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="4" t="n"/>
       <c r="M51" s="4" t="n"/>
       <c r="N51" s="4" t="n"/>
       <c r="O51" s="4" t="n"/>
-      <c r="P51" s="6" t="n"/>
-      <c r="Q51" s="3" t="n"/>
-      <c r="R51" s="4" t="n"/>
+      <c r="P51" s="4" t="n"/>
+      <c r="Q51" s="6" t="n"/>
+      <c r="R51" s="3" t="n"/>
+      <c r="S51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n"/>
@@ -2230,24 +2241,24 @@
         </is>
       </c>
       <c r="F52" s="4" t="n"/>
-      <c r="G52" s="5">
-        <f>IF(P52="","",DATEDIF(P52,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P52,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H52" s="5">
-        <f>IF(I52="","",DATEDIF(I52,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I52" s="6" t="n"/>
-      <c r="J52" s="4" t="n"/>
+        <f>IF(Q52="","",DATEDIF(Q52,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q52,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I52" s="5">
+        <f>IF(J52="","",DATEDIF(J52,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J52" s="6" t="n"/>
       <c r="K52" s="4" t="n"/>
       <c r="L52" s="4" t="n"/>
       <c r="M52" s="4" t="n"/>
       <c r="N52" s="4" t="n"/>
       <c r="O52" s="4" t="n"/>
-      <c r="P52" s="6" t="n"/>
-      <c r="Q52" s="3" t="n"/>
-      <c r="R52" s="4" t="n"/>
+      <c r="P52" s="4" t="n"/>
+      <c r="Q52" s="6" t="n"/>
+      <c r="R52" s="3" t="n"/>
+      <c r="S52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n"/>
@@ -2260,24 +2271,24 @@
         </is>
       </c>
       <c r="F53" s="4" t="n"/>
-      <c r="G53" s="5">
-        <f>IF(P53="","",DATEDIF(P53,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P53,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H53" s="5">
-        <f>IF(I53="","",DATEDIF(I53,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I53" s="6" t="n"/>
-      <c r="J53" s="4" t="n"/>
+        <f>IF(Q53="","",DATEDIF(Q53,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q53,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I53" s="5">
+        <f>IF(J53="","",DATEDIF(J53,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J53" s="6" t="n"/>
       <c r="K53" s="4" t="n"/>
       <c r="L53" s="4" t="n"/>
       <c r="M53" s="4" t="n"/>
       <c r="N53" s="4" t="n"/>
       <c r="O53" s="4" t="n"/>
-      <c r="P53" s="6" t="n"/>
-      <c r="Q53" s="3" t="n"/>
-      <c r="R53" s="4" t="n"/>
+      <c r="P53" s="4" t="n"/>
+      <c r="Q53" s="6" t="n"/>
+      <c r="R53" s="3" t="n"/>
+      <c r="S53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n"/>
@@ -2290,24 +2301,24 @@
         </is>
       </c>
       <c r="F54" s="4" t="n"/>
-      <c r="G54" s="5">
-        <f>IF(P54="","",DATEDIF(P54,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P54,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H54" s="5">
-        <f>IF(I54="","",DATEDIF(I54,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I54" s="6" t="n"/>
-      <c r="J54" s="4" t="n"/>
+        <f>IF(Q54="","",DATEDIF(Q54,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q54,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I54" s="5">
+        <f>IF(J54="","",DATEDIF(J54,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J54" s="6" t="n"/>
       <c r="K54" s="4" t="n"/>
       <c r="L54" s="4" t="n"/>
       <c r="M54" s="4" t="n"/>
       <c r="N54" s="4" t="n"/>
       <c r="O54" s="4" t="n"/>
-      <c r="P54" s="6" t="n"/>
-      <c r="Q54" s="3" t="n"/>
-      <c r="R54" s="4" t="n"/>
+      <c r="P54" s="4" t="n"/>
+      <c r="Q54" s="6" t="n"/>
+      <c r="R54" s="3" t="n"/>
+      <c r="S54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n"/>
@@ -2320,24 +2331,24 @@
         </is>
       </c>
       <c r="F55" s="4" t="n"/>
-      <c r="G55" s="5">
-        <f>IF(P55="","",DATEDIF(P55,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P55,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H55" s="5">
-        <f>IF(I55="","",DATEDIF(I55,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I55" s="6" t="n"/>
-      <c r="J55" s="4" t="n"/>
+        <f>IF(Q55="","",DATEDIF(Q55,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q55,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I55" s="5">
+        <f>IF(J55="","",DATEDIF(J55,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J55" s="6" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
       <c r="M55" s="4" t="n"/>
       <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="n"/>
-      <c r="P55" s="6" t="n"/>
-      <c r="Q55" s="3" t="n"/>
-      <c r="R55" s="4" t="n"/>
+      <c r="P55" s="4" t="n"/>
+      <c r="Q55" s="6" t="n"/>
+      <c r="R55" s="3" t="n"/>
+      <c r="S55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n"/>
@@ -2350,24 +2361,24 @@
         </is>
       </c>
       <c r="F56" s="4" t="n"/>
-      <c r="G56" s="5">
-        <f>IF(P56="","",DATEDIF(P56,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P56,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H56" s="5">
-        <f>IF(I56="","",DATEDIF(I56,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I56" s="6" t="n"/>
-      <c r="J56" s="4" t="n"/>
+        <f>IF(Q56="","",DATEDIF(Q56,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q56,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I56" s="5">
+        <f>IF(J56="","",DATEDIF(J56,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J56" s="6" t="n"/>
       <c r="K56" s="4" t="n"/>
       <c r="L56" s="4" t="n"/>
       <c r="M56" s="4" t="n"/>
       <c r="N56" s="4" t="n"/>
       <c r="O56" s="4" t="n"/>
-      <c r="P56" s="6" t="n"/>
-      <c r="Q56" s="3" t="n"/>
-      <c r="R56" s="4" t="n"/>
+      <c r="P56" s="4" t="n"/>
+      <c r="Q56" s="6" t="n"/>
+      <c r="R56" s="3" t="n"/>
+      <c r="S56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n"/>
@@ -2380,24 +2391,24 @@
         </is>
       </c>
       <c r="F57" s="4" t="n"/>
-      <c r="G57" s="5">
-        <f>IF(P57="","",DATEDIF(P57,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P57,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H57" s="5">
-        <f>IF(I57="","",DATEDIF(I57,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I57" s="6" t="n"/>
-      <c r="J57" s="4" t="n"/>
+        <f>IF(Q57="","",DATEDIF(Q57,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q57,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I57" s="5">
+        <f>IF(J57="","",DATEDIF(J57,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J57" s="6" t="n"/>
       <c r="K57" s="4" t="n"/>
       <c r="L57" s="4" t="n"/>
       <c r="M57" s="4" t="n"/>
       <c r="N57" s="4" t="n"/>
       <c r="O57" s="4" t="n"/>
-      <c r="P57" s="6" t="n"/>
-      <c r="Q57" s="3" t="n"/>
-      <c r="R57" s="4" t="n"/>
+      <c r="P57" s="4" t="n"/>
+      <c r="Q57" s="6" t="n"/>
+      <c r="R57" s="3" t="n"/>
+      <c r="S57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n"/>
@@ -2410,24 +2421,24 @@
         </is>
       </c>
       <c r="F58" s="4" t="n"/>
-      <c r="G58" s="5">
-        <f>IF(P58="","",DATEDIF(P58,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P58,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H58" s="5">
-        <f>IF(I58="","",DATEDIF(I58,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I58" s="6" t="n"/>
-      <c r="J58" s="4" t="n"/>
+        <f>IF(Q58="","",DATEDIF(Q58,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q58,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I58" s="5">
+        <f>IF(J58="","",DATEDIF(J58,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J58" s="6" t="n"/>
       <c r="K58" s="4" t="n"/>
       <c r="L58" s="4" t="n"/>
       <c r="M58" s="4" t="n"/>
       <c r="N58" s="4" t="n"/>
       <c r="O58" s="4" t="n"/>
-      <c r="P58" s="6" t="n"/>
-      <c r="Q58" s="3" t="n"/>
-      <c r="R58" s="4" t="n"/>
+      <c r="P58" s="4" t="n"/>
+      <c r="Q58" s="6" t="n"/>
+      <c r="R58" s="3" t="n"/>
+      <c r="S58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n"/>
@@ -2440,24 +2451,24 @@
         </is>
       </c>
       <c r="F59" s="4" t="n"/>
-      <c r="G59" s="5">
-        <f>IF(P59="","",DATEDIF(P59,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P59,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H59" s="5">
-        <f>IF(I59="","",DATEDIF(I59,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I59" s="6" t="n"/>
-      <c r="J59" s="4" t="n"/>
+        <f>IF(Q59="","",DATEDIF(Q59,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q59,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I59" s="5">
+        <f>IF(J59="","",DATEDIF(J59,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J59" s="6" t="n"/>
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
       <c r="M59" s="4" t="n"/>
       <c r="N59" s="4" t="n"/>
       <c r="O59" s="4" t="n"/>
-      <c r="P59" s="6" t="n"/>
-      <c r="Q59" s="3" t="n"/>
-      <c r="R59" s="4" t="n"/>
+      <c r="P59" s="4" t="n"/>
+      <c r="Q59" s="6" t="n"/>
+      <c r="R59" s="3" t="n"/>
+      <c r="S59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n"/>
@@ -2470,24 +2481,24 @@
         </is>
       </c>
       <c r="F60" s="4" t="n"/>
-      <c r="G60" s="5">
-        <f>IF(P60="","",DATEDIF(P60,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P60,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H60" s="5">
-        <f>IF(I60="","",DATEDIF(I60,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I60" s="6" t="n"/>
-      <c r="J60" s="4" t="n"/>
+        <f>IF(Q60="","",DATEDIF(Q60,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q60,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I60" s="5">
+        <f>IF(J60="","",DATEDIF(J60,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J60" s="6" t="n"/>
       <c r="K60" s="4" t="n"/>
       <c r="L60" s="4" t="n"/>
       <c r="M60" s="4" t="n"/>
       <c r="N60" s="4" t="n"/>
       <c r="O60" s="4" t="n"/>
-      <c r="P60" s="6" t="n"/>
-      <c r="Q60" s="3" t="n"/>
-      <c r="R60" s="4" t="n"/>
+      <c r="P60" s="4" t="n"/>
+      <c r="Q60" s="6" t="n"/>
+      <c r="R60" s="3" t="n"/>
+      <c r="S60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n"/>
@@ -2500,24 +2511,24 @@
         </is>
       </c>
       <c r="F61" s="4" t="n"/>
-      <c r="G61" s="5">
-        <f>IF(P61="","",DATEDIF(P61,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P61,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H61" s="5">
-        <f>IF(I61="","",DATEDIF(I61,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I61" s="6" t="n"/>
-      <c r="J61" s="4" t="n"/>
+        <f>IF(Q61="","",DATEDIF(Q61,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q61,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I61" s="5">
+        <f>IF(J61="","",DATEDIF(J61,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J61" s="6" t="n"/>
       <c r="K61" s="4" t="n"/>
       <c r="L61" s="4" t="n"/>
       <c r="M61" s="4" t="n"/>
       <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="n"/>
-      <c r="P61" s="6" t="n"/>
-      <c r="Q61" s="3" t="n"/>
-      <c r="R61" s="4" t="n"/>
+      <c r="P61" s="4" t="n"/>
+      <c r="Q61" s="6" t="n"/>
+      <c r="R61" s="3" t="n"/>
+      <c r="S61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n"/>
@@ -2530,24 +2541,24 @@
         </is>
       </c>
       <c r="F62" s="4" t="n"/>
-      <c r="G62" s="5">
-        <f>IF(P62="","",DATEDIF(P62,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P62,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H62" s="5">
-        <f>IF(I62="","",DATEDIF(I62,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I62" s="6" t="n"/>
-      <c r="J62" s="4" t="n"/>
+        <f>IF(Q62="","",DATEDIF(Q62,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q62,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I62" s="5">
+        <f>IF(J62="","",DATEDIF(J62,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J62" s="6" t="n"/>
       <c r="K62" s="4" t="n"/>
       <c r="L62" s="4" t="n"/>
       <c r="M62" s="4" t="n"/>
       <c r="N62" s="4" t="n"/>
       <c r="O62" s="4" t="n"/>
-      <c r="P62" s="6" t="n"/>
-      <c r="Q62" s="3" t="n"/>
-      <c r="R62" s="4" t="n"/>
+      <c r="P62" s="4" t="n"/>
+      <c r="Q62" s="6" t="n"/>
+      <c r="R62" s="3" t="n"/>
+      <c r="S62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n"/>
@@ -2560,24 +2571,24 @@
         </is>
       </c>
       <c r="F63" s="4" t="n"/>
-      <c r="G63" s="5">
-        <f>IF(P63="","",DATEDIF(P63,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P63,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H63" s="5">
-        <f>IF(I63="","",DATEDIF(I63,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I63" s="6" t="n"/>
-      <c r="J63" s="4" t="n"/>
+        <f>IF(Q63="","",DATEDIF(Q63,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q63,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I63" s="5">
+        <f>IF(J63="","",DATEDIF(J63,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J63" s="6" t="n"/>
       <c r="K63" s="4" t="n"/>
       <c r="L63" s="4" t="n"/>
       <c r="M63" s="4" t="n"/>
       <c r="N63" s="4" t="n"/>
       <c r="O63" s="4" t="n"/>
-      <c r="P63" s="6" t="n"/>
-      <c r="Q63" s="3" t="n"/>
-      <c r="R63" s="4" t="n"/>
+      <c r="P63" s="4" t="n"/>
+      <c r="Q63" s="6" t="n"/>
+      <c r="R63" s="3" t="n"/>
+      <c r="S63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n"/>
@@ -2590,24 +2601,24 @@
         </is>
       </c>
       <c r="F64" s="4" t="n"/>
-      <c r="G64" s="5">
-        <f>IF(P64="","",DATEDIF(P64,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P64,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H64" s="5">
-        <f>IF(I64="","",DATEDIF(I64,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I64" s="6" t="n"/>
-      <c r="J64" s="4" t="n"/>
+        <f>IF(Q64="","",DATEDIF(Q64,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q64,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I64" s="5">
+        <f>IF(J64="","",DATEDIF(J64,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J64" s="6" t="n"/>
       <c r="K64" s="4" t="n"/>
       <c r="L64" s="4" t="n"/>
       <c r="M64" s="4" t="n"/>
       <c r="N64" s="4" t="n"/>
       <c r="O64" s="4" t="n"/>
-      <c r="P64" s="6" t="n"/>
-      <c r="Q64" s="3" t="n"/>
-      <c r="R64" s="4" t="n"/>
+      <c r="P64" s="4" t="n"/>
+      <c r="Q64" s="6" t="n"/>
+      <c r="R64" s="3" t="n"/>
+      <c r="S64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n"/>
@@ -2620,24 +2631,24 @@
         </is>
       </c>
       <c r="F65" s="4" t="n"/>
-      <c r="G65" s="5">
-        <f>IF(P65="","",DATEDIF(P65,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P65,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H65" s="5">
-        <f>IF(I65="","",DATEDIF(I65,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I65" s="6" t="n"/>
-      <c r="J65" s="4" t="n"/>
+        <f>IF(Q65="","",DATEDIF(Q65,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q65,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I65" s="5">
+        <f>IF(J65="","",DATEDIF(J65,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J65" s="6" t="n"/>
       <c r="K65" s="4" t="n"/>
       <c r="L65" s="4" t="n"/>
       <c r="M65" s="4" t="n"/>
       <c r="N65" s="4" t="n"/>
       <c r="O65" s="4" t="n"/>
-      <c r="P65" s="6" t="n"/>
-      <c r="Q65" s="3" t="n"/>
-      <c r="R65" s="4" t="n"/>
+      <c r="P65" s="4" t="n"/>
+      <c r="Q65" s="6" t="n"/>
+      <c r="R65" s="3" t="n"/>
+      <c r="S65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n"/>
@@ -2650,24 +2661,24 @@
         </is>
       </c>
       <c r="F66" s="4" t="n"/>
-      <c r="G66" s="5">
-        <f>IF(P66="","",DATEDIF(P66,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P66,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H66" s="5">
-        <f>IF(I66="","",DATEDIF(I66,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I66" s="6" t="n"/>
-      <c r="J66" s="4" t="n"/>
+        <f>IF(Q66="","",DATEDIF(Q66,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q66,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I66" s="5">
+        <f>IF(J66="","",DATEDIF(J66,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J66" s="6" t="n"/>
       <c r="K66" s="4" t="n"/>
       <c r="L66" s="4" t="n"/>
       <c r="M66" s="4" t="n"/>
       <c r="N66" s="4" t="n"/>
       <c r="O66" s="4" t="n"/>
-      <c r="P66" s="6" t="n"/>
-      <c r="Q66" s="3" t="n"/>
-      <c r="R66" s="4" t="n"/>
+      <c r="P66" s="4" t="n"/>
+      <c r="Q66" s="6" t="n"/>
+      <c r="R66" s="3" t="n"/>
+      <c r="S66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n"/>
@@ -2680,24 +2691,24 @@
         </is>
       </c>
       <c r="F67" s="4" t="n"/>
-      <c r="G67" s="5">
-        <f>IF(P67="","",DATEDIF(P67,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P67,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H67" s="5">
-        <f>IF(I67="","",DATEDIF(I67,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I67" s="6" t="n"/>
-      <c r="J67" s="4" t="n"/>
+        <f>IF(Q67="","",DATEDIF(Q67,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q67,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I67" s="5">
+        <f>IF(J67="","",DATEDIF(J67,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J67" s="6" t="n"/>
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="4" t="n"/>
       <c r="M67" s="4" t="n"/>
       <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="n"/>
-      <c r="P67" s="6" t="n"/>
-      <c r="Q67" s="3" t="n"/>
-      <c r="R67" s="4" t="n"/>
+      <c r="P67" s="4" t="n"/>
+      <c r="Q67" s="6" t="n"/>
+      <c r="R67" s="3" t="n"/>
+      <c r="S67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n"/>
@@ -2710,24 +2721,24 @@
         </is>
       </c>
       <c r="F68" s="4" t="n"/>
-      <c r="G68" s="5">
-        <f>IF(P68="","",DATEDIF(P68,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P68,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H68" s="5">
-        <f>IF(I68="","",DATEDIF(I68,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I68" s="6" t="n"/>
-      <c r="J68" s="4" t="n"/>
+        <f>IF(Q68="","",DATEDIF(Q68,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q68,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I68" s="5">
+        <f>IF(J68="","",DATEDIF(J68,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J68" s="6" t="n"/>
       <c r="K68" s="4" t="n"/>
       <c r="L68" s="4" t="n"/>
       <c r="M68" s="4" t="n"/>
       <c r="N68" s="4" t="n"/>
       <c r="O68" s="4" t="n"/>
-      <c r="P68" s="6" t="n"/>
-      <c r="Q68" s="3" t="n"/>
-      <c r="R68" s="4" t="n"/>
+      <c r="P68" s="4" t="n"/>
+      <c r="Q68" s="6" t="n"/>
+      <c r="R68" s="3" t="n"/>
+      <c r="S68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n"/>
@@ -2740,24 +2751,24 @@
         </is>
       </c>
       <c r="F69" s="4" t="n"/>
-      <c r="G69" s="5">
-        <f>IF(P69="","",DATEDIF(P69,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P69,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H69" s="5">
-        <f>IF(I69="","",DATEDIF(I69,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I69" s="6" t="n"/>
-      <c r="J69" s="4" t="n"/>
+        <f>IF(Q69="","",DATEDIF(Q69,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q69,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I69" s="5">
+        <f>IF(J69="","",DATEDIF(J69,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J69" s="6" t="n"/>
       <c r="K69" s="4" t="n"/>
       <c r="L69" s="4" t="n"/>
       <c r="M69" s="4" t="n"/>
       <c r="N69" s="4" t="n"/>
       <c r="O69" s="4" t="n"/>
-      <c r="P69" s="6" t="n"/>
-      <c r="Q69" s="3" t="n"/>
-      <c r="R69" s="4" t="n"/>
+      <c r="P69" s="4" t="n"/>
+      <c r="Q69" s="6" t="n"/>
+      <c r="R69" s="3" t="n"/>
+      <c r="S69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n"/>
@@ -2770,24 +2781,24 @@
         </is>
       </c>
       <c r="F70" s="4" t="n"/>
-      <c r="G70" s="5">
-        <f>IF(P70="","",DATEDIF(P70,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P70,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H70" s="5">
-        <f>IF(I70="","",DATEDIF(I70,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I70" s="6" t="n"/>
-      <c r="J70" s="4" t="n"/>
+        <f>IF(Q70="","",DATEDIF(Q70,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q70,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I70" s="5">
+        <f>IF(J70="","",DATEDIF(J70,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J70" s="6" t="n"/>
       <c r="K70" s="4" t="n"/>
       <c r="L70" s="4" t="n"/>
       <c r="M70" s="4" t="n"/>
       <c r="N70" s="4" t="n"/>
       <c r="O70" s="4" t="n"/>
-      <c r="P70" s="6" t="n"/>
-      <c r="Q70" s="3" t="n"/>
-      <c r="R70" s="4" t="n"/>
+      <c r="P70" s="4" t="n"/>
+      <c r="Q70" s="6" t="n"/>
+      <c r="R70" s="3" t="n"/>
+      <c r="S70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n"/>
@@ -2800,24 +2811,24 @@
         </is>
       </c>
       <c r="F71" s="4" t="n"/>
-      <c r="G71" s="5">
-        <f>IF(P71="","",DATEDIF(P71,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P71,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H71" s="5">
-        <f>IF(I71="","",DATEDIF(I71,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I71" s="6" t="n"/>
-      <c r="J71" s="4" t="n"/>
+        <f>IF(Q71="","",DATEDIF(Q71,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q71,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I71" s="5">
+        <f>IF(J71="","",DATEDIF(J71,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J71" s="6" t="n"/>
       <c r="K71" s="4" t="n"/>
       <c r="L71" s="4" t="n"/>
       <c r="M71" s="4" t="n"/>
       <c r="N71" s="4" t="n"/>
       <c r="O71" s="4" t="n"/>
-      <c r="P71" s="6" t="n"/>
-      <c r="Q71" s="3" t="n"/>
-      <c r="R71" s="4" t="n"/>
+      <c r="P71" s="4" t="n"/>
+      <c r="Q71" s="6" t="n"/>
+      <c r="R71" s="3" t="n"/>
+      <c r="S71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n"/>
@@ -2830,24 +2841,24 @@
         </is>
       </c>
       <c r="F72" s="4" t="n"/>
-      <c r="G72" s="5">
-        <f>IF(P72="","",DATEDIF(P72,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P72,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H72" s="5">
-        <f>IF(I72="","",DATEDIF(I72,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I72" s="6" t="n"/>
-      <c r="J72" s="4" t="n"/>
+        <f>IF(Q72="","",DATEDIF(Q72,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q72,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I72" s="5">
+        <f>IF(J72="","",DATEDIF(J72,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J72" s="6" t="n"/>
       <c r="K72" s="4" t="n"/>
       <c r="L72" s="4" t="n"/>
       <c r="M72" s="4" t="n"/>
       <c r="N72" s="4" t="n"/>
       <c r="O72" s="4" t="n"/>
-      <c r="P72" s="6" t="n"/>
-      <c r="Q72" s="3" t="n"/>
-      <c r="R72" s="4" t="n"/>
+      <c r="P72" s="4" t="n"/>
+      <c r="Q72" s="6" t="n"/>
+      <c r="R72" s="3" t="n"/>
+      <c r="S72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n"/>
@@ -2860,24 +2871,24 @@
         </is>
       </c>
       <c r="F73" s="4" t="n"/>
-      <c r="G73" s="5">
-        <f>IF(P73="","",DATEDIF(P73,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P73,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H73" s="5">
-        <f>IF(I73="","",DATEDIF(I73,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I73" s="6" t="n"/>
-      <c r="J73" s="4" t="n"/>
+        <f>IF(Q73="","",DATEDIF(Q73,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q73,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I73" s="5">
+        <f>IF(J73="","",DATEDIF(J73,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J73" s="6" t="n"/>
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
       <c r="M73" s="4" t="n"/>
       <c r="N73" s="4" t="n"/>
       <c r="O73" s="4" t="n"/>
-      <c r="P73" s="6" t="n"/>
-      <c r="Q73" s="3" t="n"/>
-      <c r="R73" s="4" t="n"/>
+      <c r="P73" s="4" t="n"/>
+      <c r="Q73" s="6" t="n"/>
+      <c r="R73" s="3" t="n"/>
+      <c r="S73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n"/>
@@ -2890,24 +2901,24 @@
         </is>
       </c>
       <c r="F74" s="4" t="n"/>
-      <c r="G74" s="5">
-        <f>IF(P74="","",DATEDIF(P74,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P74,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H74" s="5">
-        <f>IF(I74="","",DATEDIF(I74,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I74" s="6" t="n"/>
-      <c r="J74" s="4" t="n"/>
+        <f>IF(Q74="","",DATEDIF(Q74,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q74,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I74" s="5">
+        <f>IF(J74="","",DATEDIF(J74,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J74" s="6" t="n"/>
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="n"/>
       <c r="M74" s="4" t="n"/>
       <c r="N74" s="4" t="n"/>
       <c r="O74" s="4" t="n"/>
-      <c r="P74" s="6" t="n"/>
-      <c r="Q74" s="3" t="n"/>
-      <c r="R74" s="4" t="n"/>
+      <c r="P74" s="4" t="n"/>
+      <c r="Q74" s="6" t="n"/>
+      <c r="R74" s="3" t="n"/>
+      <c r="S74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n"/>
@@ -2920,24 +2931,24 @@
         </is>
       </c>
       <c r="F75" s="4" t="n"/>
-      <c r="G75" s="5">
-        <f>IF(P75="","",DATEDIF(P75,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P75,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H75" s="5">
-        <f>IF(I75="","",DATEDIF(I75,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I75" s="6" t="n"/>
-      <c r="J75" s="4" t="n"/>
+        <f>IF(Q75="","",DATEDIF(Q75,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q75,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I75" s="5">
+        <f>IF(J75="","",DATEDIF(J75,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J75" s="6" t="n"/>
       <c r="K75" s="4" t="n"/>
       <c r="L75" s="4" t="n"/>
       <c r="M75" s="4" t="n"/>
       <c r="N75" s="4" t="n"/>
       <c r="O75" s="4" t="n"/>
-      <c r="P75" s="6" t="n"/>
-      <c r="Q75" s="3" t="n"/>
-      <c r="R75" s="4" t="n"/>
+      <c r="P75" s="4" t="n"/>
+      <c r="Q75" s="6" t="n"/>
+      <c r="R75" s="3" t="n"/>
+      <c r="S75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n"/>
@@ -2950,24 +2961,24 @@
         </is>
       </c>
       <c r="F76" s="4" t="n"/>
-      <c r="G76" s="5">
-        <f>IF(P76="","",DATEDIF(P76,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P76,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H76" s="5">
-        <f>IF(I76="","",DATEDIF(I76,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I76" s="6" t="n"/>
-      <c r="J76" s="4" t="n"/>
+        <f>IF(Q76="","",DATEDIF(Q76,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q76,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I76" s="5">
+        <f>IF(J76="","",DATEDIF(J76,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J76" s="6" t="n"/>
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>
       <c r="M76" s="4" t="n"/>
       <c r="N76" s="4" t="n"/>
       <c r="O76" s="4" t="n"/>
-      <c r="P76" s="6" t="n"/>
-      <c r="Q76" s="3" t="n"/>
-      <c r="R76" s="4" t="n"/>
+      <c r="P76" s="4" t="n"/>
+      <c r="Q76" s="6" t="n"/>
+      <c r="R76" s="3" t="n"/>
+      <c r="S76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n"/>
@@ -2980,24 +2991,24 @@
         </is>
       </c>
       <c r="F77" s="4" t="n"/>
-      <c r="G77" s="5">
-        <f>IF(P77="","",DATEDIF(P77,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P77,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H77" s="5">
-        <f>IF(I77="","",DATEDIF(I77,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I77" s="6" t="n"/>
-      <c r="J77" s="4" t="n"/>
+        <f>IF(Q77="","",DATEDIF(Q77,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q77,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I77" s="5">
+        <f>IF(J77="","",DATEDIF(J77,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J77" s="6" t="n"/>
       <c r="K77" s="4" t="n"/>
       <c r="L77" s="4" t="n"/>
       <c r="M77" s="4" t="n"/>
       <c r="N77" s="4" t="n"/>
       <c r="O77" s="4" t="n"/>
-      <c r="P77" s="6" t="n"/>
-      <c r="Q77" s="3" t="n"/>
-      <c r="R77" s="4" t="n"/>
+      <c r="P77" s="4" t="n"/>
+      <c r="Q77" s="6" t="n"/>
+      <c r="R77" s="3" t="n"/>
+      <c r="S77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n"/>
@@ -3010,24 +3021,24 @@
         </is>
       </c>
       <c r="F78" s="4" t="n"/>
-      <c r="G78" s="5">
-        <f>IF(P78="","",DATEDIF(P78,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P78,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H78" s="5">
-        <f>IF(I78="","",DATEDIF(I78,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I78" s="6" t="n"/>
-      <c r="J78" s="4" t="n"/>
+        <f>IF(Q78="","",DATEDIF(Q78,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q78,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I78" s="5">
+        <f>IF(J78="","",DATEDIF(J78,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J78" s="6" t="n"/>
       <c r="K78" s="4" t="n"/>
       <c r="L78" s="4" t="n"/>
       <c r="M78" s="4" t="n"/>
       <c r="N78" s="4" t="n"/>
       <c r="O78" s="4" t="n"/>
-      <c r="P78" s="6" t="n"/>
-      <c r="Q78" s="3" t="n"/>
-      <c r="R78" s="4" t="n"/>
+      <c r="P78" s="4" t="n"/>
+      <c r="Q78" s="6" t="n"/>
+      <c r="R78" s="3" t="n"/>
+      <c r="S78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n"/>
@@ -3040,24 +3051,24 @@
         </is>
       </c>
       <c r="F79" s="4" t="n"/>
-      <c r="G79" s="5">
-        <f>IF(P79="","",DATEDIF(P79,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P79,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H79" s="5">
-        <f>IF(I79="","",DATEDIF(I79,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I79" s="6" t="n"/>
-      <c r="J79" s="4" t="n"/>
+        <f>IF(Q79="","",DATEDIF(Q79,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q79,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I79" s="5">
+        <f>IF(J79="","",DATEDIF(J79,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J79" s="6" t="n"/>
       <c r="K79" s="4" t="n"/>
       <c r="L79" s="4" t="n"/>
       <c r="M79" s="4" t="n"/>
       <c r="N79" s="4" t="n"/>
       <c r="O79" s="4" t="n"/>
-      <c r="P79" s="6" t="n"/>
-      <c r="Q79" s="3" t="n"/>
-      <c r="R79" s="4" t="n"/>
+      <c r="P79" s="4" t="n"/>
+      <c r="Q79" s="6" t="n"/>
+      <c r="R79" s="3" t="n"/>
+      <c r="S79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n"/>
@@ -3070,24 +3081,24 @@
         </is>
       </c>
       <c r="F80" s="4" t="n"/>
-      <c r="G80" s="5">
-        <f>IF(P80="","",DATEDIF(P80,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P80,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H80" s="5">
-        <f>IF(I80="","",DATEDIF(I80,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I80" s="6" t="n"/>
-      <c r="J80" s="4" t="n"/>
+        <f>IF(Q80="","",DATEDIF(Q80,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q80,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I80" s="5">
+        <f>IF(J80="","",DATEDIF(J80,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J80" s="6" t="n"/>
       <c r="K80" s="4" t="n"/>
       <c r="L80" s="4" t="n"/>
       <c r="M80" s="4" t="n"/>
       <c r="N80" s="4" t="n"/>
       <c r="O80" s="4" t="n"/>
-      <c r="P80" s="6" t="n"/>
-      <c r="Q80" s="3" t="n"/>
-      <c r="R80" s="4" t="n"/>
+      <c r="P80" s="4" t="n"/>
+      <c r="Q80" s="6" t="n"/>
+      <c r="R80" s="3" t="n"/>
+      <c r="S80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n"/>
@@ -3100,24 +3111,24 @@
         </is>
       </c>
       <c r="F81" s="4" t="n"/>
-      <c r="G81" s="5">
-        <f>IF(P81="","",DATEDIF(P81,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P81,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H81" s="5">
-        <f>IF(I81="","",DATEDIF(I81,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I81" s="6" t="n"/>
-      <c r="J81" s="4" t="n"/>
+        <f>IF(Q81="","",DATEDIF(Q81,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q81,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I81" s="5">
+        <f>IF(J81="","",DATEDIF(J81,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J81" s="6" t="n"/>
       <c r="K81" s="4" t="n"/>
       <c r="L81" s="4" t="n"/>
       <c r="M81" s="4" t="n"/>
       <c r="N81" s="4" t="n"/>
       <c r="O81" s="4" t="n"/>
-      <c r="P81" s="6" t="n"/>
-      <c r="Q81" s="3" t="n"/>
-      <c r="R81" s="4" t="n"/>
+      <c r="P81" s="4" t="n"/>
+      <c r="Q81" s="6" t="n"/>
+      <c r="R81" s="3" t="n"/>
+      <c r="S81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n"/>
@@ -3130,24 +3141,24 @@
         </is>
       </c>
       <c r="F82" s="4" t="n"/>
-      <c r="G82" s="5">
-        <f>IF(P82="","",DATEDIF(P82,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P82,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H82" s="5">
-        <f>IF(I82="","",DATEDIF(I82,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I82" s="6" t="n"/>
-      <c r="J82" s="4" t="n"/>
+        <f>IF(Q82="","",DATEDIF(Q82,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q82,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I82" s="5">
+        <f>IF(J82="","",DATEDIF(J82,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J82" s="6" t="n"/>
       <c r="K82" s="4" t="n"/>
       <c r="L82" s="4" t="n"/>
       <c r="M82" s="4" t="n"/>
       <c r="N82" s="4" t="n"/>
       <c r="O82" s="4" t="n"/>
-      <c r="P82" s="6" t="n"/>
-      <c r="Q82" s="3" t="n"/>
-      <c r="R82" s="4" t="n"/>
+      <c r="P82" s="4" t="n"/>
+      <c r="Q82" s="6" t="n"/>
+      <c r="R82" s="3" t="n"/>
+      <c r="S82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n"/>
@@ -3160,24 +3171,24 @@
         </is>
       </c>
       <c r="F83" s="4" t="n"/>
-      <c r="G83" s="5">
-        <f>IF(P83="","",DATEDIF(P83,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P83,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H83" s="5">
-        <f>IF(I83="","",DATEDIF(I83,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I83" s="6" t="n"/>
-      <c r="J83" s="4" t="n"/>
+        <f>IF(Q83="","",DATEDIF(Q83,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q83,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I83" s="5">
+        <f>IF(J83="","",DATEDIF(J83,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J83" s="6" t="n"/>
       <c r="K83" s="4" t="n"/>
       <c r="L83" s="4" t="n"/>
       <c r="M83" s="4" t="n"/>
       <c r="N83" s="4" t="n"/>
       <c r="O83" s="4" t="n"/>
-      <c r="P83" s="6" t="n"/>
-      <c r="Q83" s="3" t="n"/>
-      <c r="R83" s="4" t="n"/>
+      <c r="P83" s="4" t="n"/>
+      <c r="Q83" s="6" t="n"/>
+      <c r="R83" s="3" t="n"/>
+      <c r="S83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n"/>
@@ -3190,24 +3201,24 @@
         </is>
       </c>
       <c r="F84" s="4" t="n"/>
-      <c r="G84" s="5">
-        <f>IF(P84="","",DATEDIF(P84,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P84,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H84" s="5">
-        <f>IF(I84="","",DATEDIF(I84,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I84" s="6" t="n"/>
-      <c r="J84" s="4" t="n"/>
+        <f>IF(Q84="","",DATEDIF(Q84,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q84,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I84" s="5">
+        <f>IF(J84="","",DATEDIF(J84,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J84" s="6" t="n"/>
       <c r="K84" s="4" t="n"/>
       <c r="L84" s="4" t="n"/>
       <c r="M84" s="4" t="n"/>
       <c r="N84" s="4" t="n"/>
       <c r="O84" s="4" t="n"/>
-      <c r="P84" s="6" t="n"/>
-      <c r="Q84" s="3" t="n"/>
-      <c r="R84" s="4" t="n"/>
+      <c r="P84" s="4" t="n"/>
+      <c r="Q84" s="6" t="n"/>
+      <c r="R84" s="3" t="n"/>
+      <c r="S84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n"/>
@@ -3220,24 +3231,24 @@
         </is>
       </c>
       <c r="F85" s="4" t="n"/>
-      <c r="G85" s="5">
-        <f>IF(P85="","",DATEDIF(P85,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P85,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H85" s="5">
-        <f>IF(I85="","",DATEDIF(I85,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I85" s="6" t="n"/>
-      <c r="J85" s="4" t="n"/>
+        <f>IF(Q85="","",DATEDIF(Q85,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q85,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I85" s="5">
+        <f>IF(J85="","",DATEDIF(J85,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J85" s="6" t="n"/>
       <c r="K85" s="4" t="n"/>
       <c r="L85" s="4" t="n"/>
       <c r="M85" s="4" t="n"/>
       <c r="N85" s="4" t="n"/>
       <c r="O85" s="4" t="n"/>
-      <c r="P85" s="6" t="n"/>
-      <c r="Q85" s="3" t="n"/>
-      <c r="R85" s="4" t="n"/>
+      <c r="P85" s="4" t="n"/>
+      <c r="Q85" s="6" t="n"/>
+      <c r="R85" s="3" t="n"/>
+      <c r="S85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n"/>
@@ -3250,24 +3261,24 @@
         </is>
       </c>
       <c r="F86" s="4" t="n"/>
-      <c r="G86" s="5">
-        <f>IF(P86="","",DATEDIF(P86,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P86,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H86" s="5">
-        <f>IF(I86="","",DATEDIF(I86,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I86" s="6" t="n"/>
-      <c r="J86" s="4" t="n"/>
+        <f>IF(Q86="","",DATEDIF(Q86,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q86,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I86" s="5">
+        <f>IF(J86="","",DATEDIF(J86,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J86" s="6" t="n"/>
       <c r="K86" s="4" t="n"/>
       <c r="L86" s="4" t="n"/>
       <c r="M86" s="4" t="n"/>
       <c r="N86" s="4" t="n"/>
       <c r="O86" s="4" t="n"/>
-      <c r="P86" s="6" t="n"/>
-      <c r="Q86" s="3" t="n"/>
-      <c r="R86" s="4" t="n"/>
+      <c r="P86" s="4" t="n"/>
+      <c r="Q86" s="6" t="n"/>
+      <c r="R86" s="3" t="n"/>
+      <c r="S86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n"/>
@@ -3280,24 +3291,24 @@
         </is>
       </c>
       <c r="F87" s="4" t="n"/>
-      <c r="G87" s="5">
-        <f>IF(P87="","",DATEDIF(P87,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P87,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H87" s="5">
-        <f>IF(I87="","",DATEDIF(I87,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I87" s="6" t="n"/>
-      <c r="J87" s="4" t="n"/>
+        <f>IF(Q87="","",DATEDIF(Q87,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q87,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I87" s="5">
+        <f>IF(J87="","",DATEDIF(J87,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J87" s="6" t="n"/>
       <c r="K87" s="4" t="n"/>
       <c r="L87" s="4" t="n"/>
       <c r="M87" s="4" t="n"/>
       <c r="N87" s="4" t="n"/>
       <c r="O87" s="4" t="n"/>
-      <c r="P87" s="6" t="n"/>
-      <c r="Q87" s="3" t="n"/>
-      <c r="R87" s="4" t="n"/>
+      <c r="P87" s="4" t="n"/>
+      <c r="Q87" s="6" t="n"/>
+      <c r="R87" s="3" t="n"/>
+      <c r="S87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n"/>
@@ -3310,24 +3321,24 @@
         </is>
       </c>
       <c r="F88" s="4" t="n"/>
-      <c r="G88" s="5">
-        <f>IF(P88="","",DATEDIF(P88,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P88,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H88" s="5">
-        <f>IF(I88="","",DATEDIF(I88,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I88" s="6" t="n"/>
-      <c r="J88" s="4" t="n"/>
+        <f>IF(Q88="","",DATEDIF(Q88,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q88,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I88" s="5">
+        <f>IF(J88="","",DATEDIF(J88,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J88" s="6" t="n"/>
       <c r="K88" s="4" t="n"/>
       <c r="L88" s="4" t="n"/>
       <c r="M88" s="4" t="n"/>
       <c r="N88" s="4" t="n"/>
       <c r="O88" s="4" t="n"/>
-      <c r="P88" s="6" t="n"/>
-      <c r="Q88" s="3" t="n"/>
-      <c r="R88" s="4" t="n"/>
+      <c r="P88" s="4" t="n"/>
+      <c r="Q88" s="6" t="n"/>
+      <c r="R88" s="3" t="n"/>
+      <c r="S88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n"/>
@@ -3340,24 +3351,24 @@
         </is>
       </c>
       <c r="F89" s="4" t="n"/>
-      <c r="G89" s="5">
-        <f>IF(P89="","",DATEDIF(P89,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P89,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H89" s="5">
-        <f>IF(I89="","",DATEDIF(I89,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I89" s="6" t="n"/>
-      <c r="J89" s="4" t="n"/>
+        <f>IF(Q89="","",DATEDIF(Q89,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q89,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I89" s="5">
+        <f>IF(J89="","",DATEDIF(J89,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J89" s="6" t="n"/>
       <c r="K89" s="4" t="n"/>
       <c r="L89" s="4" t="n"/>
       <c r="M89" s="4" t="n"/>
       <c r="N89" s="4" t="n"/>
       <c r="O89" s="4" t="n"/>
-      <c r="P89" s="6" t="n"/>
-      <c r="Q89" s="3" t="n"/>
-      <c r="R89" s="4" t="n"/>
+      <c r="P89" s="4" t="n"/>
+      <c r="Q89" s="6" t="n"/>
+      <c r="R89" s="3" t="n"/>
+      <c r="S89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n"/>
@@ -3370,24 +3381,24 @@
         </is>
       </c>
       <c r="F90" s="4" t="n"/>
-      <c r="G90" s="5">
-        <f>IF(P90="","",DATEDIF(P90,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P90,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H90" s="5">
-        <f>IF(I90="","",DATEDIF(I90,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I90" s="6" t="n"/>
-      <c r="J90" s="4" t="n"/>
+        <f>IF(Q90="","",DATEDIF(Q90,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q90,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I90" s="5">
+        <f>IF(J90="","",DATEDIF(J90,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J90" s="6" t="n"/>
       <c r="K90" s="4" t="n"/>
       <c r="L90" s="4" t="n"/>
       <c r="M90" s="4" t="n"/>
       <c r="N90" s="4" t="n"/>
       <c r="O90" s="4" t="n"/>
-      <c r="P90" s="6" t="n"/>
-      <c r="Q90" s="3" t="n"/>
-      <c r="R90" s="4" t="n"/>
+      <c r="P90" s="4" t="n"/>
+      <c r="Q90" s="6" t="n"/>
+      <c r="R90" s="3" t="n"/>
+      <c r="S90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n"/>
@@ -3400,24 +3411,24 @@
         </is>
       </c>
       <c r="F91" s="4" t="n"/>
-      <c r="G91" s="5">
-        <f>IF(P91="","",DATEDIF(P91,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P91,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H91" s="5">
-        <f>IF(I91="","",DATEDIF(I91,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I91" s="6" t="n"/>
-      <c r="J91" s="4" t="n"/>
+        <f>IF(Q91="","",DATEDIF(Q91,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q91,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I91" s="5">
+        <f>IF(J91="","",DATEDIF(J91,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J91" s="6" t="n"/>
       <c r="K91" s="4" t="n"/>
       <c r="L91" s="4" t="n"/>
       <c r="M91" s="4" t="n"/>
       <c r="N91" s="4" t="n"/>
       <c r="O91" s="4" t="n"/>
-      <c r="P91" s="6" t="n"/>
-      <c r="Q91" s="3" t="n"/>
-      <c r="R91" s="4" t="n"/>
+      <c r="P91" s="4" t="n"/>
+      <c r="Q91" s="6" t="n"/>
+      <c r="R91" s="3" t="n"/>
+      <c r="S91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n"/>
@@ -3430,24 +3441,24 @@
         </is>
       </c>
       <c r="F92" s="4" t="n"/>
-      <c r="G92" s="5">
-        <f>IF(P92="","",DATEDIF(P92,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P92,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H92" s="5">
-        <f>IF(I92="","",DATEDIF(I92,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I92" s="6" t="n"/>
-      <c r="J92" s="4" t="n"/>
+        <f>IF(Q92="","",DATEDIF(Q92,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q92,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I92" s="5">
+        <f>IF(J92="","",DATEDIF(J92,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J92" s="6" t="n"/>
       <c r="K92" s="4" t="n"/>
       <c r="L92" s="4" t="n"/>
       <c r="M92" s="4" t="n"/>
       <c r="N92" s="4" t="n"/>
       <c r="O92" s="4" t="n"/>
-      <c r="P92" s="6" t="n"/>
-      <c r="Q92" s="3" t="n"/>
-      <c r="R92" s="4" t="n"/>
+      <c r="P92" s="4" t="n"/>
+      <c r="Q92" s="6" t="n"/>
+      <c r="R92" s="3" t="n"/>
+      <c r="S92" s="4" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n"/>
@@ -3460,24 +3471,24 @@
         </is>
       </c>
       <c r="F93" s="4" t="n"/>
-      <c r="G93" s="5">
-        <f>IF(P93="","",DATEDIF(P93,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P93,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H93" s="5">
-        <f>IF(I93="","",DATEDIF(I93,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I93" s="6" t="n"/>
-      <c r="J93" s="4" t="n"/>
+        <f>IF(Q93="","",DATEDIF(Q93,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q93,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I93" s="5">
+        <f>IF(J93="","",DATEDIF(J93,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J93" s="6" t="n"/>
       <c r="K93" s="4" t="n"/>
       <c r="L93" s="4" t="n"/>
       <c r="M93" s="4" t="n"/>
       <c r="N93" s="4" t="n"/>
       <c r="O93" s="4" t="n"/>
-      <c r="P93" s="6" t="n"/>
-      <c r="Q93" s="3" t="n"/>
-      <c r="R93" s="4" t="n"/>
+      <c r="P93" s="4" t="n"/>
+      <c r="Q93" s="6" t="n"/>
+      <c r="R93" s="3" t="n"/>
+      <c r="S93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n"/>
@@ -3490,24 +3501,24 @@
         </is>
       </c>
       <c r="F94" s="4" t="n"/>
-      <c r="G94" s="5">
-        <f>IF(P94="","",DATEDIF(P94,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P94,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H94" s="5">
-        <f>IF(I94="","",DATEDIF(I94,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I94" s="6" t="n"/>
-      <c r="J94" s="4" t="n"/>
+        <f>IF(Q94="","",DATEDIF(Q94,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q94,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I94" s="5">
+        <f>IF(J94="","",DATEDIF(J94,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J94" s="6" t="n"/>
       <c r="K94" s="4" t="n"/>
       <c r="L94" s="4" t="n"/>
       <c r="M94" s="4" t="n"/>
       <c r="N94" s="4" t="n"/>
       <c r="O94" s="4" t="n"/>
-      <c r="P94" s="6" t="n"/>
-      <c r="Q94" s="3" t="n"/>
-      <c r="R94" s="4" t="n"/>
+      <c r="P94" s="4" t="n"/>
+      <c r="Q94" s="6" t="n"/>
+      <c r="R94" s="3" t="n"/>
+      <c r="S94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n"/>
@@ -3520,24 +3531,24 @@
         </is>
       </c>
       <c r="F95" s="4" t="n"/>
-      <c r="G95" s="5">
-        <f>IF(P95="","",DATEDIF(P95,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P95,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H95" s="5">
-        <f>IF(I95="","",DATEDIF(I95,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I95" s="6" t="n"/>
-      <c r="J95" s="4" t="n"/>
+        <f>IF(Q95="","",DATEDIF(Q95,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q95,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I95" s="5">
+        <f>IF(J95="","",DATEDIF(J95,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J95" s="6" t="n"/>
       <c r="K95" s="4" t="n"/>
       <c r="L95" s="4" t="n"/>
       <c r="M95" s="4" t="n"/>
       <c r="N95" s="4" t="n"/>
       <c r="O95" s="4" t="n"/>
-      <c r="P95" s="6" t="n"/>
-      <c r="Q95" s="3" t="n"/>
-      <c r="R95" s="4" t="n"/>
+      <c r="P95" s="4" t="n"/>
+      <c r="Q95" s="6" t="n"/>
+      <c r="R95" s="3" t="n"/>
+      <c r="S95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n"/>
@@ -3550,24 +3561,24 @@
         </is>
       </c>
       <c r="F96" s="4" t="n"/>
-      <c r="G96" s="5">
-        <f>IF(P96="","",DATEDIF(P96,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P96,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H96" s="5">
-        <f>IF(I96="","",DATEDIF(I96,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I96" s="6" t="n"/>
-      <c r="J96" s="4" t="n"/>
+        <f>IF(Q96="","",DATEDIF(Q96,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q96,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I96" s="5">
+        <f>IF(J96="","",DATEDIF(J96,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J96" s="6" t="n"/>
       <c r="K96" s="4" t="n"/>
       <c r="L96" s="4" t="n"/>
       <c r="M96" s="4" t="n"/>
       <c r="N96" s="4" t="n"/>
       <c r="O96" s="4" t="n"/>
-      <c r="P96" s="6" t="n"/>
-      <c r="Q96" s="3" t="n"/>
-      <c r="R96" s="4" t="n"/>
+      <c r="P96" s="4" t="n"/>
+      <c r="Q96" s="6" t="n"/>
+      <c r="R96" s="3" t="n"/>
+      <c r="S96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n"/>
@@ -3580,24 +3591,24 @@
         </is>
       </c>
       <c r="F97" s="4" t="n"/>
-      <c r="G97" s="5">
-        <f>IF(P97="","",DATEDIF(P97,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P97,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H97" s="5">
-        <f>IF(I97="","",DATEDIF(I97,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I97" s="6" t="n"/>
-      <c r="J97" s="4" t="n"/>
+        <f>IF(Q97="","",DATEDIF(Q97,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q97,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I97" s="5">
+        <f>IF(J97="","",DATEDIF(J97,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J97" s="6" t="n"/>
       <c r="K97" s="4" t="n"/>
       <c r="L97" s="4" t="n"/>
       <c r="M97" s="4" t="n"/>
       <c r="N97" s="4" t="n"/>
       <c r="O97" s="4" t="n"/>
-      <c r="P97" s="6" t="n"/>
-      <c r="Q97" s="3" t="n"/>
-      <c r="R97" s="4" t="n"/>
+      <c r="P97" s="4" t="n"/>
+      <c r="Q97" s="6" t="n"/>
+      <c r="R97" s="3" t="n"/>
+      <c r="S97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n"/>
@@ -3610,24 +3621,24 @@
         </is>
       </c>
       <c r="F98" s="4" t="n"/>
-      <c r="G98" s="5">
-        <f>IF(P98="","",DATEDIF(P98,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P98,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H98" s="5">
-        <f>IF(I98="","",DATEDIF(I98,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I98" s="6" t="n"/>
-      <c r="J98" s="4" t="n"/>
+        <f>IF(Q98="","",DATEDIF(Q98,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q98,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I98" s="5">
+        <f>IF(J98="","",DATEDIF(J98,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J98" s="6" t="n"/>
       <c r="K98" s="4" t="n"/>
       <c r="L98" s="4" t="n"/>
       <c r="M98" s="4" t="n"/>
       <c r="N98" s="4" t="n"/>
       <c r="O98" s="4" t="n"/>
-      <c r="P98" s="6" t="n"/>
-      <c r="Q98" s="3" t="n"/>
-      <c r="R98" s="4" t="n"/>
+      <c r="P98" s="4" t="n"/>
+      <c r="Q98" s="6" t="n"/>
+      <c r="R98" s="3" t="n"/>
+      <c r="S98" s="4" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n"/>
@@ -3640,24 +3651,24 @@
         </is>
       </c>
       <c r="F99" s="4" t="n"/>
-      <c r="G99" s="5">
-        <f>IF(P99="","",DATEDIF(P99,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P99,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H99" s="5">
-        <f>IF(I99="","",DATEDIF(I99,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I99" s="6" t="n"/>
-      <c r="J99" s="4" t="n"/>
+        <f>IF(Q99="","",DATEDIF(Q99,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q99,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I99" s="5">
+        <f>IF(J99="","",DATEDIF(J99,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J99" s="6" t="n"/>
       <c r="K99" s="4" t="n"/>
       <c r="L99" s="4" t="n"/>
       <c r="M99" s="4" t="n"/>
       <c r="N99" s="4" t="n"/>
       <c r="O99" s="4" t="n"/>
-      <c r="P99" s="6" t="n"/>
-      <c r="Q99" s="3" t="n"/>
-      <c r="R99" s="4" t="n"/>
+      <c r="P99" s="4" t="n"/>
+      <c r="Q99" s="6" t="n"/>
+      <c r="R99" s="3" t="n"/>
+      <c r="S99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n"/>
@@ -3670,24 +3681,24 @@
         </is>
       </c>
       <c r="F100" s="4" t="n"/>
-      <c r="G100" s="5">
-        <f>IF(P100="","",DATEDIF(P100,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P100,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H100" s="5">
-        <f>IF(I100="","",DATEDIF(I100,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I100" s="6" t="n"/>
-      <c r="J100" s="4" t="n"/>
+        <f>IF(Q100="","",DATEDIF(Q100,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q100,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I100" s="5">
+        <f>IF(J100="","",DATEDIF(J100,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J100" s="6" t="n"/>
       <c r="K100" s="4" t="n"/>
       <c r="L100" s="4" t="n"/>
       <c r="M100" s="4" t="n"/>
       <c r="N100" s="4" t="n"/>
       <c r="O100" s="4" t="n"/>
-      <c r="P100" s="6" t="n"/>
-      <c r="Q100" s="3" t="n"/>
-      <c r="R100" s="4" t="n"/>
+      <c r="P100" s="4" t="n"/>
+      <c r="Q100" s="6" t="n"/>
+      <c r="R100" s="3" t="n"/>
+      <c r="S100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n"/>
@@ -3700,24 +3711,24 @@
         </is>
       </c>
       <c r="F101" s="4" t="n"/>
-      <c r="G101" s="5">
-        <f>IF(P101="","",DATEDIF(P101,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P101,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H101" s="5">
-        <f>IF(I101="","",DATEDIF(I101,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I101" s="6" t="n"/>
-      <c r="J101" s="4" t="n"/>
+        <f>IF(Q101="","",DATEDIF(Q101,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q101,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I101" s="5">
+        <f>IF(J101="","",DATEDIF(J101,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J101" s="6" t="n"/>
       <c r="K101" s="4" t="n"/>
       <c r="L101" s="4" t="n"/>
       <c r="M101" s="4" t="n"/>
       <c r="N101" s="4" t="n"/>
       <c r="O101" s="4" t="n"/>
-      <c r="P101" s="6" t="n"/>
-      <c r="Q101" s="3" t="n"/>
-      <c r="R101" s="4" t="n"/>
+      <c r="P101" s="4" t="n"/>
+      <c r="Q101" s="6" t="n"/>
+      <c r="R101" s="3" t="n"/>
+      <c r="S101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n"/>
@@ -3730,24 +3741,24 @@
         </is>
       </c>
       <c r="F102" s="4" t="n"/>
-      <c r="G102" s="5">
-        <f>IF(P102="","",DATEDIF(P102,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P102,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H102" s="5">
-        <f>IF(I102="","",DATEDIF(I102,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I102" s="6" t="n"/>
-      <c r="J102" s="4" t="n"/>
+        <f>IF(Q102="","",DATEDIF(Q102,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q102,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I102" s="5">
+        <f>IF(J102="","",DATEDIF(J102,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J102" s="6" t="n"/>
       <c r="K102" s="4" t="n"/>
       <c r="L102" s="4" t="n"/>
       <c r="M102" s="4" t="n"/>
       <c r="N102" s="4" t="n"/>
       <c r="O102" s="4" t="n"/>
-      <c r="P102" s="6" t="n"/>
-      <c r="Q102" s="3" t="n"/>
-      <c r="R102" s="4" t="n"/>
+      <c r="P102" s="4" t="n"/>
+      <c r="Q102" s="6" t="n"/>
+      <c r="R102" s="3" t="n"/>
+      <c r="S102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n"/>
@@ -3760,24 +3771,24 @@
         </is>
       </c>
       <c r="F103" s="4" t="n"/>
-      <c r="G103" s="5">
-        <f>IF(P103="","",DATEDIF(P103,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P103,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H103" s="5">
-        <f>IF(I103="","",DATEDIF(I103,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I103" s="6" t="n"/>
-      <c r="J103" s="4" t="n"/>
+        <f>IF(Q103="","",DATEDIF(Q103,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q103,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I103" s="5">
+        <f>IF(J103="","",DATEDIF(J103,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J103" s="6" t="n"/>
       <c r="K103" s="4" t="n"/>
       <c r="L103" s="4" t="n"/>
       <c r="M103" s="4" t="n"/>
       <c r="N103" s="4" t="n"/>
       <c r="O103" s="4" t="n"/>
-      <c r="P103" s="6" t="n"/>
-      <c r="Q103" s="3" t="n"/>
-      <c r="R103" s="4" t="n"/>
+      <c r="P103" s="4" t="n"/>
+      <c r="Q103" s="6" t="n"/>
+      <c r="R103" s="3" t="n"/>
+      <c r="S103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n"/>
@@ -3790,24 +3801,24 @@
         </is>
       </c>
       <c r="F104" s="4" t="n"/>
-      <c r="G104" s="5">
-        <f>IF(P104="","",DATEDIF(P104,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P104,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H104" s="5">
-        <f>IF(I104="","",DATEDIF(I104,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I104" s="6" t="n"/>
-      <c r="J104" s="4" t="n"/>
+        <f>IF(Q104="","",DATEDIF(Q104,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q104,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I104" s="5">
+        <f>IF(J104="","",DATEDIF(J104,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J104" s="6" t="n"/>
       <c r="K104" s="4" t="n"/>
       <c r="L104" s="4" t="n"/>
       <c r="M104" s="4" t="n"/>
       <c r="N104" s="4" t="n"/>
       <c r="O104" s="4" t="n"/>
-      <c r="P104" s="6" t="n"/>
-      <c r="Q104" s="3" t="n"/>
-      <c r="R104" s="4" t="n"/>
+      <c r="P104" s="4" t="n"/>
+      <c r="Q104" s="6" t="n"/>
+      <c r="R104" s="3" t="n"/>
+      <c r="S104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n"/>
@@ -3820,24 +3831,24 @@
         </is>
       </c>
       <c r="F105" s="4" t="n"/>
-      <c r="G105" s="5">
-        <f>IF(P105="","",DATEDIF(P105,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P105,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H105" s="5">
-        <f>IF(I105="","",DATEDIF(I105,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I105" s="6" t="n"/>
-      <c r="J105" s="4" t="n"/>
+        <f>IF(Q105="","",DATEDIF(Q105,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q105,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I105" s="5">
+        <f>IF(J105="","",DATEDIF(J105,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J105" s="6" t="n"/>
       <c r="K105" s="4" t="n"/>
       <c r="L105" s="4" t="n"/>
       <c r="M105" s="4" t="n"/>
       <c r="N105" s="4" t="n"/>
       <c r="O105" s="4" t="n"/>
-      <c r="P105" s="6" t="n"/>
-      <c r="Q105" s="3" t="n"/>
-      <c r="R105" s="4" t="n"/>
+      <c r="P105" s="4" t="n"/>
+      <c r="Q105" s="6" t="n"/>
+      <c r="R105" s="3" t="n"/>
+      <c r="S105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n"/>
@@ -3850,24 +3861,24 @@
         </is>
       </c>
       <c r="F106" s="4" t="n"/>
-      <c r="G106" s="5">
-        <f>IF(P106="","",DATEDIF(P106,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P106,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H106" s="5">
-        <f>IF(I106="","",DATEDIF(I106,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I106" s="6" t="n"/>
-      <c r="J106" s="4" t="n"/>
+        <f>IF(Q106="","",DATEDIF(Q106,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q106,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I106" s="5">
+        <f>IF(J106="","",DATEDIF(J106,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J106" s="6" t="n"/>
       <c r="K106" s="4" t="n"/>
       <c r="L106" s="4" t="n"/>
       <c r="M106" s="4" t="n"/>
       <c r="N106" s="4" t="n"/>
       <c r="O106" s="4" t="n"/>
-      <c r="P106" s="6" t="n"/>
-      <c r="Q106" s="3" t="n"/>
-      <c r="R106" s="4" t="n"/>
+      <c r="P106" s="4" t="n"/>
+      <c r="Q106" s="6" t="n"/>
+      <c r="R106" s="3" t="n"/>
+      <c r="S106" s="4" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n"/>
@@ -3880,24 +3891,24 @@
         </is>
       </c>
       <c r="F107" s="4" t="n"/>
-      <c r="G107" s="5">
-        <f>IF(P107="","",DATEDIF(P107,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P107,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H107" s="5">
-        <f>IF(I107="","",DATEDIF(I107,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I107" s="6" t="n"/>
-      <c r="J107" s="4" t="n"/>
+        <f>IF(Q107="","",DATEDIF(Q107,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q107,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I107" s="5">
+        <f>IF(J107="","",DATEDIF(J107,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J107" s="6" t="n"/>
       <c r="K107" s="4" t="n"/>
       <c r="L107" s="4" t="n"/>
       <c r="M107" s="4" t="n"/>
       <c r="N107" s="4" t="n"/>
       <c r="O107" s="4" t="n"/>
-      <c r="P107" s="6" t="n"/>
-      <c r="Q107" s="3" t="n"/>
-      <c r="R107" s="4" t="n"/>
+      <c r="P107" s="4" t="n"/>
+      <c r="Q107" s="6" t="n"/>
+      <c r="R107" s="3" t="n"/>
+      <c r="S107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n"/>
@@ -3910,24 +3921,24 @@
         </is>
       </c>
       <c r="F108" s="4" t="n"/>
-      <c r="G108" s="5">
-        <f>IF(P108="","",DATEDIF(P108,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P108,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H108" s="5">
-        <f>IF(I108="","",DATEDIF(I108,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I108" s="6" t="n"/>
-      <c r="J108" s="4" t="n"/>
+        <f>IF(Q108="","",DATEDIF(Q108,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q108,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I108" s="5">
+        <f>IF(J108="","",DATEDIF(J108,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J108" s="6" t="n"/>
       <c r="K108" s="4" t="n"/>
       <c r="L108" s="4" t="n"/>
       <c r="M108" s="4" t="n"/>
       <c r="N108" s="4" t="n"/>
       <c r="O108" s="4" t="n"/>
-      <c r="P108" s="6" t="n"/>
-      <c r="Q108" s="3" t="n"/>
-      <c r="R108" s="4" t="n"/>
+      <c r="P108" s="4" t="n"/>
+      <c r="Q108" s="6" t="n"/>
+      <c r="R108" s="3" t="n"/>
+      <c r="S108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n"/>
@@ -3940,24 +3951,24 @@
         </is>
       </c>
       <c r="F109" s="4" t="n"/>
-      <c r="G109" s="5">
-        <f>IF(P109="","",DATEDIF(P109,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P109,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H109" s="5">
-        <f>IF(I109="","",DATEDIF(I109,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I109" s="6" t="n"/>
-      <c r="J109" s="4" t="n"/>
+        <f>IF(Q109="","",DATEDIF(Q109,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q109,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I109" s="5">
+        <f>IF(J109="","",DATEDIF(J109,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J109" s="6" t="n"/>
       <c r="K109" s="4" t="n"/>
       <c r="L109" s="4" t="n"/>
       <c r="M109" s="4" t="n"/>
       <c r="N109" s="4" t="n"/>
       <c r="O109" s="4" t="n"/>
-      <c r="P109" s="6" t="n"/>
-      <c r="Q109" s="3" t="n"/>
-      <c r="R109" s="4" t="n"/>
+      <c r="P109" s="4" t="n"/>
+      <c r="Q109" s="6" t="n"/>
+      <c r="R109" s="3" t="n"/>
+      <c r="S109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n"/>
@@ -3970,24 +3981,24 @@
         </is>
       </c>
       <c r="F110" s="4" t="n"/>
-      <c r="G110" s="5">
-        <f>IF(P110="","",DATEDIF(P110,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P110,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H110" s="5">
-        <f>IF(I110="","",DATEDIF(I110,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I110" s="6" t="n"/>
-      <c r="J110" s="4" t="n"/>
+        <f>IF(Q110="","",DATEDIF(Q110,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q110,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I110" s="5">
+        <f>IF(J110="","",DATEDIF(J110,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J110" s="6" t="n"/>
       <c r="K110" s="4" t="n"/>
       <c r="L110" s="4" t="n"/>
       <c r="M110" s="4" t="n"/>
       <c r="N110" s="4" t="n"/>
       <c r="O110" s="4" t="n"/>
-      <c r="P110" s="6" t="n"/>
-      <c r="Q110" s="3" t="n"/>
-      <c r="R110" s="4" t="n"/>
+      <c r="P110" s="4" t="n"/>
+      <c r="Q110" s="6" t="n"/>
+      <c r="R110" s="3" t="n"/>
+      <c r="S110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n"/>
@@ -4000,24 +4011,24 @@
         </is>
       </c>
       <c r="F111" s="4" t="n"/>
-      <c r="G111" s="5">
-        <f>IF(P111="","",DATEDIF(P111,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P111,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H111" s="5">
-        <f>IF(I111="","",DATEDIF(I111,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I111" s="6" t="n"/>
-      <c r="J111" s="4" t="n"/>
+        <f>IF(Q111="","",DATEDIF(Q111,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q111,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I111" s="5">
+        <f>IF(J111="","",DATEDIF(J111,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J111" s="6" t="n"/>
       <c r="K111" s="4" t="n"/>
       <c r="L111" s="4" t="n"/>
       <c r="M111" s="4" t="n"/>
       <c r="N111" s="4" t="n"/>
       <c r="O111" s="4" t="n"/>
-      <c r="P111" s="6" t="n"/>
-      <c r="Q111" s="3" t="n"/>
-      <c r="R111" s="4" t="n"/>
+      <c r="P111" s="4" t="n"/>
+      <c r="Q111" s="6" t="n"/>
+      <c r="R111" s="3" t="n"/>
+      <c r="S111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n"/>
@@ -4030,24 +4041,24 @@
         </is>
       </c>
       <c r="F112" s="4" t="n"/>
-      <c r="G112" s="5">
-        <f>IF(P112="","",DATEDIF(P112,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P112,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H112" s="5">
-        <f>IF(I112="","",DATEDIF(I112,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I112" s="6" t="n"/>
-      <c r="J112" s="4" t="n"/>
+        <f>IF(Q112="","",DATEDIF(Q112,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q112,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I112" s="5">
+        <f>IF(J112="","",DATEDIF(J112,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J112" s="6" t="n"/>
       <c r="K112" s="4" t="n"/>
       <c r="L112" s="4" t="n"/>
       <c r="M112" s="4" t="n"/>
       <c r="N112" s="4" t="n"/>
       <c r="O112" s="4" t="n"/>
-      <c r="P112" s="6" t="n"/>
-      <c r="Q112" s="3" t="n"/>
-      <c r="R112" s="4" t="n"/>
+      <c r="P112" s="4" t="n"/>
+      <c r="Q112" s="6" t="n"/>
+      <c r="R112" s="3" t="n"/>
+      <c r="S112" s="4" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n"/>
@@ -4060,24 +4071,24 @@
         </is>
       </c>
       <c r="F113" s="4" t="n"/>
-      <c r="G113" s="5">
-        <f>IF(P113="","",DATEDIF(P113,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P113,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H113" s="5">
-        <f>IF(I113="","",DATEDIF(I113,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I113" s="6" t="n"/>
-      <c r="J113" s="4" t="n"/>
+        <f>IF(Q113="","",DATEDIF(Q113,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q113,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I113" s="5">
+        <f>IF(J113="","",DATEDIF(J113,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J113" s="6" t="n"/>
       <c r="K113" s="4" t="n"/>
       <c r="L113" s="4" t="n"/>
       <c r="M113" s="4" t="n"/>
       <c r="N113" s="4" t="n"/>
       <c r="O113" s="4" t="n"/>
-      <c r="P113" s="6" t="n"/>
-      <c r="Q113" s="3" t="n"/>
-      <c r="R113" s="4" t="n"/>
+      <c r="P113" s="4" t="n"/>
+      <c r="Q113" s="6" t="n"/>
+      <c r="R113" s="3" t="n"/>
+      <c r="S113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n"/>
@@ -4090,24 +4101,24 @@
         </is>
       </c>
       <c r="F114" s="4" t="n"/>
-      <c r="G114" s="5">
-        <f>IF(P114="","",DATEDIF(P114,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P114,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H114" s="5">
-        <f>IF(I114="","",DATEDIF(I114,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I114" s="6" t="n"/>
-      <c r="J114" s="4" t="n"/>
+        <f>IF(Q114="","",DATEDIF(Q114,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q114,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I114" s="5">
+        <f>IF(J114="","",DATEDIF(J114,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J114" s="6" t="n"/>
       <c r="K114" s="4" t="n"/>
       <c r="L114" s="4" t="n"/>
       <c r="M114" s="4" t="n"/>
       <c r="N114" s="4" t="n"/>
       <c r="O114" s="4" t="n"/>
-      <c r="P114" s="6" t="n"/>
-      <c r="Q114" s="3" t="n"/>
-      <c r="R114" s="4" t="n"/>
+      <c r="P114" s="4" t="n"/>
+      <c r="Q114" s="6" t="n"/>
+      <c r="R114" s="3" t="n"/>
+      <c r="S114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n"/>
@@ -4120,24 +4131,24 @@
         </is>
       </c>
       <c r="F115" s="4" t="n"/>
-      <c r="G115" s="5">
-        <f>IF(P115="","",DATEDIF(P115,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P115,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H115" s="5">
-        <f>IF(I115="","",DATEDIF(I115,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I115" s="6" t="n"/>
-      <c r="J115" s="4" t="n"/>
+        <f>IF(Q115="","",DATEDIF(Q115,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q115,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I115" s="5">
+        <f>IF(J115="","",DATEDIF(J115,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J115" s="6" t="n"/>
       <c r="K115" s="4" t="n"/>
       <c r="L115" s="4" t="n"/>
       <c r="M115" s="4" t="n"/>
       <c r="N115" s="4" t="n"/>
       <c r="O115" s="4" t="n"/>
-      <c r="P115" s="6" t="n"/>
-      <c r="Q115" s="3" t="n"/>
-      <c r="R115" s="4" t="n"/>
+      <c r="P115" s="4" t="n"/>
+      <c r="Q115" s="6" t="n"/>
+      <c r="R115" s="3" t="n"/>
+      <c r="S115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n"/>
@@ -4150,24 +4161,24 @@
         </is>
       </c>
       <c r="F116" s="4" t="n"/>
-      <c r="G116" s="5">
-        <f>IF(P116="","",DATEDIF(P116,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P116,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H116" s="5">
-        <f>IF(I116="","",DATEDIF(I116,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I116" s="6" t="n"/>
-      <c r="J116" s="4" t="n"/>
+        <f>IF(Q116="","",DATEDIF(Q116,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q116,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I116" s="5">
+        <f>IF(J116="","",DATEDIF(J116,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J116" s="6" t="n"/>
       <c r="K116" s="4" t="n"/>
       <c r="L116" s="4" t="n"/>
       <c r="M116" s="4" t="n"/>
       <c r="N116" s="4" t="n"/>
       <c r="O116" s="4" t="n"/>
-      <c r="P116" s="6" t="n"/>
-      <c r="Q116" s="3" t="n"/>
-      <c r="R116" s="4" t="n"/>
+      <c r="P116" s="4" t="n"/>
+      <c r="Q116" s="6" t="n"/>
+      <c r="R116" s="3" t="n"/>
+      <c r="S116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n"/>
@@ -4180,24 +4191,24 @@
         </is>
       </c>
       <c r="F117" s="4" t="n"/>
-      <c r="G117" s="5">
-        <f>IF(P117="","",DATEDIF(P117,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P117,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H117" s="5">
-        <f>IF(I117="","",DATEDIF(I117,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I117" s="6" t="n"/>
-      <c r="J117" s="4" t="n"/>
+        <f>IF(Q117="","",DATEDIF(Q117,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q117,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I117" s="5">
+        <f>IF(J117="","",DATEDIF(J117,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J117" s="6" t="n"/>
       <c r="K117" s="4" t="n"/>
       <c r="L117" s="4" t="n"/>
       <c r="M117" s="4" t="n"/>
       <c r="N117" s="4" t="n"/>
       <c r="O117" s="4" t="n"/>
-      <c r="P117" s="6" t="n"/>
-      <c r="Q117" s="3" t="n"/>
-      <c r="R117" s="4" t="n"/>
+      <c r="P117" s="4" t="n"/>
+      <c r="Q117" s="6" t="n"/>
+      <c r="R117" s="3" t="n"/>
+      <c r="S117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n"/>
@@ -4210,24 +4221,24 @@
         </is>
       </c>
       <c r="F118" s="4" t="n"/>
-      <c r="G118" s="5">
-        <f>IF(P118="","",DATEDIF(P118,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P118,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H118" s="5">
-        <f>IF(I118="","",DATEDIF(I118,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I118" s="6" t="n"/>
-      <c r="J118" s="4" t="n"/>
+        <f>IF(Q118="","",DATEDIF(Q118,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q118,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I118" s="5">
+        <f>IF(J118="","",DATEDIF(J118,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J118" s="6" t="n"/>
       <c r="K118" s="4" t="n"/>
       <c r="L118" s="4" t="n"/>
       <c r="M118" s="4" t="n"/>
       <c r="N118" s="4" t="n"/>
       <c r="O118" s="4" t="n"/>
-      <c r="P118" s="6" t="n"/>
-      <c r="Q118" s="3" t="n"/>
-      <c r="R118" s="4" t="n"/>
+      <c r="P118" s="4" t="n"/>
+      <c r="Q118" s="6" t="n"/>
+      <c r="R118" s="3" t="n"/>
+      <c r="S118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n"/>
@@ -4240,24 +4251,24 @@
         </is>
       </c>
       <c r="F119" s="4" t="n"/>
-      <c r="G119" s="5">
-        <f>IF(P119="","",DATEDIF(P119,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P119,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H119" s="5">
-        <f>IF(I119="","",DATEDIF(I119,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I119" s="6" t="n"/>
-      <c r="J119" s="4" t="n"/>
+        <f>IF(Q119="","",DATEDIF(Q119,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q119,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I119" s="5">
+        <f>IF(J119="","",DATEDIF(J119,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J119" s="6" t="n"/>
       <c r="K119" s="4" t="n"/>
       <c r="L119" s="4" t="n"/>
       <c r="M119" s="4" t="n"/>
       <c r="N119" s="4" t="n"/>
       <c r="O119" s="4" t="n"/>
-      <c r="P119" s="6" t="n"/>
-      <c r="Q119" s="3" t="n"/>
-      <c r="R119" s="4" t="n"/>
+      <c r="P119" s="4" t="n"/>
+      <c r="Q119" s="6" t="n"/>
+      <c r="R119" s="3" t="n"/>
+      <c r="S119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n"/>
@@ -4270,24 +4281,24 @@
         </is>
       </c>
       <c r="F120" s="4" t="n"/>
-      <c r="G120" s="5">
-        <f>IF(P120="","",DATEDIF(P120,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P120,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H120" s="5">
-        <f>IF(I120="","",DATEDIF(I120,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I120" s="6" t="n"/>
-      <c r="J120" s="4" t="n"/>
+        <f>IF(Q120="","",DATEDIF(Q120,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q120,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I120" s="5">
+        <f>IF(J120="","",DATEDIF(J120,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J120" s="6" t="n"/>
       <c r="K120" s="4" t="n"/>
       <c r="L120" s="4" t="n"/>
       <c r="M120" s="4" t="n"/>
       <c r="N120" s="4" t="n"/>
       <c r="O120" s="4" t="n"/>
-      <c r="P120" s="6" t="n"/>
-      <c r="Q120" s="3" t="n"/>
-      <c r="R120" s="4" t="n"/>
+      <c r="P120" s="4" t="n"/>
+      <c r="Q120" s="6" t="n"/>
+      <c r="R120" s="3" t="n"/>
+      <c r="S120" s="4" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n"/>
@@ -4300,24 +4311,24 @@
         </is>
       </c>
       <c r="F121" s="4" t="n"/>
-      <c r="G121" s="5">
-        <f>IF(P121="","",DATEDIF(P121,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P121,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H121" s="5">
-        <f>IF(I121="","",DATEDIF(I121,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I121" s="6" t="n"/>
-      <c r="J121" s="4" t="n"/>
+        <f>IF(Q121="","",DATEDIF(Q121,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q121,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I121" s="5">
+        <f>IF(J121="","",DATEDIF(J121,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J121" s="6" t="n"/>
       <c r="K121" s="4" t="n"/>
       <c r="L121" s="4" t="n"/>
       <c r="M121" s="4" t="n"/>
       <c r="N121" s="4" t="n"/>
       <c r="O121" s="4" t="n"/>
-      <c r="P121" s="6" t="n"/>
-      <c r="Q121" s="3" t="n"/>
-      <c r="R121" s="4" t="n"/>
+      <c r="P121" s="4" t="n"/>
+      <c r="Q121" s="6" t="n"/>
+      <c r="R121" s="3" t="n"/>
+      <c r="S121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n"/>
@@ -4330,24 +4341,24 @@
         </is>
       </c>
       <c r="F122" s="4" t="n"/>
-      <c r="G122" s="5">
-        <f>IF(P122="","",DATEDIF(P122,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P122,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H122" s="5">
-        <f>IF(I122="","",DATEDIF(I122,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I122" s="6" t="n"/>
-      <c r="J122" s="4" t="n"/>
+        <f>IF(Q122="","",DATEDIF(Q122,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q122,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I122" s="5">
+        <f>IF(J122="","",DATEDIF(J122,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J122" s="6" t="n"/>
       <c r="K122" s="4" t="n"/>
       <c r="L122" s="4" t="n"/>
       <c r="M122" s="4" t="n"/>
       <c r="N122" s="4" t="n"/>
       <c r="O122" s="4" t="n"/>
-      <c r="P122" s="6" t="n"/>
-      <c r="Q122" s="3" t="n"/>
-      <c r="R122" s="4" t="n"/>
+      <c r="P122" s="4" t="n"/>
+      <c r="Q122" s="6" t="n"/>
+      <c r="R122" s="3" t="n"/>
+      <c r="S122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n"/>
@@ -4360,24 +4371,24 @@
         </is>
       </c>
       <c r="F123" s="4" t="n"/>
-      <c r="G123" s="5">
-        <f>IF(P123="","",DATEDIF(P123,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P123,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H123" s="5">
-        <f>IF(I123="","",DATEDIF(I123,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I123" s="6" t="n"/>
-      <c r="J123" s="4" t="n"/>
+        <f>IF(Q123="","",DATEDIF(Q123,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q123,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I123" s="5">
+        <f>IF(J123="","",DATEDIF(J123,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J123" s="6" t="n"/>
       <c r="K123" s="4" t="n"/>
       <c r="L123" s="4" t="n"/>
       <c r="M123" s="4" t="n"/>
       <c r="N123" s="4" t="n"/>
       <c r="O123" s="4" t="n"/>
-      <c r="P123" s="6" t="n"/>
-      <c r="Q123" s="3" t="n"/>
-      <c r="R123" s="4" t="n"/>
+      <c r="P123" s="4" t="n"/>
+      <c r="Q123" s="6" t="n"/>
+      <c r="R123" s="3" t="n"/>
+      <c r="S123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n"/>
@@ -4390,24 +4401,24 @@
         </is>
       </c>
       <c r="F124" s="4" t="n"/>
-      <c r="G124" s="5">
-        <f>IF(P124="","",DATEDIF(P124,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P124,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H124" s="5">
-        <f>IF(I124="","",DATEDIF(I124,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I124" s="6" t="n"/>
-      <c r="J124" s="4" t="n"/>
+        <f>IF(Q124="","",DATEDIF(Q124,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q124,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I124" s="5">
+        <f>IF(J124="","",DATEDIF(J124,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J124" s="6" t="n"/>
       <c r="K124" s="4" t="n"/>
       <c r="L124" s="4" t="n"/>
       <c r="M124" s="4" t="n"/>
       <c r="N124" s="4" t="n"/>
       <c r="O124" s="4" t="n"/>
-      <c r="P124" s="6" t="n"/>
-      <c r="Q124" s="3" t="n"/>
-      <c r="R124" s="4" t="n"/>
+      <c r="P124" s="4" t="n"/>
+      <c r="Q124" s="6" t="n"/>
+      <c r="R124" s="3" t="n"/>
+      <c r="S124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n"/>
@@ -4420,24 +4431,24 @@
         </is>
       </c>
       <c r="F125" s="4" t="n"/>
-      <c r="G125" s="5">
-        <f>IF(P125="","",DATEDIF(P125,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P125,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H125" s="5">
-        <f>IF(I125="","",DATEDIF(I125,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I125" s="6" t="n"/>
-      <c r="J125" s="4" t="n"/>
+        <f>IF(Q125="","",DATEDIF(Q125,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q125,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I125" s="5">
+        <f>IF(J125="","",DATEDIF(J125,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J125" s="6" t="n"/>
       <c r="K125" s="4" t="n"/>
       <c r="L125" s="4" t="n"/>
       <c r="M125" s="4" t="n"/>
       <c r="N125" s="4" t="n"/>
       <c r="O125" s="4" t="n"/>
-      <c r="P125" s="6" t="n"/>
-      <c r="Q125" s="3" t="n"/>
-      <c r="R125" s="4" t="n"/>
+      <c r="P125" s="4" t="n"/>
+      <c r="Q125" s="6" t="n"/>
+      <c r="R125" s="3" t="n"/>
+      <c r="S125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n"/>
@@ -4450,24 +4461,24 @@
         </is>
       </c>
       <c r="F126" s="4" t="n"/>
-      <c r="G126" s="5">
-        <f>IF(P126="","",DATEDIF(P126,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P126,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H126" s="5">
-        <f>IF(I126="","",DATEDIF(I126,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I126" s="6" t="n"/>
-      <c r="J126" s="4" t="n"/>
+        <f>IF(Q126="","",DATEDIF(Q126,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q126,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I126" s="5">
+        <f>IF(J126="","",DATEDIF(J126,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J126" s="6" t="n"/>
       <c r="K126" s="4" t="n"/>
       <c r="L126" s="4" t="n"/>
       <c r="M126" s="4" t="n"/>
       <c r="N126" s="4" t="n"/>
       <c r="O126" s="4" t="n"/>
-      <c r="P126" s="6" t="n"/>
-      <c r="Q126" s="3" t="n"/>
-      <c r="R126" s="4" t="n"/>
+      <c r="P126" s="4" t="n"/>
+      <c r="Q126" s="6" t="n"/>
+      <c r="R126" s="3" t="n"/>
+      <c r="S126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n"/>
@@ -4480,24 +4491,24 @@
         </is>
       </c>
       <c r="F127" s="4" t="n"/>
-      <c r="G127" s="5">
-        <f>IF(P127="","",DATEDIF(P127,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P127,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H127" s="5">
-        <f>IF(I127="","",DATEDIF(I127,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I127" s="6" t="n"/>
-      <c r="J127" s="4" t="n"/>
+        <f>IF(Q127="","",DATEDIF(Q127,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q127,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I127" s="5">
+        <f>IF(J127="","",DATEDIF(J127,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J127" s="6" t="n"/>
       <c r="K127" s="4" t="n"/>
       <c r="L127" s="4" t="n"/>
       <c r="M127" s="4" t="n"/>
       <c r="N127" s="4" t="n"/>
       <c r="O127" s="4" t="n"/>
-      <c r="P127" s="6" t="n"/>
-      <c r="Q127" s="3" t="n"/>
-      <c r="R127" s="4" t="n"/>
+      <c r="P127" s="4" t="n"/>
+      <c r="Q127" s="6" t="n"/>
+      <c r="R127" s="3" t="n"/>
+      <c r="S127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n"/>
@@ -4510,24 +4521,24 @@
         </is>
       </c>
       <c r="F128" s="4" t="n"/>
-      <c r="G128" s="5">
-        <f>IF(P128="","",DATEDIF(P128,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P128,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H128" s="5">
-        <f>IF(I128="","",DATEDIF(I128,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I128" s="6" t="n"/>
-      <c r="J128" s="4" t="n"/>
+        <f>IF(Q128="","",DATEDIF(Q128,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q128,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I128" s="5">
+        <f>IF(J128="","",DATEDIF(J128,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J128" s="6" t="n"/>
       <c r="K128" s="4" t="n"/>
       <c r="L128" s="4" t="n"/>
       <c r="M128" s="4" t="n"/>
       <c r="N128" s="4" t="n"/>
       <c r="O128" s="4" t="n"/>
-      <c r="P128" s="6" t="n"/>
-      <c r="Q128" s="3" t="n"/>
-      <c r="R128" s="4" t="n"/>
+      <c r="P128" s="4" t="n"/>
+      <c r="Q128" s="6" t="n"/>
+      <c r="R128" s="3" t="n"/>
+      <c r="S128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n"/>
@@ -4540,24 +4551,24 @@
         </is>
       </c>
       <c r="F129" s="4" t="n"/>
-      <c r="G129" s="5">
-        <f>IF(P129="","",DATEDIF(P129,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P129,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H129" s="5">
-        <f>IF(I129="","",DATEDIF(I129,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I129" s="6" t="n"/>
-      <c r="J129" s="4" t="n"/>
+        <f>IF(Q129="","",DATEDIF(Q129,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q129,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I129" s="5">
+        <f>IF(J129="","",DATEDIF(J129,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J129" s="6" t="n"/>
       <c r="K129" s="4" t="n"/>
       <c r="L129" s="4" t="n"/>
       <c r="M129" s="4" t="n"/>
       <c r="N129" s="4" t="n"/>
       <c r="O129" s="4" t="n"/>
-      <c r="P129" s="6" t="n"/>
-      <c r="Q129" s="3" t="n"/>
-      <c r="R129" s="4" t="n"/>
+      <c r="P129" s="4" t="n"/>
+      <c r="Q129" s="6" t="n"/>
+      <c r="R129" s="3" t="n"/>
+      <c r="S129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n"/>
@@ -4570,24 +4581,24 @@
         </is>
       </c>
       <c r="F130" s="4" t="n"/>
-      <c r="G130" s="5">
-        <f>IF(P130="","",DATEDIF(P130,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P130,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H130" s="5">
-        <f>IF(I130="","",DATEDIF(I130,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I130" s="6" t="n"/>
-      <c r="J130" s="4" t="n"/>
+        <f>IF(Q130="","",DATEDIF(Q130,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q130,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I130" s="5">
+        <f>IF(J130="","",DATEDIF(J130,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J130" s="6" t="n"/>
       <c r="K130" s="4" t="n"/>
       <c r="L130" s="4" t="n"/>
       <c r="M130" s="4" t="n"/>
       <c r="N130" s="4" t="n"/>
       <c r="O130" s="4" t="n"/>
-      <c r="P130" s="6" t="n"/>
-      <c r="Q130" s="3" t="n"/>
-      <c r="R130" s="4" t="n"/>
+      <c r="P130" s="4" t="n"/>
+      <c r="Q130" s="6" t="n"/>
+      <c r="R130" s="3" t="n"/>
+      <c r="S130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n"/>
@@ -4600,24 +4611,24 @@
         </is>
       </c>
       <c r="F131" s="4" t="n"/>
-      <c r="G131" s="5">
-        <f>IF(P131="","",DATEDIF(P131,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P131,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H131" s="5">
-        <f>IF(I131="","",DATEDIF(I131,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I131" s="6" t="n"/>
-      <c r="J131" s="4" t="n"/>
+        <f>IF(Q131="","",DATEDIF(Q131,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q131,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I131" s="5">
+        <f>IF(J131="","",DATEDIF(J131,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J131" s="6" t="n"/>
       <c r="K131" s="4" t="n"/>
       <c r="L131" s="4" t="n"/>
       <c r="M131" s="4" t="n"/>
       <c r="N131" s="4" t="n"/>
       <c r="O131" s="4" t="n"/>
-      <c r="P131" s="6" t="n"/>
-      <c r="Q131" s="3" t="n"/>
-      <c r="R131" s="4" t="n"/>
+      <c r="P131" s="4" t="n"/>
+      <c r="Q131" s="6" t="n"/>
+      <c r="R131" s="3" t="n"/>
+      <c r="S131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n"/>
@@ -4630,24 +4641,24 @@
         </is>
       </c>
       <c r="F132" s="4" t="n"/>
-      <c r="G132" s="5">
-        <f>IF(P132="","",DATEDIF(P132,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P132,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H132" s="5">
-        <f>IF(I132="","",DATEDIF(I132,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I132" s="6" t="n"/>
-      <c r="J132" s="4" t="n"/>
+        <f>IF(Q132="","",DATEDIF(Q132,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q132,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I132" s="5">
+        <f>IF(J132="","",DATEDIF(J132,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J132" s="6" t="n"/>
       <c r="K132" s="4" t="n"/>
       <c r="L132" s="4" t="n"/>
       <c r="M132" s="4" t="n"/>
       <c r="N132" s="4" t="n"/>
       <c r="O132" s="4" t="n"/>
-      <c r="P132" s="6" t="n"/>
-      <c r="Q132" s="3" t="n"/>
-      <c r="R132" s="4" t="n"/>
+      <c r="P132" s="4" t="n"/>
+      <c r="Q132" s="6" t="n"/>
+      <c r="R132" s="3" t="n"/>
+      <c r="S132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n"/>
@@ -4660,24 +4671,24 @@
         </is>
       </c>
       <c r="F133" s="4" t="n"/>
-      <c r="G133" s="5">
-        <f>IF(P133="","",DATEDIF(P133,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P133,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H133" s="5">
-        <f>IF(I133="","",DATEDIF(I133,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I133" s="6" t="n"/>
-      <c r="J133" s="4" t="n"/>
+        <f>IF(Q133="","",DATEDIF(Q133,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q133,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I133" s="5">
+        <f>IF(J133="","",DATEDIF(J133,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J133" s="6" t="n"/>
       <c r="K133" s="4" t="n"/>
       <c r="L133" s="4" t="n"/>
       <c r="M133" s="4" t="n"/>
       <c r="N133" s="4" t="n"/>
       <c r="O133" s="4" t="n"/>
-      <c r="P133" s="6" t="n"/>
-      <c r="Q133" s="3" t="n"/>
-      <c r="R133" s="4" t="n"/>
+      <c r="P133" s="4" t="n"/>
+      <c r="Q133" s="6" t="n"/>
+      <c r="R133" s="3" t="n"/>
+      <c r="S133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n"/>
@@ -4690,24 +4701,24 @@
         </is>
       </c>
       <c r="F134" s="4" t="n"/>
-      <c r="G134" s="5">
-        <f>IF(P134="","",DATEDIF(P134,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P134,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H134" s="5">
-        <f>IF(I134="","",DATEDIF(I134,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I134" s="6" t="n"/>
-      <c r="J134" s="4" t="n"/>
+        <f>IF(Q134="","",DATEDIF(Q134,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q134,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I134" s="5">
+        <f>IF(J134="","",DATEDIF(J134,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J134" s="6" t="n"/>
       <c r="K134" s="4" t="n"/>
       <c r="L134" s="4" t="n"/>
       <c r="M134" s="4" t="n"/>
       <c r="N134" s="4" t="n"/>
       <c r="O134" s="4" t="n"/>
-      <c r="P134" s="6" t="n"/>
-      <c r="Q134" s="3" t="n"/>
-      <c r="R134" s="4" t="n"/>
+      <c r="P134" s="4" t="n"/>
+      <c r="Q134" s="6" t="n"/>
+      <c r="R134" s="3" t="n"/>
+      <c r="S134" s="4" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n"/>
@@ -4720,24 +4731,24 @@
         </is>
       </c>
       <c r="F135" s="4" t="n"/>
-      <c r="G135" s="5">
-        <f>IF(P135="","",DATEDIF(P135,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P135,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H135" s="5">
-        <f>IF(I135="","",DATEDIF(I135,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I135" s="6" t="n"/>
-      <c r="J135" s="4" t="n"/>
+        <f>IF(Q135="","",DATEDIF(Q135,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q135,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I135" s="5">
+        <f>IF(J135="","",DATEDIF(J135,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J135" s="6" t="n"/>
       <c r="K135" s="4" t="n"/>
       <c r="L135" s="4" t="n"/>
       <c r="M135" s="4" t="n"/>
       <c r="N135" s="4" t="n"/>
       <c r="O135" s="4" t="n"/>
-      <c r="P135" s="6" t="n"/>
-      <c r="Q135" s="3" t="n"/>
-      <c r="R135" s="4" t="n"/>
+      <c r="P135" s="4" t="n"/>
+      <c r="Q135" s="6" t="n"/>
+      <c r="R135" s="3" t="n"/>
+      <c r="S135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n"/>
@@ -4750,24 +4761,24 @@
         </is>
       </c>
       <c r="F136" s="4" t="n"/>
-      <c r="G136" s="5">
-        <f>IF(P136="","",DATEDIF(P136,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P136,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H136" s="5">
-        <f>IF(I136="","",DATEDIF(I136,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I136" s="6" t="n"/>
-      <c r="J136" s="4" t="n"/>
+        <f>IF(Q136="","",DATEDIF(Q136,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q136,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I136" s="5">
+        <f>IF(J136="","",DATEDIF(J136,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J136" s="6" t="n"/>
       <c r="K136" s="4" t="n"/>
       <c r="L136" s="4" t="n"/>
       <c r="M136" s="4" t="n"/>
       <c r="N136" s="4" t="n"/>
       <c r="O136" s="4" t="n"/>
-      <c r="P136" s="6" t="n"/>
-      <c r="Q136" s="3" t="n"/>
-      <c r="R136" s="4" t="n"/>
+      <c r="P136" s="4" t="n"/>
+      <c r="Q136" s="6" t="n"/>
+      <c r="R136" s="3" t="n"/>
+      <c r="S136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n"/>
@@ -4780,24 +4791,24 @@
         </is>
       </c>
       <c r="F137" s="4" t="n"/>
-      <c r="G137" s="5">
-        <f>IF(P137="","",DATEDIF(P137,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P137,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H137" s="5">
-        <f>IF(I137="","",DATEDIF(I137,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I137" s="6" t="n"/>
-      <c r="J137" s="4" t="n"/>
+        <f>IF(Q137="","",DATEDIF(Q137,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q137,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I137" s="5">
+        <f>IF(J137="","",DATEDIF(J137,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J137" s="6" t="n"/>
       <c r="K137" s="4" t="n"/>
       <c r="L137" s="4" t="n"/>
       <c r="M137" s="4" t="n"/>
       <c r="N137" s="4" t="n"/>
       <c r="O137" s="4" t="n"/>
-      <c r="P137" s="6" t="n"/>
-      <c r="Q137" s="3" t="n"/>
-      <c r="R137" s="4" t="n"/>
+      <c r="P137" s="4" t="n"/>
+      <c r="Q137" s="6" t="n"/>
+      <c r="R137" s="3" t="n"/>
+      <c r="S137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n"/>
@@ -4810,24 +4821,24 @@
         </is>
       </c>
       <c r="F138" s="4" t="n"/>
-      <c r="G138" s="5">
-        <f>IF(P138="","",DATEDIF(P138,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P138,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H138" s="5">
-        <f>IF(I138="","",DATEDIF(I138,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I138" s="6" t="n"/>
-      <c r="J138" s="4" t="n"/>
+        <f>IF(Q138="","",DATEDIF(Q138,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q138,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I138" s="5">
+        <f>IF(J138="","",DATEDIF(J138,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J138" s="6" t="n"/>
       <c r="K138" s="4" t="n"/>
       <c r="L138" s="4" t="n"/>
       <c r="M138" s="4" t="n"/>
       <c r="N138" s="4" t="n"/>
       <c r="O138" s="4" t="n"/>
-      <c r="P138" s="6" t="n"/>
-      <c r="Q138" s="3" t="n"/>
-      <c r="R138" s="4" t="n"/>
+      <c r="P138" s="4" t="n"/>
+      <c r="Q138" s="6" t="n"/>
+      <c r="R138" s="3" t="n"/>
+      <c r="S138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n"/>
@@ -4840,24 +4851,24 @@
         </is>
       </c>
       <c r="F139" s="4" t="n"/>
-      <c r="G139" s="5">
-        <f>IF(P139="","",DATEDIF(P139,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P139,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H139" s="5">
-        <f>IF(I139="","",DATEDIF(I139,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I139" s="6" t="n"/>
-      <c r="J139" s="4" t="n"/>
+        <f>IF(Q139="","",DATEDIF(Q139,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q139,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I139" s="5">
+        <f>IF(J139="","",DATEDIF(J139,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J139" s="6" t="n"/>
       <c r="K139" s="4" t="n"/>
       <c r="L139" s="4" t="n"/>
       <c r="M139" s="4" t="n"/>
       <c r="N139" s="4" t="n"/>
       <c r="O139" s="4" t="n"/>
-      <c r="P139" s="6" t="n"/>
-      <c r="Q139" s="3" t="n"/>
-      <c r="R139" s="4" t="n"/>
+      <c r="P139" s="4" t="n"/>
+      <c r="Q139" s="6" t="n"/>
+      <c r="R139" s="3" t="n"/>
+      <c r="S139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n"/>
@@ -4870,24 +4881,24 @@
         </is>
       </c>
       <c r="F140" s="4" t="n"/>
-      <c r="G140" s="5">
-        <f>IF(P140="","",DATEDIF(P140,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P140,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H140" s="5">
-        <f>IF(I140="","",DATEDIF(I140,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I140" s="6" t="n"/>
-      <c r="J140" s="4" t="n"/>
+        <f>IF(Q140="","",DATEDIF(Q140,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q140,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I140" s="5">
+        <f>IF(J140="","",DATEDIF(J140,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J140" s="6" t="n"/>
       <c r="K140" s="4" t="n"/>
       <c r="L140" s="4" t="n"/>
       <c r="M140" s="4" t="n"/>
       <c r="N140" s="4" t="n"/>
       <c r="O140" s="4" t="n"/>
-      <c r="P140" s="6" t="n"/>
-      <c r="Q140" s="3" t="n"/>
-      <c r="R140" s="4" t="n"/>
+      <c r="P140" s="4" t="n"/>
+      <c r="Q140" s="6" t="n"/>
+      <c r="R140" s="3" t="n"/>
+      <c r="S140" s="4" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n"/>
@@ -4900,24 +4911,24 @@
         </is>
       </c>
       <c r="F141" s="4" t="n"/>
-      <c r="G141" s="5">
-        <f>IF(P141="","",DATEDIF(P141,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P141,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H141" s="5">
-        <f>IF(I141="","",DATEDIF(I141,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I141" s="6" t="n"/>
-      <c r="J141" s="4" t="n"/>
+        <f>IF(Q141="","",DATEDIF(Q141,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q141,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I141" s="5">
+        <f>IF(J141="","",DATEDIF(J141,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J141" s="6" t="n"/>
       <c r="K141" s="4" t="n"/>
       <c r="L141" s="4" t="n"/>
       <c r="M141" s="4" t="n"/>
       <c r="N141" s="4" t="n"/>
       <c r="O141" s="4" t="n"/>
-      <c r="P141" s="6" t="n"/>
-      <c r="Q141" s="3" t="n"/>
-      <c r="R141" s="4" t="n"/>
+      <c r="P141" s="4" t="n"/>
+      <c r="Q141" s="6" t="n"/>
+      <c r="R141" s="3" t="n"/>
+      <c r="S141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n"/>
@@ -4930,24 +4941,24 @@
         </is>
       </c>
       <c r="F142" s="4" t="n"/>
-      <c r="G142" s="5">
-        <f>IF(P142="","",DATEDIF(P142,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P142,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H142" s="5">
-        <f>IF(I142="","",DATEDIF(I142,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I142" s="6" t="n"/>
-      <c r="J142" s="4" t="n"/>
+        <f>IF(Q142="","",DATEDIF(Q142,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q142,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I142" s="5">
+        <f>IF(J142="","",DATEDIF(J142,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J142" s="6" t="n"/>
       <c r="K142" s="4" t="n"/>
       <c r="L142" s="4" t="n"/>
       <c r="M142" s="4" t="n"/>
       <c r="N142" s="4" t="n"/>
       <c r="O142" s="4" t="n"/>
-      <c r="P142" s="6" t="n"/>
-      <c r="Q142" s="3" t="n"/>
-      <c r="R142" s="4" t="n"/>
+      <c r="P142" s="4" t="n"/>
+      <c r="Q142" s="6" t="n"/>
+      <c r="R142" s="3" t="n"/>
+      <c r="S142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n"/>
@@ -4960,24 +4971,24 @@
         </is>
       </c>
       <c r="F143" s="4" t="n"/>
-      <c r="G143" s="5">
-        <f>IF(P143="","",DATEDIF(P143,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P143,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H143" s="5">
-        <f>IF(I143="","",DATEDIF(I143,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I143" s="6" t="n"/>
-      <c r="J143" s="4" t="n"/>
+        <f>IF(Q143="","",DATEDIF(Q143,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q143,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I143" s="5">
+        <f>IF(J143="","",DATEDIF(J143,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J143" s="6" t="n"/>
       <c r="K143" s="4" t="n"/>
       <c r="L143" s="4" t="n"/>
       <c r="M143" s="4" t="n"/>
       <c r="N143" s="4" t="n"/>
       <c r="O143" s="4" t="n"/>
-      <c r="P143" s="6" t="n"/>
-      <c r="Q143" s="3" t="n"/>
-      <c r="R143" s="4" t="n"/>
+      <c r="P143" s="4" t="n"/>
+      <c r="Q143" s="6" t="n"/>
+      <c r="R143" s="3" t="n"/>
+      <c r="S143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n"/>
@@ -4990,24 +5001,24 @@
         </is>
       </c>
       <c r="F144" s="4" t="n"/>
-      <c r="G144" s="5">
-        <f>IF(P144="","",DATEDIF(P144,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P144,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H144" s="5">
-        <f>IF(I144="","",DATEDIF(I144,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I144" s="6" t="n"/>
-      <c r="J144" s="4" t="n"/>
+        <f>IF(Q144="","",DATEDIF(Q144,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q144,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I144" s="5">
+        <f>IF(J144="","",DATEDIF(J144,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J144" s="6" t="n"/>
       <c r="K144" s="4" t="n"/>
       <c r="L144" s="4" t="n"/>
       <c r="M144" s="4" t="n"/>
       <c r="N144" s="4" t="n"/>
       <c r="O144" s="4" t="n"/>
-      <c r="P144" s="6" t="n"/>
-      <c r="Q144" s="3" t="n"/>
-      <c r="R144" s="4" t="n"/>
+      <c r="P144" s="4" t="n"/>
+      <c r="Q144" s="6" t="n"/>
+      <c r="R144" s="3" t="n"/>
+      <c r="S144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n"/>
@@ -5020,24 +5031,24 @@
         </is>
       </c>
       <c r="F145" s="4" t="n"/>
-      <c r="G145" s="5">
-        <f>IF(P145="","",DATEDIF(P145,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P145,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H145" s="5">
-        <f>IF(I145="","",DATEDIF(I145,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I145" s="6" t="n"/>
-      <c r="J145" s="4" t="n"/>
+        <f>IF(Q145="","",DATEDIF(Q145,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q145,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I145" s="5">
+        <f>IF(J145="","",DATEDIF(J145,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J145" s="6" t="n"/>
       <c r="K145" s="4" t="n"/>
       <c r="L145" s="4" t="n"/>
       <c r="M145" s="4" t="n"/>
       <c r="N145" s="4" t="n"/>
       <c r="O145" s="4" t="n"/>
-      <c r="P145" s="6" t="n"/>
-      <c r="Q145" s="3" t="n"/>
-      <c r="R145" s="4" t="n"/>
+      <c r="P145" s="4" t="n"/>
+      <c r="Q145" s="6" t="n"/>
+      <c r="R145" s="3" t="n"/>
+      <c r="S145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n"/>
@@ -5050,24 +5061,24 @@
         </is>
       </c>
       <c r="F146" s="4" t="n"/>
-      <c r="G146" s="5">
-        <f>IF(P146="","",DATEDIF(P146,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P146,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H146" s="5">
-        <f>IF(I146="","",DATEDIF(I146,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I146" s="6" t="n"/>
-      <c r="J146" s="4" t="n"/>
+        <f>IF(Q146="","",DATEDIF(Q146,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q146,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I146" s="5">
+        <f>IF(J146="","",DATEDIF(J146,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J146" s="6" t="n"/>
       <c r="K146" s="4" t="n"/>
       <c r="L146" s="4" t="n"/>
       <c r="M146" s="4" t="n"/>
       <c r="N146" s="4" t="n"/>
       <c r="O146" s="4" t="n"/>
-      <c r="P146" s="6" t="n"/>
-      <c r="Q146" s="3" t="n"/>
-      <c r="R146" s="4" t="n"/>
+      <c r="P146" s="4" t="n"/>
+      <c r="Q146" s="6" t="n"/>
+      <c r="R146" s="3" t="n"/>
+      <c r="S146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n"/>
@@ -5080,24 +5091,24 @@
         </is>
       </c>
       <c r="F147" s="4" t="n"/>
-      <c r="G147" s="5">
-        <f>IF(P147="","",DATEDIF(P147,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P147,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H147" s="5">
-        <f>IF(I147="","",DATEDIF(I147,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I147" s="6" t="n"/>
-      <c r="J147" s="4" t="n"/>
+        <f>IF(Q147="","",DATEDIF(Q147,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q147,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I147" s="5">
+        <f>IF(J147="","",DATEDIF(J147,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J147" s="6" t="n"/>
       <c r="K147" s="4" t="n"/>
       <c r="L147" s="4" t="n"/>
       <c r="M147" s="4" t="n"/>
       <c r="N147" s="4" t="n"/>
       <c r="O147" s="4" t="n"/>
-      <c r="P147" s="6" t="n"/>
-      <c r="Q147" s="3" t="n"/>
-      <c r="R147" s="4" t="n"/>
+      <c r="P147" s="4" t="n"/>
+      <c r="Q147" s="6" t="n"/>
+      <c r="R147" s="3" t="n"/>
+      <c r="S147" s="4" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n"/>
@@ -5110,24 +5121,24 @@
         </is>
       </c>
       <c r="F148" s="4" t="n"/>
-      <c r="G148" s="5">
-        <f>IF(P148="","",DATEDIF(P148,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P148,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H148" s="5">
-        <f>IF(I148="","",DATEDIF(I148,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I148" s="6" t="n"/>
-      <c r="J148" s="4" t="n"/>
+        <f>IF(Q148="","",DATEDIF(Q148,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q148,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I148" s="5">
+        <f>IF(J148="","",DATEDIF(J148,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J148" s="6" t="n"/>
       <c r="K148" s="4" t="n"/>
       <c r="L148" s="4" t="n"/>
       <c r="M148" s="4" t="n"/>
       <c r="N148" s="4" t="n"/>
       <c r="O148" s="4" t="n"/>
-      <c r="P148" s="6" t="n"/>
-      <c r="Q148" s="3" t="n"/>
-      <c r="R148" s="4" t="n"/>
+      <c r="P148" s="4" t="n"/>
+      <c r="Q148" s="6" t="n"/>
+      <c r="R148" s="3" t="n"/>
+      <c r="S148" s="4" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n"/>
@@ -5140,24 +5151,24 @@
         </is>
       </c>
       <c r="F149" s="4" t="n"/>
-      <c r="G149" s="5">
-        <f>IF(P149="","",DATEDIF(P149,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P149,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H149" s="5">
-        <f>IF(I149="","",DATEDIF(I149,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I149" s="6" t="n"/>
-      <c r="J149" s="4" t="n"/>
+        <f>IF(Q149="","",DATEDIF(Q149,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q149,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I149" s="5">
+        <f>IF(J149="","",DATEDIF(J149,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J149" s="6" t="n"/>
       <c r="K149" s="4" t="n"/>
       <c r="L149" s="4" t="n"/>
       <c r="M149" s="4" t="n"/>
       <c r="N149" s="4" t="n"/>
       <c r="O149" s="4" t="n"/>
-      <c r="P149" s="6" t="n"/>
-      <c r="Q149" s="3" t="n"/>
-      <c r="R149" s="4" t="n"/>
+      <c r="P149" s="4" t="n"/>
+      <c r="Q149" s="6" t="n"/>
+      <c r="R149" s="3" t="n"/>
+      <c r="S149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n"/>
@@ -5170,24 +5181,24 @@
         </is>
       </c>
       <c r="F150" s="4" t="n"/>
-      <c r="G150" s="5">
-        <f>IF(P150="","",DATEDIF(P150,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P150,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H150" s="5">
-        <f>IF(I150="","",DATEDIF(I150,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I150" s="6" t="n"/>
-      <c r="J150" s="4" t="n"/>
+        <f>IF(Q150="","",DATEDIF(Q150,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q150,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I150" s="5">
+        <f>IF(J150="","",DATEDIF(J150,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J150" s="6" t="n"/>
       <c r="K150" s="4" t="n"/>
       <c r="L150" s="4" t="n"/>
       <c r="M150" s="4" t="n"/>
       <c r="N150" s="4" t="n"/>
       <c r="O150" s="4" t="n"/>
-      <c r="P150" s="6" t="n"/>
-      <c r="Q150" s="3" t="n"/>
-      <c r="R150" s="4" t="n"/>
+      <c r="P150" s="4" t="n"/>
+      <c r="Q150" s="6" t="n"/>
+      <c r="R150" s="3" t="n"/>
+      <c r="S150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n"/>
@@ -5200,24 +5211,24 @@
         </is>
       </c>
       <c r="F151" s="4" t="n"/>
-      <c r="G151" s="5">
-        <f>IF(P151="","",DATEDIF(P151,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P151,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H151" s="5">
-        <f>IF(I151="","",DATEDIF(I151,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I151" s="6" t="n"/>
-      <c r="J151" s="4" t="n"/>
+        <f>IF(Q151="","",DATEDIF(Q151,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q151,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I151" s="5">
+        <f>IF(J151="","",DATEDIF(J151,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J151" s="6" t="n"/>
       <c r="K151" s="4" t="n"/>
       <c r="L151" s="4" t="n"/>
       <c r="M151" s="4" t="n"/>
       <c r="N151" s="4" t="n"/>
       <c r="O151" s="4" t="n"/>
-      <c r="P151" s="6" t="n"/>
-      <c r="Q151" s="3" t="n"/>
-      <c r="R151" s="4" t="n"/>
+      <c r="P151" s="4" t="n"/>
+      <c r="Q151" s="6" t="n"/>
+      <c r="R151" s="3" t="n"/>
+      <c r="S151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n"/>
@@ -5230,24 +5241,24 @@
         </is>
       </c>
       <c r="F152" s="4" t="n"/>
-      <c r="G152" s="5">
-        <f>IF(P152="","",DATEDIF(P152,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P152,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H152" s="5">
-        <f>IF(I152="","",DATEDIF(I152,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I152" s="6" t="n"/>
-      <c r="J152" s="4" t="n"/>
+        <f>IF(Q152="","",DATEDIF(Q152,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q152,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I152" s="5">
+        <f>IF(J152="","",DATEDIF(J152,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J152" s="6" t="n"/>
       <c r="K152" s="4" t="n"/>
       <c r="L152" s="4" t="n"/>
       <c r="M152" s="4" t="n"/>
       <c r="N152" s="4" t="n"/>
       <c r="O152" s="4" t="n"/>
-      <c r="P152" s="6" t="n"/>
-      <c r="Q152" s="3" t="n"/>
-      <c r="R152" s="4" t="n"/>
+      <c r="P152" s="4" t="n"/>
+      <c r="Q152" s="6" t="n"/>
+      <c r="R152" s="3" t="n"/>
+      <c r="S152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n"/>
@@ -5260,24 +5271,24 @@
         </is>
       </c>
       <c r="F153" s="4" t="n"/>
-      <c r="G153" s="5">
-        <f>IF(P153="","",DATEDIF(P153,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P153,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H153" s="5">
-        <f>IF(I153="","",DATEDIF(I153,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I153" s="6" t="n"/>
-      <c r="J153" s="4" t="n"/>
+        <f>IF(Q153="","",DATEDIF(Q153,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q153,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I153" s="5">
+        <f>IF(J153="","",DATEDIF(J153,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J153" s="6" t="n"/>
       <c r="K153" s="4" t="n"/>
       <c r="L153" s="4" t="n"/>
       <c r="M153" s="4" t="n"/>
       <c r="N153" s="4" t="n"/>
       <c r="O153" s="4" t="n"/>
-      <c r="P153" s="6" t="n"/>
-      <c r="Q153" s="3" t="n"/>
-      <c r="R153" s="4" t="n"/>
+      <c r="P153" s="4" t="n"/>
+      <c r="Q153" s="6" t="n"/>
+      <c r="R153" s="3" t="n"/>
+      <c r="S153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n"/>
@@ -5290,24 +5301,24 @@
         </is>
       </c>
       <c r="F154" s="4" t="n"/>
-      <c r="G154" s="5">
-        <f>IF(P154="","",DATEDIF(P154,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P154,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H154" s="5">
-        <f>IF(I154="","",DATEDIF(I154,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I154" s="6" t="n"/>
-      <c r="J154" s="4" t="n"/>
+        <f>IF(Q154="","",DATEDIF(Q154,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q154,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I154" s="5">
+        <f>IF(J154="","",DATEDIF(J154,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J154" s="6" t="n"/>
       <c r="K154" s="4" t="n"/>
       <c r="L154" s="4" t="n"/>
       <c r="M154" s="4" t="n"/>
       <c r="N154" s="4" t="n"/>
       <c r="O154" s="4" t="n"/>
-      <c r="P154" s="6" t="n"/>
-      <c r="Q154" s="3" t="n"/>
-      <c r="R154" s="4" t="n"/>
+      <c r="P154" s="4" t="n"/>
+      <c r="Q154" s="6" t="n"/>
+      <c r="R154" s="3" t="n"/>
+      <c r="S154" s="4" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n"/>
@@ -5320,24 +5331,24 @@
         </is>
       </c>
       <c r="F155" s="4" t="n"/>
-      <c r="G155" s="5">
-        <f>IF(P155="","",DATEDIF(P155,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P155,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H155" s="5">
-        <f>IF(I155="","",DATEDIF(I155,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I155" s="6" t="n"/>
-      <c r="J155" s="4" t="n"/>
+        <f>IF(Q155="","",DATEDIF(Q155,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q155,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I155" s="5">
+        <f>IF(J155="","",DATEDIF(J155,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J155" s="6" t="n"/>
       <c r="K155" s="4" t="n"/>
       <c r="L155" s="4" t="n"/>
       <c r="M155" s="4" t="n"/>
       <c r="N155" s="4" t="n"/>
       <c r="O155" s="4" t="n"/>
-      <c r="P155" s="6" t="n"/>
-      <c r="Q155" s="3" t="n"/>
-      <c r="R155" s="4" t="n"/>
+      <c r="P155" s="4" t="n"/>
+      <c r="Q155" s="6" t="n"/>
+      <c r="R155" s="3" t="n"/>
+      <c r="S155" s="4" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n"/>
@@ -5350,24 +5361,24 @@
         </is>
       </c>
       <c r="F156" s="4" t="n"/>
-      <c r="G156" s="5">
-        <f>IF(P156="","",DATEDIF(P156,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P156,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H156" s="5">
-        <f>IF(I156="","",DATEDIF(I156,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I156" s="6" t="n"/>
-      <c r="J156" s="4" t="n"/>
+        <f>IF(Q156="","",DATEDIF(Q156,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q156,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I156" s="5">
+        <f>IF(J156="","",DATEDIF(J156,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J156" s="6" t="n"/>
       <c r="K156" s="4" t="n"/>
       <c r="L156" s="4" t="n"/>
       <c r="M156" s="4" t="n"/>
       <c r="N156" s="4" t="n"/>
       <c r="O156" s="4" t="n"/>
-      <c r="P156" s="6" t="n"/>
-      <c r="Q156" s="3" t="n"/>
-      <c r="R156" s="4" t="n"/>
+      <c r="P156" s="4" t="n"/>
+      <c r="Q156" s="6" t="n"/>
+      <c r="R156" s="3" t="n"/>
+      <c r="S156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n"/>
@@ -5380,24 +5391,24 @@
         </is>
       </c>
       <c r="F157" s="4" t="n"/>
-      <c r="G157" s="5">
-        <f>IF(P157="","",DATEDIF(P157,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P157,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H157" s="5">
-        <f>IF(I157="","",DATEDIF(I157,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I157" s="6" t="n"/>
-      <c r="J157" s="4" t="n"/>
+        <f>IF(Q157="","",DATEDIF(Q157,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q157,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I157" s="5">
+        <f>IF(J157="","",DATEDIF(J157,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J157" s="6" t="n"/>
       <c r="K157" s="4" t="n"/>
       <c r="L157" s="4" t="n"/>
       <c r="M157" s="4" t="n"/>
       <c r="N157" s="4" t="n"/>
       <c r="O157" s="4" t="n"/>
-      <c r="P157" s="6" t="n"/>
-      <c r="Q157" s="3" t="n"/>
-      <c r="R157" s="4" t="n"/>
+      <c r="P157" s="4" t="n"/>
+      <c r="Q157" s="6" t="n"/>
+      <c r="R157" s="3" t="n"/>
+      <c r="S157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n"/>
@@ -5410,24 +5421,24 @@
         </is>
       </c>
       <c r="F158" s="4" t="n"/>
-      <c r="G158" s="5">
-        <f>IF(P158="","",DATEDIF(P158,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P158,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H158" s="5">
-        <f>IF(I158="","",DATEDIF(I158,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I158" s="6" t="n"/>
-      <c r="J158" s="4" t="n"/>
+        <f>IF(Q158="","",DATEDIF(Q158,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q158,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I158" s="5">
+        <f>IF(J158="","",DATEDIF(J158,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J158" s="6" t="n"/>
       <c r="K158" s="4" t="n"/>
       <c r="L158" s="4" t="n"/>
       <c r="M158" s="4" t="n"/>
       <c r="N158" s="4" t="n"/>
       <c r="O158" s="4" t="n"/>
-      <c r="P158" s="6" t="n"/>
-      <c r="Q158" s="3" t="n"/>
-      <c r="R158" s="4" t="n"/>
+      <c r="P158" s="4" t="n"/>
+      <c r="Q158" s="6" t="n"/>
+      <c r="R158" s="3" t="n"/>
+      <c r="S158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n"/>
@@ -5440,24 +5451,24 @@
         </is>
       </c>
       <c r="F159" s="4" t="n"/>
-      <c r="G159" s="5">
-        <f>IF(P159="","",DATEDIF(P159,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P159,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H159" s="5">
-        <f>IF(I159="","",DATEDIF(I159,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I159" s="6" t="n"/>
-      <c r="J159" s="4" t="n"/>
+        <f>IF(Q159="","",DATEDIF(Q159,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q159,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I159" s="5">
+        <f>IF(J159="","",DATEDIF(J159,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J159" s="6" t="n"/>
       <c r="K159" s="4" t="n"/>
       <c r="L159" s="4" t="n"/>
       <c r="M159" s="4" t="n"/>
       <c r="N159" s="4" t="n"/>
       <c r="O159" s="4" t="n"/>
-      <c r="P159" s="6" t="n"/>
-      <c r="Q159" s="3" t="n"/>
-      <c r="R159" s="4" t="n"/>
+      <c r="P159" s="4" t="n"/>
+      <c r="Q159" s="6" t="n"/>
+      <c r="R159" s="3" t="n"/>
+      <c r="S159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n"/>
@@ -5470,24 +5481,24 @@
         </is>
       </c>
       <c r="F160" s="4" t="n"/>
-      <c r="G160" s="5">
-        <f>IF(P160="","",DATEDIF(P160,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P160,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H160" s="5">
-        <f>IF(I160="","",DATEDIF(I160,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I160" s="6" t="n"/>
-      <c r="J160" s="4" t="n"/>
+        <f>IF(Q160="","",DATEDIF(Q160,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q160,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I160" s="5">
+        <f>IF(J160="","",DATEDIF(J160,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J160" s="6" t="n"/>
       <c r="K160" s="4" t="n"/>
       <c r="L160" s="4" t="n"/>
       <c r="M160" s="4" t="n"/>
       <c r="N160" s="4" t="n"/>
       <c r="O160" s="4" t="n"/>
-      <c r="P160" s="6" t="n"/>
-      <c r="Q160" s="3" t="n"/>
-      <c r="R160" s="4" t="n"/>
+      <c r="P160" s="4" t="n"/>
+      <c r="Q160" s="6" t="n"/>
+      <c r="R160" s="3" t="n"/>
+      <c r="S160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n"/>
@@ -5500,24 +5511,24 @@
         </is>
       </c>
       <c r="F161" s="4" t="n"/>
-      <c r="G161" s="5">
-        <f>IF(P161="","",DATEDIF(P161,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P161,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H161" s="5">
-        <f>IF(I161="","",DATEDIF(I161,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I161" s="6" t="n"/>
-      <c r="J161" s="4" t="n"/>
+        <f>IF(Q161="","",DATEDIF(Q161,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q161,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I161" s="5">
+        <f>IF(J161="","",DATEDIF(J161,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J161" s="6" t="n"/>
       <c r="K161" s="4" t="n"/>
       <c r="L161" s="4" t="n"/>
       <c r="M161" s="4" t="n"/>
       <c r="N161" s="4" t="n"/>
       <c r="O161" s="4" t="n"/>
-      <c r="P161" s="6" t="n"/>
-      <c r="Q161" s="3" t="n"/>
-      <c r="R161" s="4" t="n"/>
+      <c r="P161" s="4" t="n"/>
+      <c r="Q161" s="6" t="n"/>
+      <c r="R161" s="3" t="n"/>
+      <c r="S161" s="4" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n"/>
@@ -5530,24 +5541,24 @@
         </is>
       </c>
       <c r="F162" s="4" t="n"/>
-      <c r="G162" s="5">
-        <f>IF(P162="","",DATEDIF(P162,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P162,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H162" s="5">
-        <f>IF(I162="","",DATEDIF(I162,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I162" s="6" t="n"/>
-      <c r="J162" s="4" t="n"/>
+        <f>IF(Q162="","",DATEDIF(Q162,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q162,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I162" s="5">
+        <f>IF(J162="","",DATEDIF(J162,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J162" s="6" t="n"/>
       <c r="K162" s="4" t="n"/>
       <c r="L162" s="4" t="n"/>
       <c r="M162" s="4" t="n"/>
       <c r="N162" s="4" t="n"/>
       <c r="O162" s="4" t="n"/>
-      <c r="P162" s="6" t="n"/>
-      <c r="Q162" s="3" t="n"/>
-      <c r="R162" s="4" t="n"/>
+      <c r="P162" s="4" t="n"/>
+      <c r="Q162" s="6" t="n"/>
+      <c r="R162" s="3" t="n"/>
+      <c r="S162" s="4" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n"/>
@@ -5560,24 +5571,24 @@
         </is>
       </c>
       <c r="F163" s="4" t="n"/>
-      <c r="G163" s="5">
-        <f>IF(P163="","",DATEDIF(P163,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P163,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H163" s="5">
-        <f>IF(I163="","",DATEDIF(I163,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I163" s="6" t="n"/>
-      <c r="J163" s="4" t="n"/>
+        <f>IF(Q163="","",DATEDIF(Q163,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q163,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I163" s="5">
+        <f>IF(J163="","",DATEDIF(J163,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J163" s="6" t="n"/>
       <c r="K163" s="4" t="n"/>
       <c r="L163" s="4" t="n"/>
       <c r="M163" s="4" t="n"/>
       <c r="N163" s="4" t="n"/>
       <c r="O163" s="4" t="n"/>
-      <c r="P163" s="6" t="n"/>
-      <c r="Q163" s="3" t="n"/>
-      <c r="R163" s="4" t="n"/>
+      <c r="P163" s="4" t="n"/>
+      <c r="Q163" s="6" t="n"/>
+      <c r="R163" s="3" t="n"/>
+      <c r="S163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n"/>
@@ -5590,24 +5601,24 @@
         </is>
       </c>
       <c r="F164" s="4" t="n"/>
-      <c r="G164" s="5">
-        <f>IF(P164="","",DATEDIF(P164,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P164,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H164" s="5">
-        <f>IF(I164="","",DATEDIF(I164,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I164" s="6" t="n"/>
-      <c r="J164" s="4" t="n"/>
+        <f>IF(Q164="","",DATEDIF(Q164,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q164,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I164" s="5">
+        <f>IF(J164="","",DATEDIF(J164,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J164" s="6" t="n"/>
       <c r="K164" s="4" t="n"/>
       <c r="L164" s="4" t="n"/>
       <c r="M164" s="4" t="n"/>
       <c r="N164" s="4" t="n"/>
       <c r="O164" s="4" t="n"/>
-      <c r="P164" s="6" t="n"/>
-      <c r="Q164" s="3" t="n"/>
-      <c r="R164" s="4" t="n"/>
+      <c r="P164" s="4" t="n"/>
+      <c r="Q164" s="6" t="n"/>
+      <c r="R164" s="3" t="n"/>
+      <c r="S164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n"/>
@@ -5620,24 +5631,24 @@
         </is>
       </c>
       <c r="F165" s="4" t="n"/>
-      <c r="G165" s="5">
-        <f>IF(P165="","",DATEDIF(P165,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P165,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H165" s="5">
-        <f>IF(I165="","",DATEDIF(I165,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I165" s="6" t="n"/>
-      <c r="J165" s="4" t="n"/>
+        <f>IF(Q165="","",DATEDIF(Q165,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q165,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I165" s="5">
+        <f>IF(J165="","",DATEDIF(J165,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J165" s="6" t="n"/>
       <c r="K165" s="4" t="n"/>
       <c r="L165" s="4" t="n"/>
       <c r="M165" s="4" t="n"/>
       <c r="N165" s="4" t="n"/>
       <c r="O165" s="4" t="n"/>
-      <c r="P165" s="6" t="n"/>
-      <c r="Q165" s="3" t="n"/>
-      <c r="R165" s="4" t="n"/>
+      <c r="P165" s="4" t="n"/>
+      <c r="Q165" s="6" t="n"/>
+      <c r="R165" s="3" t="n"/>
+      <c r="S165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n"/>
@@ -5650,24 +5661,24 @@
         </is>
       </c>
       <c r="F166" s="4" t="n"/>
-      <c r="G166" s="5">
-        <f>IF(P166="","",DATEDIF(P166,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P166,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H166" s="5">
-        <f>IF(I166="","",DATEDIF(I166,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I166" s="6" t="n"/>
-      <c r="J166" s="4" t="n"/>
+        <f>IF(Q166="","",DATEDIF(Q166,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q166,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I166" s="5">
+        <f>IF(J166="","",DATEDIF(J166,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J166" s="6" t="n"/>
       <c r="K166" s="4" t="n"/>
       <c r="L166" s="4" t="n"/>
       <c r="M166" s="4" t="n"/>
       <c r="N166" s="4" t="n"/>
       <c r="O166" s="4" t="n"/>
-      <c r="P166" s="6" t="n"/>
-      <c r="Q166" s="3" t="n"/>
-      <c r="R166" s="4" t="n"/>
+      <c r="P166" s="4" t="n"/>
+      <c r="Q166" s="6" t="n"/>
+      <c r="R166" s="3" t="n"/>
+      <c r="S166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n"/>
@@ -5680,24 +5691,24 @@
         </is>
       </c>
       <c r="F167" s="4" t="n"/>
-      <c r="G167" s="5">
-        <f>IF(P167="","",DATEDIF(P167,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P167,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H167" s="5">
-        <f>IF(I167="","",DATEDIF(I167,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I167" s="6" t="n"/>
-      <c r="J167" s="4" t="n"/>
+        <f>IF(Q167="","",DATEDIF(Q167,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q167,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I167" s="5">
+        <f>IF(J167="","",DATEDIF(J167,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J167" s="6" t="n"/>
       <c r="K167" s="4" t="n"/>
       <c r="L167" s="4" t="n"/>
       <c r="M167" s="4" t="n"/>
       <c r="N167" s="4" t="n"/>
       <c r="O167" s="4" t="n"/>
-      <c r="P167" s="6" t="n"/>
-      <c r="Q167" s="3" t="n"/>
-      <c r="R167" s="4" t="n"/>
+      <c r="P167" s="4" t="n"/>
+      <c r="Q167" s="6" t="n"/>
+      <c r="R167" s="3" t="n"/>
+      <c r="S167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n"/>
@@ -5710,24 +5721,24 @@
         </is>
       </c>
       <c r="F168" s="4" t="n"/>
-      <c r="G168" s="5">
-        <f>IF(P168="","",DATEDIF(P168,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P168,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H168" s="5">
-        <f>IF(I168="","",DATEDIF(I168,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I168" s="6" t="n"/>
-      <c r="J168" s="4" t="n"/>
+        <f>IF(Q168="","",DATEDIF(Q168,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q168,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I168" s="5">
+        <f>IF(J168="","",DATEDIF(J168,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J168" s="6" t="n"/>
       <c r="K168" s="4" t="n"/>
       <c r="L168" s="4" t="n"/>
       <c r="M168" s="4" t="n"/>
       <c r="N168" s="4" t="n"/>
       <c r="O168" s="4" t="n"/>
-      <c r="P168" s="6" t="n"/>
-      <c r="Q168" s="3" t="n"/>
-      <c r="R168" s="4" t="n"/>
+      <c r="P168" s="4" t="n"/>
+      <c r="Q168" s="6" t="n"/>
+      <c r="R168" s="3" t="n"/>
+      <c r="S168" s="4" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n"/>
@@ -5740,24 +5751,24 @@
         </is>
       </c>
       <c r="F169" s="4" t="n"/>
-      <c r="G169" s="5">
-        <f>IF(P169="","",DATEDIF(P169,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P169,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H169" s="5">
-        <f>IF(I169="","",DATEDIF(I169,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I169" s="6" t="n"/>
-      <c r="J169" s="4" t="n"/>
+        <f>IF(Q169="","",DATEDIF(Q169,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q169,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I169" s="5">
+        <f>IF(J169="","",DATEDIF(J169,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J169" s="6" t="n"/>
       <c r="K169" s="4" t="n"/>
       <c r="L169" s="4" t="n"/>
       <c r="M169" s="4" t="n"/>
       <c r="N169" s="4" t="n"/>
       <c r="O169" s="4" t="n"/>
-      <c r="P169" s="6" t="n"/>
-      <c r="Q169" s="3" t="n"/>
-      <c r="R169" s="4" t="n"/>
+      <c r="P169" s="4" t="n"/>
+      <c r="Q169" s="6" t="n"/>
+      <c r="R169" s="3" t="n"/>
+      <c r="S169" s="4" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n"/>
@@ -5770,24 +5781,24 @@
         </is>
       </c>
       <c r="F170" s="4" t="n"/>
-      <c r="G170" s="5">
-        <f>IF(P170="","",DATEDIF(P170,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P170,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H170" s="5">
-        <f>IF(I170="","",DATEDIF(I170,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I170" s="6" t="n"/>
-      <c r="J170" s="4" t="n"/>
+        <f>IF(Q170="","",DATEDIF(Q170,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q170,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I170" s="5">
+        <f>IF(J170="","",DATEDIF(J170,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J170" s="6" t="n"/>
       <c r="K170" s="4" t="n"/>
       <c r="L170" s="4" t="n"/>
       <c r="M170" s="4" t="n"/>
       <c r="N170" s="4" t="n"/>
       <c r="O170" s="4" t="n"/>
-      <c r="P170" s="6" t="n"/>
-      <c r="Q170" s="3" t="n"/>
-      <c r="R170" s="4" t="n"/>
+      <c r="P170" s="4" t="n"/>
+      <c r="Q170" s="6" t="n"/>
+      <c r="R170" s="3" t="n"/>
+      <c r="S170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n"/>
@@ -5800,24 +5811,24 @@
         </is>
       </c>
       <c r="F171" s="4" t="n"/>
-      <c r="G171" s="5">
-        <f>IF(P171="","",DATEDIF(P171,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P171,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H171" s="5">
-        <f>IF(I171="","",DATEDIF(I171,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I171" s="6" t="n"/>
-      <c r="J171" s="4" t="n"/>
+        <f>IF(Q171="","",DATEDIF(Q171,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q171,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I171" s="5">
+        <f>IF(J171="","",DATEDIF(J171,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J171" s="6" t="n"/>
       <c r="K171" s="4" t="n"/>
       <c r="L171" s="4" t="n"/>
       <c r="M171" s="4" t="n"/>
       <c r="N171" s="4" t="n"/>
       <c r="O171" s="4" t="n"/>
-      <c r="P171" s="6" t="n"/>
-      <c r="Q171" s="3" t="n"/>
-      <c r="R171" s="4" t="n"/>
+      <c r="P171" s="4" t="n"/>
+      <c r="Q171" s="6" t="n"/>
+      <c r="R171" s="3" t="n"/>
+      <c r="S171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n"/>
@@ -5830,24 +5841,24 @@
         </is>
       </c>
       <c r="F172" s="4" t="n"/>
-      <c r="G172" s="5">
-        <f>IF(P172="","",DATEDIF(P172,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P172,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H172" s="5">
-        <f>IF(I172="","",DATEDIF(I172,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I172" s="6" t="n"/>
-      <c r="J172" s="4" t="n"/>
+        <f>IF(Q172="","",DATEDIF(Q172,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q172,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I172" s="5">
+        <f>IF(J172="","",DATEDIF(J172,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J172" s="6" t="n"/>
       <c r="K172" s="4" t="n"/>
       <c r="L172" s="4" t="n"/>
       <c r="M172" s="4" t="n"/>
       <c r="N172" s="4" t="n"/>
       <c r="O172" s="4" t="n"/>
-      <c r="P172" s="6" t="n"/>
-      <c r="Q172" s="3" t="n"/>
-      <c r="R172" s="4" t="n"/>
+      <c r="P172" s="4" t="n"/>
+      <c r="Q172" s="6" t="n"/>
+      <c r="R172" s="3" t="n"/>
+      <c r="S172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n"/>
@@ -5860,24 +5871,24 @@
         </is>
       </c>
       <c r="F173" s="4" t="n"/>
-      <c r="G173" s="5">
-        <f>IF(P173="","",DATEDIF(P173,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P173,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H173" s="5">
-        <f>IF(I173="","",DATEDIF(I173,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I173" s="6" t="n"/>
-      <c r="J173" s="4" t="n"/>
+        <f>IF(Q173="","",DATEDIF(Q173,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q173,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I173" s="5">
+        <f>IF(J173="","",DATEDIF(J173,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J173" s="6" t="n"/>
       <c r="K173" s="4" t="n"/>
       <c r="L173" s="4" t="n"/>
       <c r="M173" s="4" t="n"/>
       <c r="N173" s="4" t="n"/>
       <c r="O173" s="4" t="n"/>
-      <c r="P173" s="6" t="n"/>
-      <c r="Q173" s="3" t="n"/>
-      <c r="R173" s="4" t="n"/>
+      <c r="P173" s="4" t="n"/>
+      <c r="Q173" s="6" t="n"/>
+      <c r="R173" s="3" t="n"/>
+      <c r="S173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n"/>
@@ -5890,24 +5901,24 @@
         </is>
       </c>
       <c r="F174" s="4" t="n"/>
-      <c r="G174" s="5">
-        <f>IF(P174="","",DATEDIF(P174,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P174,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H174" s="5">
-        <f>IF(I174="","",DATEDIF(I174,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I174" s="6" t="n"/>
-      <c r="J174" s="4" t="n"/>
+        <f>IF(Q174="","",DATEDIF(Q174,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q174,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I174" s="5">
+        <f>IF(J174="","",DATEDIF(J174,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J174" s="6" t="n"/>
       <c r="K174" s="4" t="n"/>
       <c r="L174" s="4" t="n"/>
       <c r="M174" s="4" t="n"/>
       <c r="N174" s="4" t="n"/>
       <c r="O174" s="4" t="n"/>
-      <c r="P174" s="6" t="n"/>
-      <c r="Q174" s="3" t="n"/>
-      <c r="R174" s="4" t="n"/>
+      <c r="P174" s="4" t="n"/>
+      <c r="Q174" s="6" t="n"/>
+      <c r="R174" s="3" t="n"/>
+      <c r="S174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="n"/>
@@ -5920,24 +5931,24 @@
         </is>
       </c>
       <c r="F175" s="4" t="n"/>
-      <c r="G175" s="5">
-        <f>IF(P175="","",DATEDIF(P175,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P175,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H175" s="5">
-        <f>IF(I175="","",DATEDIF(I175,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I175" s="6" t="n"/>
-      <c r="J175" s="4" t="n"/>
+        <f>IF(Q175="","",DATEDIF(Q175,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q175,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I175" s="5">
+        <f>IF(J175="","",DATEDIF(J175,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J175" s="6" t="n"/>
       <c r="K175" s="4" t="n"/>
       <c r="L175" s="4" t="n"/>
       <c r="M175" s="4" t="n"/>
       <c r="N175" s="4" t="n"/>
       <c r="O175" s="4" t="n"/>
-      <c r="P175" s="6" t="n"/>
-      <c r="Q175" s="3" t="n"/>
-      <c r="R175" s="4" t="n"/>
+      <c r="P175" s="4" t="n"/>
+      <c r="Q175" s="6" t="n"/>
+      <c r="R175" s="3" t="n"/>
+      <c r="S175" s="4" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n"/>
@@ -5950,24 +5961,24 @@
         </is>
       </c>
       <c r="F176" s="4" t="n"/>
-      <c r="G176" s="5">
-        <f>IF(P176="","",DATEDIF(P176,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P176,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H176" s="5">
-        <f>IF(I176="","",DATEDIF(I176,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I176" s="6" t="n"/>
-      <c r="J176" s="4" t="n"/>
+        <f>IF(Q176="","",DATEDIF(Q176,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q176,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I176" s="5">
+        <f>IF(J176="","",DATEDIF(J176,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J176" s="6" t="n"/>
       <c r="K176" s="4" t="n"/>
       <c r="L176" s="4" t="n"/>
       <c r="M176" s="4" t="n"/>
       <c r="N176" s="4" t="n"/>
       <c r="O176" s="4" t="n"/>
-      <c r="P176" s="6" t="n"/>
-      <c r="Q176" s="3" t="n"/>
-      <c r="R176" s="4" t="n"/>
+      <c r="P176" s="4" t="n"/>
+      <c r="Q176" s="6" t="n"/>
+      <c r="R176" s="3" t="n"/>
+      <c r="S176" s="4" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n"/>
@@ -5980,24 +5991,24 @@
         </is>
       </c>
       <c r="F177" s="4" t="n"/>
-      <c r="G177" s="5">
-        <f>IF(P177="","",DATEDIF(P177,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P177,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H177" s="5">
-        <f>IF(I177="","",DATEDIF(I177,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I177" s="6" t="n"/>
-      <c r="J177" s="4" t="n"/>
+        <f>IF(Q177="","",DATEDIF(Q177,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q177,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I177" s="5">
+        <f>IF(J177="","",DATEDIF(J177,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J177" s="6" t="n"/>
       <c r="K177" s="4" t="n"/>
       <c r="L177" s="4" t="n"/>
       <c r="M177" s="4" t="n"/>
       <c r="N177" s="4" t="n"/>
       <c r="O177" s="4" t="n"/>
-      <c r="P177" s="6" t="n"/>
-      <c r="Q177" s="3" t="n"/>
-      <c r="R177" s="4" t="n"/>
+      <c r="P177" s="4" t="n"/>
+      <c r="Q177" s="6" t="n"/>
+      <c r="R177" s="3" t="n"/>
+      <c r="S177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n"/>
@@ -6010,24 +6021,24 @@
         </is>
       </c>
       <c r="F178" s="4" t="n"/>
-      <c r="G178" s="5">
-        <f>IF(P178="","",DATEDIF(P178,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P178,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H178" s="5">
-        <f>IF(I178="","",DATEDIF(I178,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I178" s="6" t="n"/>
-      <c r="J178" s="4" t="n"/>
+        <f>IF(Q178="","",DATEDIF(Q178,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q178,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I178" s="5">
+        <f>IF(J178="","",DATEDIF(J178,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J178" s="6" t="n"/>
       <c r="K178" s="4" t="n"/>
       <c r="L178" s="4" t="n"/>
       <c r="M178" s="4" t="n"/>
       <c r="N178" s="4" t="n"/>
       <c r="O178" s="4" t="n"/>
-      <c r="P178" s="6" t="n"/>
-      <c r="Q178" s="3" t="n"/>
-      <c r="R178" s="4" t="n"/>
+      <c r="P178" s="4" t="n"/>
+      <c r="Q178" s="6" t="n"/>
+      <c r="R178" s="3" t="n"/>
+      <c r="S178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n"/>
@@ -6040,24 +6051,24 @@
         </is>
       </c>
       <c r="F179" s="4" t="n"/>
-      <c r="G179" s="5">
-        <f>IF(P179="","",DATEDIF(P179,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P179,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H179" s="5">
-        <f>IF(I179="","",DATEDIF(I179,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I179" s="6" t="n"/>
-      <c r="J179" s="4" t="n"/>
+        <f>IF(Q179="","",DATEDIF(Q179,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q179,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I179" s="5">
+        <f>IF(J179="","",DATEDIF(J179,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J179" s="6" t="n"/>
       <c r="K179" s="4" t="n"/>
       <c r="L179" s="4" t="n"/>
       <c r="M179" s="4" t="n"/>
       <c r="N179" s="4" t="n"/>
       <c r="O179" s="4" t="n"/>
-      <c r="P179" s="6" t="n"/>
-      <c r="Q179" s="3" t="n"/>
-      <c r="R179" s="4" t="n"/>
+      <c r="P179" s="4" t="n"/>
+      <c r="Q179" s="6" t="n"/>
+      <c r="R179" s="3" t="n"/>
+      <c r="S179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="n"/>
@@ -6070,24 +6081,24 @@
         </is>
       </c>
       <c r="F180" s="4" t="n"/>
-      <c r="G180" s="5">
-        <f>IF(P180="","",DATEDIF(P180,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P180,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H180" s="5">
-        <f>IF(I180="","",DATEDIF(I180,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I180" s="6" t="n"/>
-      <c r="J180" s="4" t="n"/>
+        <f>IF(Q180="","",DATEDIF(Q180,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q180,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I180" s="5">
+        <f>IF(J180="","",DATEDIF(J180,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J180" s="6" t="n"/>
       <c r="K180" s="4" t="n"/>
       <c r="L180" s="4" t="n"/>
       <c r="M180" s="4" t="n"/>
       <c r="N180" s="4" t="n"/>
       <c r="O180" s="4" t="n"/>
-      <c r="P180" s="6" t="n"/>
-      <c r="Q180" s="3" t="n"/>
-      <c r="R180" s="4" t="n"/>
+      <c r="P180" s="4" t="n"/>
+      <c r="Q180" s="6" t="n"/>
+      <c r="R180" s="3" t="n"/>
+      <c r="S180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="n"/>
@@ -6100,24 +6111,24 @@
         </is>
       </c>
       <c r="F181" s="4" t="n"/>
-      <c r="G181" s="5">
-        <f>IF(P181="","",DATEDIF(P181,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P181,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H181" s="5">
-        <f>IF(I181="","",DATEDIF(I181,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I181" s="6" t="n"/>
-      <c r="J181" s="4" t="n"/>
+        <f>IF(Q181="","",DATEDIF(Q181,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q181,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I181" s="5">
+        <f>IF(J181="","",DATEDIF(J181,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J181" s="6" t="n"/>
       <c r="K181" s="4" t="n"/>
       <c r="L181" s="4" t="n"/>
       <c r="M181" s="4" t="n"/>
       <c r="N181" s="4" t="n"/>
       <c r="O181" s="4" t="n"/>
-      <c r="P181" s="6" t="n"/>
-      <c r="Q181" s="3" t="n"/>
-      <c r="R181" s="4" t="n"/>
+      <c r="P181" s="4" t="n"/>
+      <c r="Q181" s="6" t="n"/>
+      <c r="R181" s="3" t="n"/>
+      <c r="S181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n"/>
@@ -6130,24 +6141,24 @@
         </is>
       </c>
       <c r="F182" s="4" t="n"/>
-      <c r="G182" s="5">
-        <f>IF(P182="","",DATEDIF(P182,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P182,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H182" s="5">
-        <f>IF(I182="","",DATEDIF(I182,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I182" s="6" t="n"/>
-      <c r="J182" s="4" t="n"/>
+        <f>IF(Q182="","",DATEDIF(Q182,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q182,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I182" s="5">
+        <f>IF(J182="","",DATEDIF(J182,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J182" s="6" t="n"/>
       <c r="K182" s="4" t="n"/>
       <c r="L182" s="4" t="n"/>
       <c r="M182" s="4" t="n"/>
       <c r="N182" s="4" t="n"/>
       <c r="O182" s="4" t="n"/>
-      <c r="P182" s="6" t="n"/>
-      <c r="Q182" s="3" t="n"/>
-      <c r="R182" s="4" t="n"/>
+      <c r="P182" s="4" t="n"/>
+      <c r="Q182" s="6" t="n"/>
+      <c r="R182" s="3" t="n"/>
+      <c r="S182" s="4" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="n"/>
@@ -6160,24 +6171,24 @@
         </is>
       </c>
       <c r="F183" s="4" t="n"/>
-      <c r="G183" s="5">
-        <f>IF(P183="","",DATEDIF(P183,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P183,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H183" s="5">
-        <f>IF(I183="","",DATEDIF(I183,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I183" s="6" t="n"/>
-      <c r="J183" s="4" t="n"/>
+        <f>IF(Q183="","",DATEDIF(Q183,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q183,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I183" s="5">
+        <f>IF(J183="","",DATEDIF(J183,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J183" s="6" t="n"/>
       <c r="K183" s="4" t="n"/>
       <c r="L183" s="4" t="n"/>
       <c r="M183" s="4" t="n"/>
       <c r="N183" s="4" t="n"/>
       <c r="O183" s="4" t="n"/>
-      <c r="P183" s="6" t="n"/>
-      <c r="Q183" s="3" t="n"/>
-      <c r="R183" s="4" t="n"/>
+      <c r="P183" s="4" t="n"/>
+      <c r="Q183" s="6" t="n"/>
+      <c r="R183" s="3" t="n"/>
+      <c r="S183" s="4" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="n"/>
@@ -6190,24 +6201,24 @@
         </is>
       </c>
       <c r="F184" s="4" t="n"/>
-      <c r="G184" s="5">
-        <f>IF(P184="","",DATEDIF(P184,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P184,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H184" s="5">
-        <f>IF(I184="","",DATEDIF(I184,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I184" s="6" t="n"/>
-      <c r="J184" s="4" t="n"/>
+        <f>IF(Q184="","",DATEDIF(Q184,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q184,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I184" s="5">
+        <f>IF(J184="","",DATEDIF(J184,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J184" s="6" t="n"/>
       <c r="K184" s="4" t="n"/>
       <c r="L184" s="4" t="n"/>
       <c r="M184" s="4" t="n"/>
       <c r="N184" s="4" t="n"/>
       <c r="O184" s="4" t="n"/>
-      <c r="P184" s="6" t="n"/>
-      <c r="Q184" s="3" t="n"/>
-      <c r="R184" s="4" t="n"/>
+      <c r="P184" s="4" t="n"/>
+      <c r="Q184" s="6" t="n"/>
+      <c r="R184" s="3" t="n"/>
+      <c r="S184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="n"/>
@@ -6220,24 +6231,24 @@
         </is>
       </c>
       <c r="F185" s="4" t="n"/>
-      <c r="G185" s="5">
-        <f>IF(P185="","",DATEDIF(P185,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P185,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H185" s="5">
-        <f>IF(I185="","",DATEDIF(I185,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I185" s="6" t="n"/>
-      <c r="J185" s="4" t="n"/>
+        <f>IF(Q185="","",DATEDIF(Q185,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q185,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I185" s="5">
+        <f>IF(J185="","",DATEDIF(J185,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J185" s="6" t="n"/>
       <c r="K185" s="4" t="n"/>
       <c r="L185" s="4" t="n"/>
       <c r="M185" s="4" t="n"/>
       <c r="N185" s="4" t="n"/>
       <c r="O185" s="4" t="n"/>
-      <c r="P185" s="6" t="n"/>
-      <c r="Q185" s="3" t="n"/>
-      <c r="R185" s="4" t="n"/>
+      <c r="P185" s="4" t="n"/>
+      <c r="Q185" s="6" t="n"/>
+      <c r="R185" s="3" t="n"/>
+      <c r="S185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="n"/>
@@ -6250,24 +6261,24 @@
         </is>
       </c>
       <c r="F186" s="4" t="n"/>
-      <c r="G186" s="5">
-        <f>IF(P186="","",DATEDIF(P186,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P186,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H186" s="5">
-        <f>IF(I186="","",DATEDIF(I186,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I186" s="6" t="n"/>
-      <c r="J186" s="4" t="n"/>
+        <f>IF(Q186="","",DATEDIF(Q186,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q186,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I186" s="5">
+        <f>IF(J186="","",DATEDIF(J186,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J186" s="6" t="n"/>
       <c r="K186" s="4" t="n"/>
       <c r="L186" s="4" t="n"/>
       <c r="M186" s="4" t="n"/>
       <c r="N186" s="4" t="n"/>
       <c r="O186" s="4" t="n"/>
-      <c r="P186" s="6" t="n"/>
-      <c r="Q186" s="3" t="n"/>
-      <c r="R186" s="4" t="n"/>
+      <c r="P186" s="4" t="n"/>
+      <c r="Q186" s="6" t="n"/>
+      <c r="R186" s="3" t="n"/>
+      <c r="S186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="n"/>
@@ -6280,24 +6291,24 @@
         </is>
       </c>
       <c r="F187" s="4" t="n"/>
-      <c r="G187" s="5">
-        <f>IF(P187="","",DATEDIF(P187,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P187,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H187" s="5">
-        <f>IF(I187="","",DATEDIF(I187,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I187" s="6" t="n"/>
-      <c r="J187" s="4" t="n"/>
+        <f>IF(Q187="","",DATEDIF(Q187,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q187,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I187" s="5">
+        <f>IF(J187="","",DATEDIF(J187,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J187" s="6" t="n"/>
       <c r="K187" s="4" t="n"/>
       <c r="L187" s="4" t="n"/>
       <c r="M187" s="4" t="n"/>
       <c r="N187" s="4" t="n"/>
       <c r="O187" s="4" t="n"/>
-      <c r="P187" s="6" t="n"/>
-      <c r="Q187" s="3" t="n"/>
-      <c r="R187" s="4" t="n"/>
+      <c r="P187" s="4" t="n"/>
+      <c r="Q187" s="6" t="n"/>
+      <c r="R187" s="3" t="n"/>
+      <c r="S187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="n"/>
@@ -6310,24 +6321,24 @@
         </is>
       </c>
       <c r="F188" s="4" t="n"/>
-      <c r="G188" s="5">
-        <f>IF(P188="","",DATEDIF(P188,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P188,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H188" s="5">
-        <f>IF(I188="","",DATEDIF(I188,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I188" s="6" t="n"/>
-      <c r="J188" s="4" t="n"/>
+        <f>IF(Q188="","",DATEDIF(Q188,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q188,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I188" s="5">
+        <f>IF(J188="","",DATEDIF(J188,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J188" s="6" t="n"/>
       <c r="K188" s="4" t="n"/>
       <c r="L188" s="4" t="n"/>
       <c r="M188" s="4" t="n"/>
       <c r="N188" s="4" t="n"/>
       <c r="O188" s="4" t="n"/>
-      <c r="P188" s="6" t="n"/>
-      <c r="Q188" s="3" t="n"/>
-      <c r="R188" s="4" t="n"/>
+      <c r="P188" s="4" t="n"/>
+      <c r="Q188" s="6" t="n"/>
+      <c r="R188" s="3" t="n"/>
+      <c r="S188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="n"/>
@@ -6340,24 +6351,24 @@
         </is>
       </c>
       <c r="F189" s="4" t="n"/>
-      <c r="G189" s="5">
-        <f>IF(P189="","",DATEDIF(P189,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P189,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H189" s="5">
-        <f>IF(I189="","",DATEDIF(I189,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I189" s="6" t="n"/>
-      <c r="J189" s="4" t="n"/>
+        <f>IF(Q189="","",DATEDIF(Q189,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q189,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I189" s="5">
+        <f>IF(J189="","",DATEDIF(J189,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J189" s="6" t="n"/>
       <c r="K189" s="4" t="n"/>
       <c r="L189" s="4" t="n"/>
       <c r="M189" s="4" t="n"/>
       <c r="N189" s="4" t="n"/>
       <c r="O189" s="4" t="n"/>
-      <c r="P189" s="6" t="n"/>
-      <c r="Q189" s="3" t="n"/>
-      <c r="R189" s="4" t="n"/>
+      <c r="P189" s="4" t="n"/>
+      <c r="Q189" s="6" t="n"/>
+      <c r="R189" s="3" t="n"/>
+      <c r="S189" s="4" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="n"/>
@@ -6370,24 +6381,24 @@
         </is>
       </c>
       <c r="F190" s="4" t="n"/>
-      <c r="G190" s="5">
-        <f>IF(P190="","",DATEDIF(P190,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P190,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H190" s="5">
-        <f>IF(I190="","",DATEDIF(I190,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I190" s="6" t="n"/>
-      <c r="J190" s="4" t="n"/>
+        <f>IF(Q190="","",DATEDIF(Q190,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q190,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I190" s="5">
+        <f>IF(J190="","",DATEDIF(J190,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J190" s="6" t="n"/>
       <c r="K190" s="4" t="n"/>
       <c r="L190" s="4" t="n"/>
       <c r="M190" s="4" t="n"/>
       <c r="N190" s="4" t="n"/>
       <c r="O190" s="4" t="n"/>
-      <c r="P190" s="6" t="n"/>
-      <c r="Q190" s="3" t="n"/>
-      <c r="R190" s="4" t="n"/>
+      <c r="P190" s="4" t="n"/>
+      <c r="Q190" s="6" t="n"/>
+      <c r="R190" s="3" t="n"/>
+      <c r="S190" s="4" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="n"/>
@@ -6400,24 +6411,24 @@
         </is>
       </c>
       <c r="F191" s="4" t="n"/>
-      <c r="G191" s="5">
-        <f>IF(P191="","",DATEDIF(P191,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P191,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H191" s="5">
-        <f>IF(I191="","",DATEDIF(I191,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I191" s="6" t="n"/>
-      <c r="J191" s="4" t="n"/>
+        <f>IF(Q191="","",DATEDIF(Q191,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q191,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I191" s="5">
+        <f>IF(J191="","",DATEDIF(J191,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J191" s="6" t="n"/>
       <c r="K191" s="4" t="n"/>
       <c r="L191" s="4" t="n"/>
       <c r="M191" s="4" t="n"/>
       <c r="N191" s="4" t="n"/>
       <c r="O191" s="4" t="n"/>
-      <c r="P191" s="6" t="n"/>
-      <c r="Q191" s="3" t="n"/>
-      <c r="R191" s="4" t="n"/>
+      <c r="P191" s="4" t="n"/>
+      <c r="Q191" s="6" t="n"/>
+      <c r="R191" s="3" t="n"/>
+      <c r="S191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="n"/>
@@ -6430,24 +6441,24 @@
         </is>
       </c>
       <c r="F192" s="4" t="n"/>
-      <c r="G192" s="5">
-        <f>IF(P192="","",DATEDIF(P192,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P192,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H192" s="5">
-        <f>IF(I192="","",DATEDIF(I192,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I192" s="6" t="n"/>
-      <c r="J192" s="4" t="n"/>
+        <f>IF(Q192="","",DATEDIF(Q192,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q192,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I192" s="5">
+        <f>IF(J192="","",DATEDIF(J192,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J192" s="6" t="n"/>
       <c r="K192" s="4" t="n"/>
       <c r="L192" s="4" t="n"/>
       <c r="M192" s="4" t="n"/>
       <c r="N192" s="4" t="n"/>
       <c r="O192" s="4" t="n"/>
-      <c r="P192" s="6" t="n"/>
-      <c r="Q192" s="3" t="n"/>
-      <c r="R192" s="4" t="n"/>
+      <c r="P192" s="4" t="n"/>
+      <c r="Q192" s="6" t="n"/>
+      <c r="R192" s="3" t="n"/>
+      <c r="S192" s="4" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="n"/>
@@ -6460,24 +6471,24 @@
         </is>
       </c>
       <c r="F193" s="4" t="n"/>
-      <c r="G193" s="5">
-        <f>IF(P193="","",DATEDIF(P193,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P193,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H193" s="5">
-        <f>IF(I193="","",DATEDIF(I193,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I193" s="6" t="n"/>
-      <c r="J193" s="4" t="n"/>
+        <f>IF(Q193="","",DATEDIF(Q193,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q193,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I193" s="5">
+        <f>IF(J193="","",DATEDIF(J193,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J193" s="6" t="n"/>
       <c r="K193" s="4" t="n"/>
       <c r="L193" s="4" t="n"/>
       <c r="M193" s="4" t="n"/>
       <c r="N193" s="4" t="n"/>
       <c r="O193" s="4" t="n"/>
-      <c r="P193" s="6" t="n"/>
-      <c r="Q193" s="3" t="n"/>
-      <c r="R193" s="4" t="n"/>
+      <c r="P193" s="4" t="n"/>
+      <c r="Q193" s="6" t="n"/>
+      <c r="R193" s="3" t="n"/>
+      <c r="S193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="n"/>
@@ -6490,24 +6501,24 @@
         </is>
       </c>
       <c r="F194" s="4" t="n"/>
-      <c r="G194" s="5">
-        <f>IF(P194="","",DATEDIF(P194,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P194,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H194" s="5">
-        <f>IF(I194="","",DATEDIF(I194,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I194" s="6" t="n"/>
-      <c r="J194" s="4" t="n"/>
+        <f>IF(Q194="","",DATEDIF(Q194,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q194,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I194" s="5">
+        <f>IF(J194="","",DATEDIF(J194,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J194" s="6" t="n"/>
       <c r="K194" s="4" t="n"/>
       <c r="L194" s="4" t="n"/>
       <c r="M194" s="4" t="n"/>
       <c r="N194" s="4" t="n"/>
       <c r="O194" s="4" t="n"/>
-      <c r="P194" s="6" t="n"/>
-      <c r="Q194" s="3" t="n"/>
-      <c r="R194" s="4" t="n"/>
+      <c r="P194" s="4" t="n"/>
+      <c r="Q194" s="6" t="n"/>
+      <c r="R194" s="3" t="n"/>
+      <c r="S194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="n"/>
@@ -6520,24 +6531,24 @@
         </is>
       </c>
       <c r="F195" s="4" t="n"/>
-      <c r="G195" s="5">
-        <f>IF(P195="","",DATEDIF(P195,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P195,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H195" s="5">
-        <f>IF(I195="","",DATEDIF(I195,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I195" s="6" t="n"/>
-      <c r="J195" s="4" t="n"/>
+        <f>IF(Q195="","",DATEDIF(Q195,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q195,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I195" s="5">
+        <f>IF(J195="","",DATEDIF(J195,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J195" s="6" t="n"/>
       <c r="K195" s="4" t="n"/>
       <c r="L195" s="4" t="n"/>
       <c r="M195" s="4" t="n"/>
       <c r="N195" s="4" t="n"/>
       <c r="O195" s="4" t="n"/>
-      <c r="P195" s="6" t="n"/>
-      <c r="Q195" s="3" t="n"/>
-      <c r="R195" s="4" t="n"/>
+      <c r="P195" s="4" t="n"/>
+      <c r="Q195" s="6" t="n"/>
+      <c r="R195" s="3" t="n"/>
+      <c r="S195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="n"/>
@@ -6550,24 +6561,24 @@
         </is>
       </c>
       <c r="F196" s="4" t="n"/>
-      <c r="G196" s="5">
-        <f>IF(P196="","",DATEDIF(P196,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P196,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H196" s="5">
-        <f>IF(I196="","",DATEDIF(I196,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I196" s="6" t="n"/>
-      <c r="J196" s="4" t="n"/>
+        <f>IF(Q196="","",DATEDIF(Q196,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q196,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I196" s="5">
+        <f>IF(J196="","",DATEDIF(J196,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J196" s="6" t="n"/>
       <c r="K196" s="4" t="n"/>
       <c r="L196" s="4" t="n"/>
       <c r="M196" s="4" t="n"/>
       <c r="N196" s="4" t="n"/>
       <c r="O196" s="4" t="n"/>
-      <c r="P196" s="6" t="n"/>
-      <c r="Q196" s="3" t="n"/>
-      <c r="R196" s="4" t="n"/>
+      <c r="P196" s="4" t="n"/>
+      <c r="Q196" s="6" t="n"/>
+      <c r="R196" s="3" t="n"/>
+      <c r="S196" s="4" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="n"/>
@@ -6580,24 +6591,24 @@
         </is>
       </c>
       <c r="F197" s="4" t="n"/>
-      <c r="G197" s="5">
-        <f>IF(P197="","",DATEDIF(P197,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P197,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H197" s="5">
-        <f>IF(I197="","",DATEDIF(I197,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I197" s="6" t="n"/>
-      <c r="J197" s="4" t="n"/>
+        <f>IF(Q197="","",DATEDIF(Q197,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q197,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I197" s="5">
+        <f>IF(J197="","",DATEDIF(J197,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J197" s="6" t="n"/>
       <c r="K197" s="4" t="n"/>
       <c r="L197" s="4" t="n"/>
       <c r="M197" s="4" t="n"/>
       <c r="N197" s="4" t="n"/>
       <c r="O197" s="4" t="n"/>
-      <c r="P197" s="6" t="n"/>
-      <c r="Q197" s="3" t="n"/>
-      <c r="R197" s="4" t="n"/>
+      <c r="P197" s="4" t="n"/>
+      <c r="Q197" s="6" t="n"/>
+      <c r="R197" s="3" t="n"/>
+      <c r="S197" s="4" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="n"/>
@@ -6610,24 +6621,24 @@
         </is>
       </c>
       <c r="F198" s="4" t="n"/>
-      <c r="G198" s="5">
-        <f>IF(P198="","",DATEDIF(P198,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P198,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H198" s="5">
-        <f>IF(I198="","",DATEDIF(I198,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I198" s="6" t="n"/>
-      <c r="J198" s="4" t="n"/>
+        <f>IF(Q198="","",DATEDIF(Q198,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q198,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I198" s="5">
+        <f>IF(J198="","",DATEDIF(J198,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J198" s="6" t="n"/>
       <c r="K198" s="4" t="n"/>
       <c r="L198" s="4" t="n"/>
       <c r="M198" s="4" t="n"/>
       <c r="N198" s="4" t="n"/>
       <c r="O198" s="4" t="n"/>
-      <c r="P198" s="6" t="n"/>
-      <c r="Q198" s="3" t="n"/>
-      <c r="R198" s="4" t="n"/>
+      <c r="P198" s="4" t="n"/>
+      <c r="Q198" s="6" t="n"/>
+      <c r="R198" s="3" t="n"/>
+      <c r="S198" s="4" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="n"/>
@@ -6640,24 +6651,24 @@
         </is>
       </c>
       <c r="F199" s="4" t="n"/>
-      <c r="G199" s="5">
-        <f>IF(P199="","",DATEDIF(P199,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P199,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H199" s="5">
-        <f>IF(I199="","",DATEDIF(I199,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I199" s="6" t="n"/>
-      <c r="J199" s="4" t="n"/>
+        <f>IF(Q199="","",DATEDIF(Q199,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q199,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I199" s="5">
+        <f>IF(J199="","",DATEDIF(J199,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J199" s="6" t="n"/>
       <c r="K199" s="4" t="n"/>
       <c r="L199" s="4" t="n"/>
       <c r="M199" s="4" t="n"/>
       <c r="N199" s="4" t="n"/>
       <c r="O199" s="4" t="n"/>
-      <c r="P199" s="6" t="n"/>
-      <c r="Q199" s="3" t="n"/>
-      <c r="R199" s="4" t="n"/>
+      <c r="P199" s="4" t="n"/>
+      <c r="Q199" s="6" t="n"/>
+      <c r="R199" s="3" t="n"/>
+      <c r="S199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="n"/>
@@ -6670,24 +6681,24 @@
         </is>
       </c>
       <c r="F200" s="4" t="n"/>
-      <c r="G200" s="5">
-        <f>IF(P200="","",DATEDIF(P200,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P200,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H200" s="5">
-        <f>IF(I200="","",DATEDIF(I200,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I200" s="6" t="n"/>
-      <c r="J200" s="4" t="n"/>
+        <f>IF(Q200="","",DATEDIF(Q200,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q200,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I200" s="5">
+        <f>IF(J200="","",DATEDIF(J200,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J200" s="6" t="n"/>
       <c r="K200" s="4" t="n"/>
       <c r="L200" s="4" t="n"/>
       <c r="M200" s="4" t="n"/>
       <c r="N200" s="4" t="n"/>
       <c r="O200" s="4" t="n"/>
-      <c r="P200" s="6" t="n"/>
-      <c r="Q200" s="3" t="n"/>
-      <c r="R200" s="4" t="n"/>
+      <c r="P200" s="4" t="n"/>
+      <c r="Q200" s="6" t="n"/>
+      <c r="R200" s="3" t="n"/>
+      <c r="S200" s="4" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="n"/>
@@ -6700,24 +6711,24 @@
         </is>
       </c>
       <c r="F201" s="4" t="n"/>
-      <c r="G201" s="5">
-        <f>IF(P201="","",DATEDIF(P201,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P201,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H201" s="5">
-        <f>IF(I201="","",DATEDIF(I201,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I201" s="6" t="n"/>
-      <c r="J201" s="4" t="n"/>
+        <f>IF(Q201="","",DATEDIF(Q201,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q201,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I201" s="5">
+        <f>IF(J201="","",DATEDIF(J201,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J201" s="6" t="n"/>
       <c r="K201" s="4" t="n"/>
       <c r="L201" s="4" t="n"/>
       <c r="M201" s="4" t="n"/>
       <c r="N201" s="4" t="n"/>
       <c r="O201" s="4" t="n"/>
-      <c r="P201" s="6" t="n"/>
-      <c r="Q201" s="3" t="n"/>
-      <c r="R201" s="4" t="n"/>
+      <c r="P201" s="4" t="n"/>
+      <c r="Q201" s="6" t="n"/>
+      <c r="R201" s="3" t="n"/>
+      <c r="S201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="n"/>
@@ -6730,60 +6741,63 @@
         </is>
       </c>
       <c r="F202" s="4" t="n"/>
-      <c r="G202" s="5">
-        <f>IF(P202="","",DATEDIF(P202,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(P202,TODAY(),"YM")&amp;" bulan")</f>
-        <v/>
-      </c>
       <c r="H202" s="5">
-        <f>IF(I202="","",DATEDIF(I202,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="I202" s="6" t="n"/>
-      <c r="J202" s="4" t="n"/>
+        <f>IF(Q202="","",DATEDIF(Q202,TODAY(),"Y")&amp;" tahun "&amp;DATEDIF(Q202,TODAY(),"YM")&amp;" bulan")</f>
+        <v/>
+      </c>
+      <c r="I202" s="5">
+        <f>IF(J202="","",DATEDIF(J202,TODAY(),"Y"))</f>
+        <v/>
+      </c>
+      <c r="J202" s="6" t="n"/>
       <c r="K202" s="4" t="n"/>
       <c r="L202" s="4" t="n"/>
       <c r="M202" s="4" t="n"/>
       <c r="N202" s="4" t="n"/>
       <c r="O202" s="4" t="n"/>
-      <c r="P202" s="6" t="n"/>
-      <c r="Q202" s="3" t="n"/>
-      <c r="R202" s="4" t="n"/>
+      <c r="P202" s="4" t="n"/>
+      <c r="Q202" s="6" t="n"/>
+      <c r="R202" s="3" t="n"/>
+      <c r="S202" s="4" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R2"/>
-  <dataValidations count="11">
-    <dataValidation sqref="D3:D202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Input tidak valid" error="Nilai tidak sesuai referensi template import." promptTitle="Pilihan valid" prompt="Pilih nilai dari daftar referensi yang tersedia." type="list">
+  <dataValidations count="12">
+    <dataValidation sqref="D3:D202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=EmploymentTypeList</formula1>
     </dataValidation>
-    <dataValidation sqref="F3:F202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Input tidak valid" error="Nilai tidak sesuai referensi template import." promptTitle="Pilihan valid" prompt="Pilih nilai dari daftar referensi yang tersedia." type="list">
+    <dataValidation sqref="F3:F202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=DepartmentList</formula1>
     </dataValidation>
-    <dataValidation sqref="J3:J202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Input tidak valid" error="Nilai tidak sesuai referensi template import." promptTitle="Pilihan valid" prompt="Pilih nilai dari daftar referensi yang tersedia." type="list">
+    <dataValidation sqref="G3:G202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=GroupShiftList</formula1>
+    </dataValidation>
+    <dataValidation sqref="K3:K202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=GenderList</formula1>
     </dataValidation>
-    <dataValidation sqref="K3:K202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Input tidak valid" error="Nilai tidak sesuai referensi template import." promptTitle="Pilihan valid" prompt="Pilih nilai dari daftar referensi yang tersedia." type="list">
+    <dataValidation sqref="L3:L202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=WorkLocationList</formula1>
     </dataValidation>
-    <dataValidation sqref="L3:L202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Input tidak valid" error="Nilai tidak sesuai referensi template import." promptTitle="Pilihan valid" prompt="Pilih nilai dari daftar referensi yang tersedia." type="list">
+    <dataValidation sqref="M3:M202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=JobRoleList</formula1>
     </dataValidation>
-    <dataValidation sqref="M3:M202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Input tidak valid" error="Nilai tidak sesuai referensi template import." promptTitle="Pilihan valid" prompt="Pilih nilai dari daftar referensi yang tersedia." type="list">
+    <dataValidation sqref="N3:N202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=JobLevelList</formula1>
     </dataValidation>
-    <dataValidation sqref="N3:N202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Input tidak valid" error="Nilai tidak sesuai referensi template import." promptTitle="Pilihan valid" prompt="Pilih nilai dari daftar referensi yang tersedia." type="list">
+    <dataValidation sqref="O3:O202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=EducationLevelList</formula1>
     </dataValidation>
-    <dataValidation sqref="O3:O202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Input tidak valid" error="Nilai tidak sesuai referensi template import." promptTitle="Pilihan valid" prompt="Pilih nilai dari daftar referensi yang tersedia." type="list">
+    <dataValidation sqref="P3:P202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=GradeList</formula1>
     </dataValidation>
-    <dataValidation sqref="I3:I202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Input tidak valid" error="Tanggal tidak valid." promptTitle="Format tanggal" prompt="Masukkan tanggal dengan format DD/MM/YYYY." type="date" operator="greaterThan">
+    <dataValidation sqref="J3:J202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date">
       <formula1>DATE(1960,1,1)</formula1>
     </dataValidation>
-    <dataValidation sqref="P3:P202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Input tidak valid" error="Tanggal tidak valid." promptTitle="Format tanggal" prompt="Masukkan tanggal dengan format DD/MM/YYYY." type="date" operator="greaterThan">
+    <dataValidation sqref="Q3:Q202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date">
       <formula1>DATE(1960,1,1)</formula1>
     </dataValidation>
-    <dataValidation sqref="R3:R202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Input tidak valid" error="Email harus mengandung karakter @ atau dikosongkan." type="custom">
-      <formula1>OR(R3="",ISNUMBER(SEARCH("@",R3)))</formula1>
+    <dataValidation sqref="S3:S202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="custom">
+      <formula1>OR(S3="",ISNUMBER(SEARCH("@",S3)))</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6796,7 +6810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -6850,6 +6864,11 @@
           <t>Job Level</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Group Shift</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
@@ -6890,6 +6909,11 @@
       <c r="H2" s="8" t="inlineStr">
         <is>
           <t>21212</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Group Shift A</t>
         </is>
       </c>
     </row>
